--- a/BOYS PRESENT.xlsx
+++ b/BOYS PRESENT.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15600" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15600" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="OCT-NOV" sheetId="1" r:id="rId1"/>
+    <sheet name="DEC-JAN" sheetId="2" r:id="rId2"/>
+    <sheet name="STAFF" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
   <extLst>
@@ -19,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="163">
   <si>
     <t>S.NO</t>
   </si>
@@ -66,9 +68,6 @@
     <t>M REHAN</t>
   </si>
   <si>
-    <t>AWAIS JAVAID</t>
-  </si>
-  <si>
     <t>KHIZAR AKRAM</t>
   </si>
   <si>
@@ -490,13 +489,34 @@
   </si>
   <si>
     <t>03321905316</t>
+  </si>
+  <si>
+    <t>OWAIS JAVAID</t>
+  </si>
+  <si>
+    <t>HABIB UL HASSAN</t>
+  </si>
+  <si>
+    <t>ABDUL GHAFFAR</t>
+  </si>
+  <si>
+    <t>03042103958</t>
+  </si>
+  <si>
+    <t>M ANAS</t>
+  </si>
+  <si>
+    <t>M SHAKEEL</t>
+  </si>
+  <si>
+    <t>03222033277</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -579,6 +599,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -654,7 +686,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -691,6 +723,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -988,7 +1028,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -999,7 +1039,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:Y62"/>
+  <dimension ref="B2:Y64"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="3"/>
@@ -1024,28 +1064,28 @@
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="23" t="s">
+      <c r="E2" s="30"/>
+      <c r="F2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
     </row>
     <row r="3" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
@@ -1054,24 +1094,24 @@
       <c r="C3" s="2">
         <v>2025</v>
       </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
     </row>
     <row r="5" spans="2:25" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
@@ -1141,7 +1181,7 @@
         <v>9</v>
       </c>
       <c r="X5" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="2:25" ht="15" x14ac:dyDescent="0.2">
@@ -1149,59 +1189,65 @@
         <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>43</v>
-      </c>
       <c r="F6" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V6" s="7">
         <f>COUNTIF(F6:U6,"P")</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W6" s="7">
         <f>COUNTIF(F6:U6,"A")</f>
@@ -1221,63 +1267,69 @@
         <v>11</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>88</v>
-      </c>
       <c r="F7" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="T7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U7" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V7" s="7">
         <f>COUNTIF(F7:U7,"P")</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W7" s="7">
-        <f t="shared" ref="W7:W55" si="0">COUNTIF(F7:U7,"A")</f>
-        <v>1</v>
+        <f t="shared" ref="W7:W57" si="0">COUNTIF(F7:U7,"A")</f>
+        <v>2</v>
       </c>
       <c r="X7" s="7">
-        <f t="shared" ref="X7:X55" si="1">COUNTIF(F7:P7,"L")</f>
+        <f t="shared" ref="X7:X57" si="1">COUNTIF(F7:P7,"L")</f>
         <v>0</v>
       </c>
       <c r="Y7" s="21"/>
@@ -1290,60 +1342,66 @@
         <v>12</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="T8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="V8" s="7">
         <f>COUNTIF(F8:U8,"P")</f>
         <v>12</v>
       </c>
       <c r="W8" s="7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X8" s="7">
         <f t="shared" si="1"/>
@@ -1356,63 +1414,69 @@
         <v>4</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="V9" s="7">
-        <f t="shared" ref="V9:V55" si="2">COUNTIF(F9:U9,"P")</f>
-        <v>13</v>
+        <f t="shared" ref="V9:V57" si="2">COUNTIF(F9:U9,"P")</f>
+        <v>15</v>
       </c>
       <c r="W9" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="7">
         <f t="shared" si="1"/>
@@ -1424,60 +1488,66 @@
       <c r="B10" s="14">
         <v>5</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="20" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V10" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W10" s="7">
         <f>COUNTIF(F10:U10,"A")</f>
@@ -1497,56 +1567,62 @@
         <v>14</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V11" s="7">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W11" s="7">
         <f>COUNTIF(F11:U11,"A")</f>
@@ -1562,60 +1638,66 @@
       <c r="B12" s="14">
         <v>7</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>15</v>
+      <c r="C12" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U12" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V12" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W12" s="7">
         <f t="shared" si="0"/>
@@ -1631,60 +1713,66 @@
       <c r="B13" s="14">
         <v>8</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>95</v>
+      <c r="C13" s="20" t="s">
+        <v>94</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V13" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W13" s="7">
         <f t="shared" si="0"/>
@@ -1701,63 +1789,69 @@
         <v>9</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O14" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P14" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q14" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R14" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
+        <v>76</v>
+      </c>
+      <c r="S14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="T14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="U14" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="V14" s="16">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W14" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X14" s="16">
         <f t="shared" si="1"/>
@@ -1770,59 +1864,65 @@
         <v>10</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V15" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W15" s="7">
         <f t="shared" si="0"/>
@@ -1839,63 +1939,69 @@
         <v>11</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R16" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
+        <v>77</v>
+      </c>
+      <c r="S16" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="T16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="U16" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="V16" s="16">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W16" s="16">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X16" s="7">
         <f t="shared" si="1"/>
@@ -1908,59 +2014,65 @@
         <v>12</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V17" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W17" s="7">
         <f t="shared" si="0"/>
@@ -1977,59 +2089,65 @@
         <v>13</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V18" s="7">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W18" s="7">
         <f t="shared" si="0"/>
@@ -2046,63 +2164,69 @@
         <v>14</v>
       </c>
       <c r="C19" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D19" s="16" t="s">
-        <v>99</v>
-      </c>
       <c r="E19" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N19" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O19" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P19" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q19" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R19" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
+        <v>76</v>
+      </c>
+      <c r="S19" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="T19" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="U19" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="V19" s="16">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="W19" s="16">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X19" s="16">
         <f t="shared" si="1"/>
@@ -2115,59 +2239,65 @@
         <v>15</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V20" s="7">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W20" s="7">
         <f t="shared" si="0"/>
@@ -2183,60 +2313,66 @@
       <c r="B21" s="14">
         <v>16</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>21</v>
+      <c r="C21" s="20" t="s">
+        <v>20</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V21" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W21" s="7">
         <f t="shared" si="0"/>
@@ -2252,60 +2388,66 @@
       <c r="B22" s="14">
         <v>17</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>22</v>
+      <c r="C22" s="20" t="s">
+        <v>21</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R22" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U22" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V22" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W22" s="7">
         <f t="shared" si="0"/>
@@ -2322,59 +2464,65 @@
         <v>18</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R23" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U23" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V23" s="7">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W23" s="7">
         <f t="shared" si="0"/>
@@ -2390,60 +2538,66 @@
       <c r="B24" s="14">
         <v>19</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>24</v>
+      <c r="C24" s="20" t="s">
+        <v>23</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
-      <c r="U24" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U24" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V24" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W24" s="7">
         <f t="shared" si="0"/>
@@ -2459,60 +2613,66 @@
       <c r="B25" s="14">
         <v>20</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="E25" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U25" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V25" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W25" s="7">
         <f t="shared" si="0"/>
@@ -2529,59 +2689,65 @@
         <v>21</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J26" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N26" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O26" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P26" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q26" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R26" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="S26" s="16"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="16"/>
+        <v>76</v>
+      </c>
+      <c r="S26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="T26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="U26" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="V26" s="16">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W26" s="16">
         <f t="shared" si="0"/>
@@ -2600,59 +2766,65 @@
         <v>22</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N27" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R27" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U27" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V27" s="7">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W27" s="7">
         <f t="shared" si="0"/>
@@ -2668,60 +2840,66 @@
       <c r="B28" s="14">
         <v>23</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>27</v>
+      <c r="C28" s="20" t="s">
+        <v>26</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U28" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V28" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W28" s="7">
         <f t="shared" si="0"/>
@@ -2738,59 +2916,65 @@
         <v>24</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D29" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E29" s="15" t="s">
-        <v>111</v>
-      </c>
       <c r="F29" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R29" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U29" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V29" s="7">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W29" s="7">
         <f t="shared" si="0"/>
@@ -2807,59 +2991,65 @@
         <v>25</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N30" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R30" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
-      <c r="U30" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S30" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T30" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U30" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V30" s="7">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W30" s="7">
         <f t="shared" si="0"/>
@@ -2876,59 +3066,65 @@
         <v>26</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N31" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R31" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U31" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V31" s="7">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W31" s="7">
         <f t="shared" si="0"/>
@@ -2944,60 +3140,66 @@
       <c r="B32" s="14">
         <v>27</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>30</v>
+      <c r="C32" s="20" t="s">
+        <v>29</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N32" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O32" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P32" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
-      <c r="U32" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U32" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V32" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W32" s="7">
         <f t="shared" si="0"/>
@@ -3013,60 +3215,66 @@
       <c r="B33" s="14">
         <v>28</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>31</v>
+      <c r="C33" s="20" t="s">
+        <v>30</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N33" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U33" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V33" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W33" s="7">
         <f t="shared" si="0"/>
@@ -3083,59 +3291,65 @@
         <v>29</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I34" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J34" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N34" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O34" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P34" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q34" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R34" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="S34" s="16"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="16"/>
+        <v>76</v>
+      </c>
+      <c r="S34" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="T34" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="U34" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="V34" s="16">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="W34" s="16">
         <f t="shared" si="0"/>
@@ -3152,63 +3366,69 @@
         <v>30</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N35" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R35" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-      <c r="U35" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U35" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="V35" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W35" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" s="7">
         <f t="shared" si="1"/>
@@ -3221,63 +3441,69 @@
         <v>31</v>
       </c>
       <c r="C36" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D36" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="D36" s="16" t="s">
-        <v>117</v>
-      </c>
       <c r="E36" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J36" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O36" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P36" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q36" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R36" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="S36" s="16"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="16"/>
+        <v>77</v>
+      </c>
+      <c r="S36" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="T36" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="U36" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="V36" s="16">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="W36" s="16">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X36" s="7">
         <f t="shared" si="1"/>
@@ -3290,59 +3516,65 @@
         <v>32</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M37" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N37" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P37" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S37" s="7"/>
-      <c r="T37" s="7"/>
-      <c r="U37" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U37" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V37" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W37" s="7">
         <f t="shared" si="0"/>
@@ -3359,63 +3591,69 @@
         <v>33</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I38" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J38" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N38" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O38" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P38" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q38" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R38" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="S38" s="16"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="16"/>
+        <v>76</v>
+      </c>
+      <c r="S38" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="T38" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="U38" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="V38" s="16">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W38" s="16">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X38" s="16">
         <f t="shared" si="1"/>
@@ -3428,59 +3666,65 @@
         <v>34</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I39" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J39" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N39" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O39" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P39" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q39" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R39" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="S39" s="16"/>
-      <c r="T39" s="16"/>
-      <c r="U39" s="16"/>
+        <v>76</v>
+      </c>
+      <c r="S39" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="T39" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="U39" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="V39" s="16">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W39" s="16">
         <f t="shared" si="0"/>
@@ -3497,63 +3741,69 @@
         <v>35</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J40" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N40" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O40" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P40" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R40" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S40" s="7"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="U40" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V40" s="7">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W40" s="7">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X40" s="7">
         <f t="shared" si="1"/>
@@ -3566,59 +3816,65 @@
         <v>36</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M41" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N41" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P41" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R41" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="S41" s="7"/>
-      <c r="T41" s="7"/>
-      <c r="U41" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="S41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U41" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V41" s="7">
         <f>COUNTIF(F41:U41,"P")</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W41" s="7">
         <f>COUNTIF(F41:U41,"A")</f>
@@ -3635,59 +3891,65 @@
         <v>37</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H42" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I42" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J42" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N42" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O42" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P42" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q42" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R42" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="S42" s="16"/>
-      <c r="T42" s="16"/>
-      <c r="U42" s="16"/>
+        <v>80</v>
+      </c>
+      <c r="S42" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="T42" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="U42" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="V42" s="16">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W42" s="16">
         <f t="shared" si="0"/>
@@ -3703,60 +3965,66 @@
       <c r="B43" s="14">
         <v>38</v>
       </c>
-      <c r="C43" s="16" t="s">
-        <v>38</v>
+      <c r="C43" s="20" t="s">
+        <v>37</v>
       </c>
       <c r="D43" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E43" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E43" s="15" t="s">
-        <v>124</v>
-      </c>
       <c r="F43" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M43" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N43" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O43" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P43" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R43" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S43" s="7"/>
-      <c r="T43" s="7"/>
-      <c r="U43" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T43" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U43" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V43" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W43" s="7">
         <f t="shared" si="0"/>
@@ -3773,59 +4041,65 @@
         <v>39</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M44" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N44" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O44" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P44" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R44" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="S44" s="7"/>
-      <c r="T44" s="7"/>
-      <c r="U44" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="S44" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T44" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U44" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V44" s="7">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W44" s="7">
         <f t="shared" si="0"/>
@@ -3842,59 +4116,65 @@
         <v>40</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N45" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O45" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P45" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R45" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="S45" s="7"/>
-      <c r="T45" s="7"/>
-      <c r="U45" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="S45" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T45" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U45" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V45" s="7">
         <f>COUNTIF(F45:U45,"P")</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W45" s="7">
         <f>COUNTIF(F45:U45,"A")</f>
@@ -3911,63 +4191,69 @@
         <v>41</v>
       </c>
       <c r="C46" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E46" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>130</v>
-      </c>
       <c r="F46" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N46" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O46" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P46" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R46" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="S46" s="7"/>
-      <c r="T46" s="7"/>
-      <c r="U46" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="S46" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="T46" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U46" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V46" s="7">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W46" s="7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X46" s="7">
         <f t="shared" si="1"/>
@@ -3980,59 +4266,65 @@
         <v>42</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M47" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N47" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P47" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R47" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S47" s="7"/>
-      <c r="T47" s="7"/>
-      <c r="U47" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V47" s="7">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W47" s="7">
         <f t="shared" si="0"/>
@@ -4049,63 +4341,69 @@
         <v>43</v>
       </c>
       <c r="C48" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D48" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="E48" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="E48" s="15" t="s">
-        <v>137</v>
-      </c>
       <c r="F48" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N48" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O48" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P48" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R48" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="S48" s="7"/>
-      <c r="T48" s="7"/>
-      <c r="U48" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="S48" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="T48" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U48" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="V48" s="7">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W48" s="7">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X48" s="7">
         <f t="shared" si="1"/>
@@ -4118,63 +4416,69 @@
         <v>44</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D49" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E49" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E49" s="15" t="s">
-        <v>132</v>
-      </c>
       <c r="F49" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M49" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N49" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O49" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P49" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R49" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="S49" s="7"/>
-      <c r="T49" s="7"/>
-      <c r="U49" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="S49" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="T49" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="U49" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="V49" s="7">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="W49" s="7">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="X49" s="7">
         <f t="shared" si="1"/>
@@ -4187,13 +4491,13 @@
         <v>45</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>77</v>
@@ -4208,46 +4512,52 @@
         <v>77</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="M50" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="N50" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="O50" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="P50" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q50" s="7" t="s">
         <v>77</v>
       </c>
       <c r="R50" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="S50" s="7"/>
-      <c r="T50" s="7"/>
-      <c r="U50" s="7"/>
+        <v>77</v>
+      </c>
+      <c r="S50" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="T50" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="U50" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V50" s="7">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W50" s="7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="X50" s="7">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y50" s="21"/>
     </row>
@@ -4256,67 +4566,73 @@
         <v>46</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N51" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="P51" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R51" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="S51" s="7"/>
-      <c r="T51" s="7"/>
-      <c r="U51" s="7"/>
+      <c r="S51" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="T51" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="U51" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="V51" s="7">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="W51" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X51" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y51" s="21"/>
     </row>
@@ -4325,59 +4641,65 @@
         <v>47</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M52" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N52" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="O52" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="P52" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="R52" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="S52" s="7"/>
-      <c r="T52" s="7"/>
-      <c r="U52" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="S52" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="T52" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U52" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V52" s="7">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="W52" s="7">
         <f t="shared" si="0"/>
@@ -4385,7 +4707,7 @@
       </c>
       <c r="X52" s="7">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y52" s="21"/>
     </row>
@@ -4394,59 +4716,65 @@
         <v>48</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M53" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N53" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="O53" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="P53" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="R53" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="S53" s="7"/>
-      <c r="T53" s="7"/>
-      <c r="U53" s="7"/>
+        <v>80</v>
+      </c>
+      <c r="S53" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="T53" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U53" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V53" s="7">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W53" s="7">
         <f t="shared" si="0"/>
@@ -4454,7 +4782,7 @@
       </c>
       <c r="X53" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y53" s="21"/>
     </row>
@@ -4466,56 +4794,62 @@
         <v>147</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M54" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N54" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O54" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P54" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R54" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S54" s="7"/>
-      <c r="T54" s="7"/>
-      <c r="U54" s="7"/>
+        <v>80</v>
+      </c>
+      <c r="S54" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="T54" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="U54" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="V54" s="7">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="W54" s="7">
         <f t="shared" si="0"/>
@@ -4523,7 +4857,7 @@
       </c>
       <c r="X54" s="7">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y54" s="21"/>
     </row>
@@ -4532,312 +4866,3913 @@
         <v>50</v>
       </c>
       <c r="C55" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M55" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N55" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O55" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P55" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q55" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R55" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S55" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T55" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U55" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V55" s="7">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="W55" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X55" s="7">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="Y55" s="21"/>
+    </row>
+    <row r="56" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+      <c r="B56" s="14">
+        <v>51</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M56" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N56" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="O56" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="P56" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q56" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R56" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S56" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T56" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U56" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V56" s="7">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="W56" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X56" s="7">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Y56" s="21"/>
+    </row>
+    <row r="57" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+      <c r="B57" s="14">
+        <v>52</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D57" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="E57" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="E55" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K55" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="L55" s="7" t="s">
+      <c r="F57" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="M57" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N57" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="O57" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="P57" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q57" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="R57" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S57" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="T57" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U57" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V57" s="7">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="W57" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="X57" s="7">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="Y57" s="21"/>
+    </row>
+    <row r="58" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B58" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="M55" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="N55" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="O55" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="P55" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q55" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="R55" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S55" s="7"/>
-      <c r="T55" s="7"/>
-      <c r="U55" s="7"/>
-      <c r="V55" s="7">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="W55" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X55" s="7">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="Y55" s="21"/>
-    </row>
-    <row r="56" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B56" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C56" s="28"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="8">
-        <f>COUNTIF(F6:F55,"P")</f>
-        <v>33</v>
-      </c>
-      <c r="G56" s="8">
-        <f t="shared" ref="G56:U56" si="3">COUNTIF(G6:G55,"P")</f>
-        <v>37</v>
-      </c>
-      <c r="H56" s="8">
+      <c r="C58" s="32"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="8">
+        <f>COUNTIF(F6:F57,"P")</f>
+        <v>34</v>
+      </c>
+      <c r="G58" s="8">
+        <f t="shared" ref="G58:U58" si="3">COUNTIF(G6:G57,"P")</f>
+        <v>38</v>
+      </c>
+      <c r="H58" s="8">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="I56" s="8">
+      <c r="I58" s="8">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="J56" s="8">
+      <c r="J58" s="8">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="K56" s="8">
+      <c r="K58" s="8">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="L58" s="8">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="M58" s="8">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="N58" s="8">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="L56" s="8">
+      <c r="O58" s="8">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="P58" s="8">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="Q58" s="8">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="R58" s="8">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="S58" s="8">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="T58" s="8">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="M56" s="8">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="N56" s="8">
+      <c r="U58" s="8">
         <f t="shared" si="3"/>
         <v>42</v>
-      </c>
-      <c r="O56" s="8">
-        <f t="shared" si="3"/>
-        <v>41</v>
-      </c>
-      <c r="P56" s="8">
-        <f t="shared" si="3"/>
-        <v>39</v>
-      </c>
-      <c r="Q56" s="8">
-        <f t="shared" si="3"/>
-        <v>44</v>
-      </c>
-      <c r="R56" s="8">
-        <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-      <c r="S56" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T56" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U56" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V56" s="7"/>
-      <c r="W56" s="7"/>
-      <c r="X56" s="7"/>
-      <c r="Y56" s="21"/>
-    </row>
-    <row r="57" spans="2:25" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B57" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C57" s="29"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7">
-        <f>COUNTIF(F6:F55,"A")</f>
-        <v>17</v>
-      </c>
-      <c r="G57" s="7">
-        <f t="shared" ref="G57:U57" si="4">COUNTIF(G6:G55,"A")</f>
-        <v>12</v>
-      </c>
-      <c r="H57" s="7">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="I57" s="7">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="J57" s="7">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="K57" s="7">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="L57" s="7">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="M57" s="7">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="N57" s="7">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="O57" s="7">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="P57" s="7">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="Q57" s="7">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="R57" s="7">
-        <f t="shared" si="4"/>
-        <v>13</v>
-      </c>
-      <c r="S57" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T57" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U57" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V57" s="7"/>
-      <c r="W57" s="7"/>
-      <c r="X57" s="7"/>
-      <c r="Y57" s="21"/>
-    </row>
-    <row r="58" spans="2:25" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B58" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C58" s="22"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7">
-        <f>COUNTIF(F6:F55,"L")</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="7">
-        <f t="shared" ref="G58:U58" si="5">COUNTIF(G6:G55,"L")</f>
-        <v>1</v>
-      </c>
-      <c r="H58" s="7">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="I58" s="7">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="J58" s="7">
-        <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="K58" s="7">
-        <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="L58" s="7">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="M58" s="7">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="N58" s="7">
-        <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="O58" s="7">
-        <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="P58" s="7">
-        <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="Q58" s="7">
-        <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="R58" s="7">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="S58" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T58" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U58" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
       </c>
       <c r="V58" s="7"/>
       <c r="W58" s="7"/>
       <c r="X58" s="7"/>
       <c r="Y58" s="21"/>
     </row>
-    <row r="62" spans="2:25" x14ac:dyDescent="0.2">
-      <c r="S62" s="3" t="s">
-        <v>85</v>
+    <row r="59" spans="2:25" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B59" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59" s="33"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7">
+        <f>COUNTIF(F6:F57,"A")</f>
+        <v>18</v>
+      </c>
+      <c r="G59" s="7">
+        <f t="shared" ref="G59:U59" si="4">COUNTIF(G6:G57,"A")</f>
+        <v>13</v>
+      </c>
+      <c r="H59" s="7">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="I59" s="7">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="J59" s="7">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="K59" s="7">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="L59" s="7">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="M59" s="7">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="N59" s="7">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="O59" s="7">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="P59" s="7">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="Q59" s="7">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="R59" s="7">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="S59" s="7">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="T59" s="7">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="U59" s="7">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="V59" s="7"/>
+      <c r="W59" s="7"/>
+      <c r="X59" s="7"/>
+      <c r="Y59" s="21"/>
+    </row>
+    <row r="60" spans="2:25" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B60" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" s="26"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7">
+        <f>COUNTIF(F6:F57,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="7">
+        <f t="shared" ref="G60:U60" si="5">COUNTIF(G6:G57,"L")</f>
+        <v>1</v>
+      </c>
+      <c r="H60" s="7">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="I60" s="7">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="J60" s="7">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="K60" s="7">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="L60" s="7">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="M60" s="7">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="N60" s="7">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="O60" s="7">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="P60" s="7">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="Q60" s="7">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="R60" s="7">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="S60" s="7">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="T60" s="7">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="U60" s="7">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="V60" s="7"/>
+      <c r="W60" s="7"/>
+      <c r="X60" s="7"/>
+      <c r="Y60" s="21"/>
+    </row>
+    <row r="64" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="S64" s="3" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="F2:U3"/>
     <mergeCell ref="D2:E3"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="77" fitToWidth="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:Z55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="27.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" hidden="1" customWidth="1"/>
+    <col min="6" max="13" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="22" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="25">
+        <v>45941</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="30"/>
+      <c r="F2" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+    </row>
+    <row r="3" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="22">
+        <v>2025</v>
+      </c>
+      <c r="D3" s="31"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+    </row>
+    <row r="4" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B4" s="5"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+    </row>
+    <row r="5" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="8">
+        <v>6</v>
+      </c>
+      <c r="G5" s="8">
+        <v>7</v>
+      </c>
+      <c r="H5" s="8">
+        <v>13</v>
+      </c>
+      <c r="I5" s="8">
+        <v>14</v>
+      </c>
+      <c r="J5" s="8">
+        <v>20</v>
+      </c>
+      <c r="K5" s="8">
+        <v>21</v>
+      </c>
+      <c r="L5" s="8">
+        <v>27</v>
+      </c>
+      <c r="M5" s="8">
+        <v>28</v>
+      </c>
+      <c r="N5" s="8">
+        <v>3</v>
+      </c>
+      <c r="O5" s="8">
+        <v>4</v>
+      </c>
+      <c r="P5" s="8">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>11</v>
+      </c>
+      <c r="R5" s="8">
+        <v>17</v>
+      </c>
+      <c r="S5" s="8">
+        <v>18</v>
+      </c>
+      <c r="T5" s="8">
+        <v>24</v>
+      </c>
+      <c r="U5" s="8">
+        <v>25</v>
+      </c>
+      <c r="V5" s="8">
+        <v>31</v>
+      </c>
+      <c r="W5" s="8">
+        <v>1</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="14">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7">
+        <f t="shared" ref="X6:X52" si="0">COUNTIF(F6:W6,"P")</f>
+        <v>1</v>
+      </c>
+      <c r="Y6" s="7">
+        <f t="shared" ref="Y6:Y52" si="1">COUNTIF(F6:W6,"A")</f>
+        <v>2</v>
+      </c>
+      <c r="Z6" s="7">
+        <f t="shared" ref="Z6:Z52" si="2">COUNTIF(F6:P6,"L")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="14">
+        <v>2</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y7" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Z7" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="14">
+        <v>3</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="7">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Z8" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="14">
+        <v>4</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y9" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="14">
+        <v>5</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y10" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="14">
+        <v>6</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y11" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="14">
+        <v>7</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y12" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="14">
+        <v>8</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y13" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="14">
+        <v>9</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
+      <c r="X14" s="16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y14" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z14" s="16">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="14">
+        <v>10</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y15" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z15" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="14">
+        <v>11</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y16" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z16" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="14">
+        <v>12</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y17" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z17" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="14">
+        <v>13</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y18" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="14">
+        <v>14</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="16">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Z19" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="14">
+        <v>15</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y20" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="14">
+        <v>16</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7"/>
+      <c r="X21" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y21" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="14">
+        <v>17</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y22" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="14">
+        <v>18</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y23" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="14">
+        <v>19</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7"/>
+      <c r="X24" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y24" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z24" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B25" s="14">
+        <v>20</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y25" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="14">
+        <v>21</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="16"/>
+      <c r="U26" s="16"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="16"/>
+      <c r="X26" s="16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y26" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z26" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="14">
+        <v>22</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7"/>
+      <c r="X27" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y27" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="14">
+        <v>23</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7"/>
+      <c r="X28" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y28" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="14">
+        <v>24</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7"/>
+      <c r="X29" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y29" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z29" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="14">
+        <v>25</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7"/>
+      <c r="W30" s="7"/>
+      <c r="X30" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y30" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="14">
+        <v>26</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y31" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Z31" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="14">
+        <v>27</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="7"/>
+      <c r="V32" s="7"/>
+      <c r="W32" s="7"/>
+      <c r="X32" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y32" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z32" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="14">
+        <v>28</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7"/>
+      <c r="X33" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y33" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z33" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B34" s="14">
+        <v>29</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="16"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="16"/>
+      <c r="Q34" s="16"/>
+      <c r="R34" s="16"/>
+      <c r="S34" s="16"/>
+      <c r="T34" s="16"/>
+      <c r="U34" s="16"/>
+      <c r="V34" s="16"/>
+      <c r="W34" s="16"/>
+      <c r="X34" s="16">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y34" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="14">
+        <v>30</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y35" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z35" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="14">
+        <v>31</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="16"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16"/>
+      <c r="S36" s="16"/>
+      <c r="T36" s="16"/>
+      <c r="U36" s="16"/>
+      <c r="V36" s="16"/>
+      <c r="W36" s="16"/>
+      <c r="X36" s="16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y36" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z36" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B37" s="14">
+        <v>32</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y37" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="14">
+        <v>33</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+      <c r="N38" s="16"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="16"/>
+      <c r="Q38" s="16"/>
+      <c r="R38" s="16"/>
+      <c r="S38" s="16"/>
+      <c r="T38" s="16"/>
+      <c r="U38" s="16"/>
+      <c r="V38" s="16"/>
+      <c r="W38" s="16"/>
+      <c r="X38" s="16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y38" s="16">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Z38" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="17">
+        <v>34</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="16"/>
+      <c r="Q39" s="16"/>
+      <c r="R39" s="16"/>
+      <c r="S39" s="16"/>
+      <c r="T39" s="16"/>
+      <c r="U39" s="16"/>
+      <c r="V39" s="16"/>
+      <c r="W39" s="16"/>
+      <c r="X39" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="16">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Z39" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B40" s="14">
+        <v>35</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="7"/>
+      <c r="W40" s="7"/>
+      <c r="X40" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y40" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Z40" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B41" s="14">
+        <v>36</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="7"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y41" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z41" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B42" s="17">
+        <v>37</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="16"/>
+      <c r="O42" s="16"/>
+      <c r="P42" s="16"/>
+      <c r="Q42" s="16"/>
+      <c r="R42" s="16"/>
+      <c r="S42" s="16"/>
+      <c r="T42" s="16"/>
+      <c r="U42" s="16"/>
+      <c r="V42" s="16"/>
+      <c r="W42" s="16"/>
+      <c r="X42" s="16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y42" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z42" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B43" s="14">
+        <v>38</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="7"/>
+      <c r="N43" s="7"/>
+      <c r="O43" s="7"/>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="7"/>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="U43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
+      <c r="X43" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y43" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z43" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B44" s="14">
+        <v>39</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="7"/>
+      <c r="N44" s="7"/>
+      <c r="O44" s="7"/>
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7"/>
+      <c r="R44" s="7"/>
+      <c r="S44" s="7"/>
+      <c r="T44" s="7"/>
+      <c r="U44" s="7"/>
+      <c r="V44" s="7"/>
+      <c r="W44" s="7"/>
+      <c r="X44" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y44" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B45" s="14">
+        <v>40</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="7"/>
+      <c r="O45" s="7"/>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="7"/>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+      <c r="U45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="7"/>
+      <c r="X45" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y45" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z45" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B46" s="14">
+        <v>41</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="7"/>
+      <c r="X46" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y46" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z46" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B47" s="14">
+        <v>42</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y47" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z47" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B48" s="14">
+        <v>43</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="7"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
+      <c r="R48" s="7"/>
+      <c r="S48" s="7"/>
+      <c r="T48" s="7"/>
+      <c r="U48" s="7"/>
+      <c r="V48" s="7"/>
+      <c r="W48" s="7"/>
+      <c r="X48" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="7">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Z48" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B49" s="14">
+        <v>44</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+      <c r="R49" s="7"/>
+      <c r="S49" s="7"/>
+      <c r="T49" s="7"/>
+      <c r="U49" s="7"/>
+      <c r="V49" s="7"/>
+      <c r="W49" s="7"/>
+      <c r="X49" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="7">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Z49" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B50" s="14">
+        <v>45</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="7"/>
+      <c r="O50" s="7"/>
+      <c r="P50" s="7"/>
+      <c r="Q50" s="7"/>
+      <c r="R50" s="7"/>
+      <c r="S50" s="7"/>
+      <c r="T50" s="7"/>
+      <c r="U50" s="7"/>
+      <c r="V50" s="7"/>
+      <c r="W50" s="7"/>
+      <c r="X50" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="7">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Z50" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B51" s="14">
+        <v>46</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+      <c r="M51" s="7"/>
+      <c r="N51" s="7"/>
+      <c r="O51" s="7"/>
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="7"/>
+      <c r="S51" s="7"/>
+      <c r="T51" s="7"/>
+      <c r="U51" s="7"/>
+      <c r="V51" s="7"/>
+      <c r="W51" s="7"/>
+      <c r="X51" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="7">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Z51" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B52" s="14">
+        <v>47</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
+      <c r="K52" s="7"/>
+      <c r="L52" s="7"/>
+      <c r="M52" s="7"/>
+      <c r="N52" s="7"/>
+      <c r="O52" s="7"/>
+      <c r="P52" s="7"/>
+      <c r="Q52" s="7"/>
+      <c r="R52" s="7"/>
+      <c r="S52" s="7"/>
+      <c r="T52" s="7"/>
+      <c r="U52" s="7"/>
+      <c r="V52" s="7"/>
+      <c r="W52" s="7"/>
+      <c r="X52" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y52" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z52" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B53" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" s="32"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="8">
+        <f t="shared" ref="F53:S53" si="3">COUNTIF(F6:F52,"P")</f>
+        <v>31</v>
+      </c>
+      <c r="G53" s="8">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="H53" s="8">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="I53" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L53" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M53" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N53" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O53" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P53" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q53" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R53" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="8"/>
+      <c r="U53" s="8"/>
+      <c r="V53" s="8">
+        <f>COUNTIF(V6:V52,"P")</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="8">
+        <f>COUNTIF(W6:W52,"P")</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="7"/>
+      <c r="Y53" s="7"/>
+      <c r="Z53" s="7"/>
+    </row>
+    <row r="54" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B54" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C54" s="33"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7">
+        <f t="shared" ref="F54:S54" si="4">COUNTIF(F6:F52,"A")</f>
+        <v>15</v>
+      </c>
+      <c r="G54" s="7">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="H54" s="7">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="I54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="7"/>
+      <c r="U54" s="7"/>
+      <c r="V54" s="7">
+        <f>COUNTIF(V6:V52,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="W54" s="7">
+        <f>COUNTIF(W6:W52,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="X54" s="7"/>
+      <c r="Y54" s="7"/>
+      <c r="Z54" s="7"/>
+    </row>
+    <row r="55" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B55" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" s="26"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7">
+        <f t="shared" ref="F55:S55" si="5">COUNTIF(F6:F52,"L")</f>
+        <v>1</v>
+      </c>
+      <c r="G55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H55" s="7">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="7"/>
+      <c r="U55" s="7"/>
+      <c r="V55" s="7">
+        <f>COUNTIF(V6:V52,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="W55" s="7">
+        <f>COUNTIF(W6:W52,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="X55" s="7"/>
+      <c r="Y55" s="7"/>
+      <c r="Z55" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D2:E3"/>
+    <mergeCell ref="F2:W3"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C2:AA13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="25">
+        <v>45941</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="30"/>
+      <c r="G2" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+    </row>
+    <row r="3" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="22">
+        <v>2025</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+    </row>
+    <row r="4" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="C4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+    </row>
+    <row r="5" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C5" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="8">
+        <v>6</v>
+      </c>
+      <c r="H5" s="8">
+        <v>7</v>
+      </c>
+      <c r="I5" s="8">
+        <v>13</v>
+      </c>
+      <c r="J5" s="8">
+        <v>14</v>
+      </c>
+      <c r="K5" s="8">
+        <v>20</v>
+      </c>
+      <c r="L5" s="8">
+        <v>21</v>
+      </c>
+      <c r="M5" s="8">
+        <v>27</v>
+      </c>
+      <c r="N5" s="8">
+        <v>28</v>
+      </c>
+      <c r="O5" s="8">
+        <v>3</v>
+      </c>
+      <c r="P5" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>10</v>
+      </c>
+      <c r="R5" s="8">
+        <v>11</v>
+      </c>
+      <c r="S5" s="8">
+        <v>17</v>
+      </c>
+      <c r="T5" s="8">
+        <v>18</v>
+      </c>
+      <c r="U5" s="8">
+        <v>24</v>
+      </c>
+      <c r="V5" s="8">
+        <v>25</v>
+      </c>
+      <c r="W5" s="8">
+        <v>31</v>
+      </c>
+      <c r="X5" s="8">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C6" s="14">
+        <v>47</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7">
+        <f>COUNTIF(G6:X6,"P")</f>
+        <v>3</v>
+      </c>
+      <c r="Z6" s="7">
+        <f>COUNTIF(G6:X6,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="7">
+        <f>COUNTIF(G6:Q6,"L")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C7" s="14">
+        <v>48</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7">
+        <f>COUNTIF(G7:X7,"P")</f>
+        <v>1</v>
+      </c>
+      <c r="Z7" s="7">
+        <f>COUNTIF(G7:X7,"A")</f>
+        <v>1</v>
+      </c>
+      <c r="AA7" s="7">
+        <f>COUNTIF(G7:Q7,"L")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C8" s="14">
+        <v>49</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7">
+        <f>COUNTIF(G8:X8,"P")</f>
+        <v>3</v>
+      </c>
+      <c r="Z8" s="7">
+        <f>COUNTIF(G8:X8,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AA8" s="7">
+        <f>COUNTIF(G8:Q8,"L")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C9" s="14">
+        <v>50</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7">
+        <f>COUNTIF(G9:X9,"P")</f>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="7">
+        <f>COUNTIF(G9:X9,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AA9" s="7">
+        <f>COUNTIF(G9:Q9,"L")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C10" s="14">
+        <v>51</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7">
+        <f>COUNTIF(G10:X10,"P")</f>
+        <v>1</v>
+      </c>
+      <c r="Z10" s="7">
+        <f>COUNTIF(G10:X10,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AA10" s="7">
+        <f>COUNTIF(G10:Q10,"L")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C11" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="32"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="N11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="S11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="X11" s="8" t="e">
+        <f>COUNTIF(#REF!,"P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+    </row>
+    <row r="12" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C12" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="33"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="N12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="S12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="X12" s="7" t="e">
+        <f>COUNTIF(#REF!,"A")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+    </row>
+    <row r="13" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C13" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="26"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="N13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="P13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Q13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="R13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="S13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="T13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="X13" s="7" t="e">
+        <f>COUNTIF(#REF!,"L")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="E2:F3"/>
+    <mergeCell ref="G2:X3"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/BOYS PRESENT.xlsx
+++ b/BOYS PRESENT.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="165">
   <si>
     <t>S.NO</t>
   </si>
@@ -510,13 +510,19 @@
   </si>
   <si>
     <t>03222033277</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>a</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -611,6 +617,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -649,7 +668,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -681,12 +700,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -731,6 +787,12 @@
     <xf numFmtId="16" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -754,6 +816,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1064,28 +1135,28 @@
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="27" t="s">
+      <c r="E2" s="34"/>
+      <c r="F2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
     </row>
     <row r="3" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
@@ -1094,24 +1165,24 @@
       <c r="C3" s="2">
         <v>2025</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
     </row>
     <row r="5" spans="2:25" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
@@ -5087,10 +5158,10 @@
       <c r="Y57" s="21"/>
     </row>
     <row r="58" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B58" s="32" t="s">
+      <c r="B58" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="C58" s="32"/>
+      <c r="C58" s="36"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
       <c r="F58" s="8">
@@ -5163,10 +5234,10 @@
       <c r="Y58" s="21"/>
     </row>
     <row r="59" spans="2:25" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B59" s="33" t="s">
+      <c r="B59" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="C59" s="33"/>
+      <c r="C59" s="37"/>
       <c r="D59" s="9"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7">
@@ -5239,10 +5310,10 @@
       <c r="Y59" s="21"/>
     </row>
     <row r="60" spans="2:25" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B60" s="26" t="s">
+      <c r="B60" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C60" s="26"/>
+      <c r="C60" s="30"/>
       <c r="D60" s="9"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7">
@@ -5353,30 +5424,30 @@
       <c r="C2" s="25">
         <v>45941</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="27" t="s">
+      <c r="E2" s="34"/>
+      <c r="F2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
@@ -5388,26 +5459,26 @@
       <c r="C3" s="22">
         <v>2025</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
@@ -5536,12 +5607,18 @@
         <v>76</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="I6" s="38"/>
+      <c r="J6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
@@ -5555,7 +5632,7 @@
       <c r="W6" s="7"/>
       <c r="X6" s="7">
         <f t="shared" ref="X6:X52" si="0">COUNTIF(F6:W6,"P")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y6" s="7">
         <f t="shared" ref="Y6:Y52" si="1">COUNTIF(F6:W6,"A")</f>
@@ -5588,10 +5665,16 @@
       <c r="H7" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
@@ -5605,7 +5688,7 @@
       <c r="W7" s="7"/>
       <c r="X7" s="7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y7" s="7">
         <f t="shared" si="1"/>
@@ -5638,10 +5721,16 @@
       <c r="H8" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>164</v>
+      </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
@@ -5659,7 +5748,7 @@
       </c>
       <c r="Y8" s="7">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z8" s="7">
         <f t="shared" si="2"/>
@@ -5688,10 +5777,16 @@
       <c r="H9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
@@ -5705,7 +5800,7 @@
       <c r="W9" s="7"/>
       <c r="X9" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y9" s="7">
         <f t="shared" si="1"/>
@@ -5738,10 +5833,16 @@
       <c r="H10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
@@ -5755,7 +5856,7 @@
       <c r="W10" s="7"/>
       <c r="X10" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y10" s="7">
         <f t="shared" si="1"/>
@@ -5788,10 +5889,16 @@
       <c r="H11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
@@ -5805,7 +5912,7 @@
       <c r="W11" s="7"/>
       <c r="X11" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y11" s="7">
         <f t="shared" si="1"/>
@@ -5838,10 +5945,16 @@
       <c r="H12" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
@@ -5855,7 +5968,7 @@
       <c r="W12" s="7"/>
       <c r="X12" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y12" s="7">
         <f t="shared" si="1"/>
@@ -5888,10 +6001,16 @@
       <c r="H13" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
@@ -5905,7 +6024,7 @@
       <c r="W13" s="7"/>
       <c r="X13" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y13" s="7">
         <f t="shared" si="1"/>
@@ -5936,13 +6055,19 @@
         <v>76</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
+        <v>80</v>
+      </c>
+      <c r="I14" s="39"/>
+      <c r="J14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="M14" s="7"/>
       <c r="N14" s="16"/>
       <c r="O14" s="16"/>
       <c r="P14" s="16"/>
@@ -5955,15 +6080,15 @@
       <c r="W14" s="16"/>
       <c r="X14" s="16">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y14" s="16">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="16">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
@@ -5988,10 +6113,16 @@
       <c r="H15" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -6005,7 +6136,7 @@
       <c r="W15" s="7"/>
       <c r="X15" s="7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y15" s="7">
         <f t="shared" si="1"/>
@@ -6038,11 +6169,17 @@
       <c r="H16" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="M16" s="7"/>
       <c r="N16" s="16"/>
       <c r="O16" s="16"/>
       <c r="P16" s="16"/>
@@ -6055,7 +6192,7 @@
       <c r="W16" s="16"/>
       <c r="X16" s="16">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y16" s="16">
         <f t="shared" si="1"/>
@@ -6088,10 +6225,16 @@
       <c r="H17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
@@ -6105,7 +6248,7 @@
       <c r="W17" s="7"/>
       <c r="X17" s="7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y17" s="7">
         <f t="shared" si="1"/>
@@ -6138,10 +6281,16 @@
       <c r="H18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
@@ -6155,7 +6304,7 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y18" s="7">
         <f t="shared" si="1"/>
@@ -6188,11 +6337,17 @@
       <c r="H19" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="M19" s="7"/>
       <c r="N19" s="16"/>
       <c r="O19" s="16"/>
       <c r="P19" s="16"/>
@@ -6209,7 +6364,7 @@
       </c>
       <c r="Y19" s="16">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z19" s="16">
         <f t="shared" si="2"/>
@@ -6238,10 +6393,16 @@
       <c r="H20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M20" s="7"/>
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
@@ -6255,11 +6416,11 @@
       <c r="W20" s="7"/>
       <c r="X20" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y20" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="7">
         <f t="shared" si="2"/>
@@ -6288,10 +6449,16 @@
       <c r="H21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
@@ -6305,7 +6472,7 @@
       <c r="W21" s="7"/>
       <c r="X21" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y21" s="7">
         <f t="shared" si="1"/>
@@ -6338,10 +6505,16 @@
       <c r="H22" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
@@ -6355,7 +6528,7 @@
       <c r="W22" s="7"/>
       <c r="X22" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y22" s="7">
         <f t="shared" si="1"/>
@@ -6366,52 +6539,58 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="14">
+    <row r="23" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="26">
         <v>18</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="F23" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
+      <c r="F23" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="39"/>
+      <c r="J23" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K23" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L23" s="27" t="s">
+        <v>164</v>
+      </c>
       <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="7"/>
-      <c r="X23" s="7">
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="27"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27"/>
+      <c r="W23" s="27"/>
+      <c r="X23" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Y23" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z23" s="7">
+      <c r="Y23" s="27">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Z23" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6438,10 +6617,16 @@
       <c r="H24" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M24" s="7"/>
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
@@ -6455,7 +6640,7 @@
       <c r="W24" s="7"/>
       <c r="X24" s="7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y24" s="7">
         <f t="shared" si="1"/>
@@ -6488,10 +6673,16 @@
       <c r="H25" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M25" s="7"/>
       <c r="N25" s="7"/>
       <c r="O25" s="7"/>
@@ -6505,7 +6696,7 @@
       <c r="W25" s="7"/>
       <c r="X25" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y25" s="7">
         <f t="shared" si="1"/>
@@ -6538,11 +6729,17 @@
       <c r="H26" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="M26" s="7"/>
       <c r="N26" s="16"/>
       <c r="O26" s="16"/>
       <c r="P26" s="16"/>
@@ -6559,7 +6756,7 @@
       </c>
       <c r="Y26" s="16">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z26" s="16">
         <f t="shared" si="2"/>
@@ -6588,10 +6785,16 @@
       <c r="H27" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
@@ -6605,7 +6808,7 @@
       <c r="W27" s="7"/>
       <c r="X27" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y27" s="7">
         <f t="shared" si="1"/>
@@ -6638,10 +6841,16 @@
       <c r="H28" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M28" s="7"/>
       <c r="N28" s="7"/>
       <c r="O28" s="7"/>
@@ -6655,7 +6864,7 @@
       <c r="W28" s="7"/>
       <c r="X28" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y28" s="7">
         <f t="shared" si="1"/>
@@ -6688,10 +6897,16 @@
       <c r="H29" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M29" s="7"/>
       <c r="N29" s="7"/>
       <c r="O29" s="7"/>
@@ -6705,7 +6920,7 @@
       <c r="W29" s="7"/>
       <c r="X29" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y29" s="7">
         <f t="shared" si="1"/>
@@ -6738,10 +6953,16 @@
       <c r="H30" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M30" s="7"/>
       <c r="N30" s="7"/>
       <c r="O30" s="7"/>
@@ -6755,7 +6976,7 @@
       <c r="W30" s="7"/>
       <c r="X30" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y30" s="7">
         <f t="shared" si="1"/>
@@ -6788,10 +7009,16 @@
       <c r="H31" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>164</v>
+      </c>
       <c r="M31" s="7"/>
       <c r="N31" s="7"/>
       <c r="O31" s="7"/>
@@ -6809,7 +7036,7 @@
       </c>
       <c r="Y31" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z31" s="7">
         <f t="shared" si="2"/>
@@ -6838,10 +7065,16 @@
       <c r="H32" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M32" s="7"/>
       <c r="N32" s="7"/>
       <c r="O32" s="7"/>
@@ -6855,7 +7088,7 @@
       <c r="W32" s="7"/>
       <c r="X32" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y32" s="7">
         <f t="shared" si="1"/>
@@ -6866,52 +7099,58 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="14">
+    <row r="33" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="26">
         <v>28</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="7"/>
-      <c r="V33" s="7"/>
-      <c r="W33" s="7"/>
-      <c r="X33" s="7">
+      <c r="F33" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="H33" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" s="39"/>
+      <c r="J33" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K33" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L33" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="M33" s="27"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="27"/>
+      <c r="P33" s="27"/>
+      <c r="Q33" s="27"/>
+      <c r="R33" s="27"/>
+      <c r="S33" s="27"/>
+      <c r="T33" s="27"/>
+      <c r="U33" s="27"/>
+      <c r="V33" s="27"/>
+      <c r="W33" s="27"/>
+      <c r="X33" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="Y33" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z33" s="7">
+      <c r="Y33" s="27">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Z33" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6938,10 +7177,16 @@
       <c r="H34" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>163</v>
+      </c>
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
       <c r="O34" s="16"/>
@@ -6955,7 +7200,7 @@
       <c r="W34" s="16"/>
       <c r="X34" s="16">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y34" s="16">
         <f t="shared" si="1"/>
@@ -6988,9 +7233,13 @@
       <c r="H35" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
       <c r="N35" s="7"/>
@@ -7005,7 +7254,7 @@
       <c r="W35" s="7"/>
       <c r="X35" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y35" s="7">
         <f t="shared" si="1"/>
@@ -7038,9 +7287,13 @@
       <c r="H36" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="L36" s="16"/>
       <c r="M36" s="16"/>
       <c r="N36" s="16"/>
@@ -7055,11 +7308,11 @@
       <c r="W36" s="16"/>
       <c r="X36" s="16">
         <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="Y36" s="16">
+        <f t="shared" si="1"/>
         <v>2</v>
-      </c>
-      <c r="Y36" s="16">
-        <f t="shared" si="1"/>
-        <v>1</v>
       </c>
       <c r="Z36" s="7">
         <f t="shared" si="2"/>
@@ -7088,9 +7341,13 @@
       <c r="H37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
       <c r="N37" s="7"/>
@@ -7105,7 +7362,7 @@
       <c r="W37" s="7"/>
       <c r="X37" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y37" s="7">
         <f t="shared" si="1"/>
@@ -7138,10 +7395,16 @@
       <c r="H38" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>164</v>
+      </c>
       <c r="M38" s="16"/>
       <c r="N38" s="16"/>
       <c r="O38" s="16"/>
@@ -7159,7 +7422,7 @@
       </c>
       <c r="Y38" s="16">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z38" s="16">
         <f t="shared" si="2"/>
@@ -7188,10 +7451,16 @@
       <c r="H39" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>164</v>
+      </c>
       <c r="M39" s="16"/>
       <c r="N39" s="16"/>
       <c r="O39" s="16"/>
@@ -7209,7 +7478,7 @@
       </c>
       <c r="Y39" s="16">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z39" s="16">
         <f t="shared" si="2"/>
@@ -7229,19 +7498,25 @@
       <c r="E40" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
+      <c r="F40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I40" s="39"/>
+      <c r="J40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>164</v>
+      </c>
       <c r="M40" s="7"/>
       <c r="N40" s="7"/>
       <c r="O40" s="7"/>
@@ -7259,7 +7534,7 @@
       </c>
       <c r="Y40" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z40" s="7">
         <f t="shared" si="2"/>
@@ -7288,10 +7563,16 @@
       <c r="H41" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>164</v>
+      </c>
       <c r="M41" s="7"/>
       <c r="N41" s="7"/>
       <c r="O41" s="7"/>
@@ -7305,11 +7586,11 @@
       <c r="W41" s="7"/>
       <c r="X41" s="7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y41" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z41" s="7">
         <f t="shared" si="2"/>
@@ -7338,10 +7619,16 @@
       <c r="H42" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>163</v>
+      </c>
       <c r="M42" s="16"/>
       <c r="N42" s="16"/>
       <c r="O42" s="16"/>
@@ -7355,7 +7642,7 @@
       <c r="W42" s="16"/>
       <c r="X42" s="16">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y42" s="16">
         <f t="shared" si="1"/>
@@ -7363,7 +7650,7 @@
       </c>
       <c r="Z42" s="16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
@@ -7388,10 +7675,16 @@
       <c r="H43" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
+      <c r="I43" s="39"/>
+      <c r="J43" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M43" s="7"/>
       <c r="N43" s="7"/>
       <c r="O43" s="7"/>
@@ -7405,7 +7698,7 @@
       <c r="W43" s="7"/>
       <c r="X43" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y43" s="7">
         <f t="shared" si="1"/>
@@ -7438,10 +7731,16 @@
       <c r="H44" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
+      <c r="I44" s="39"/>
+      <c r="J44" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>164</v>
+      </c>
       <c r="M44" s="7"/>
       <c r="N44" s="7"/>
       <c r="O44" s="7"/>
@@ -7459,7 +7758,7 @@
       </c>
       <c r="Y44" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z44" s="7">
         <f t="shared" si="2"/>
@@ -7488,10 +7787,16 @@
       <c r="H45" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
+      <c r="I45" s="39"/>
+      <c r="J45" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M45" s="7"/>
       <c r="N45" s="7"/>
       <c r="O45" s="7"/>
@@ -7505,7 +7810,7 @@
       <c r="W45" s="7"/>
       <c r="X45" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y45" s="7">
         <f t="shared" si="1"/>
@@ -7538,10 +7843,16 @@
       <c r="H46" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
+      <c r="I46" s="39"/>
+      <c r="J46" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
       <c r="O46" s="7"/>
@@ -7555,7 +7866,7 @@
       <c r="W46" s="7"/>
       <c r="X46" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y46" s="7">
         <f t="shared" si="1"/>
@@ -7588,10 +7899,16 @@
       <c r="H47" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
+      <c r="I47" s="39"/>
+      <c r="J47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
       <c r="O47" s="7"/>
@@ -7605,7 +7922,7 @@
       <c r="W47" s="7"/>
       <c r="X47" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y47" s="7">
         <f t="shared" si="1"/>
@@ -7638,10 +7955,16 @@
       <c r="H48" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
+      <c r="I48" s="39"/>
+      <c r="J48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L48" s="7" t="s">
+        <v>164</v>
+      </c>
       <c r="M48" s="7"/>
       <c r="N48" s="7"/>
       <c r="O48" s="7"/>
@@ -7659,59 +7982,65 @@
       </c>
       <c r="Y48" s="7">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z48" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="14">
+    <row r="49" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B49" s="26">
         <v>44</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E49" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="F49" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
-      <c r="O49" s="7"/>
-      <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="7"/>
-      <c r="S49" s="7"/>
-      <c r="T49" s="7"/>
-      <c r="U49" s="7"/>
-      <c r="V49" s="7"/>
-      <c r="W49" s="7"/>
-      <c r="X49" s="7">
+      <c r="F49" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G49" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H49" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I49" s="39"/>
+      <c r="J49" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K49" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L49" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="M49" s="27"/>
+      <c r="N49" s="27"/>
+      <c r="O49" s="27"/>
+      <c r="P49" s="27"/>
+      <c r="Q49" s="27"/>
+      <c r="R49" s="27"/>
+      <c r="S49" s="27"/>
+      <c r="T49" s="27"/>
+      <c r="U49" s="27"/>
+      <c r="V49" s="27"/>
+      <c r="W49" s="27"/>
+      <c r="X49" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y49" s="7">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="Z49" s="7">
+      <c r="Y49" s="27">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Z49" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7738,10 +8067,16 @@
       <c r="H50" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
+      <c r="I50" s="39"/>
+      <c r="J50" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>164</v>
+      </c>
       <c r="M50" s="7"/>
       <c r="N50" s="7"/>
       <c r="O50" s="7"/>
@@ -7759,7 +8094,7 @@
       </c>
       <c r="Y50" s="7">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z50" s="7">
         <f t="shared" si="2"/>
@@ -7788,10 +8123,16 @@
       <c r="H51" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
+      <c r="I51" s="39"/>
+      <c r="J51" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>164</v>
+      </c>
       <c r="M51" s="7"/>
       <c r="N51" s="7"/>
       <c r="O51" s="7"/>
@@ -7809,7 +8150,7 @@
       </c>
       <c r="Y51" s="7">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Z51" s="7">
         <f t="shared" si="2"/>
@@ -7838,10 +8179,16 @@
       <c r="H52" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
+      <c r="I52" s="40"/>
+      <c r="J52" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="M52" s="7"/>
       <c r="N52" s="7"/>
       <c r="O52" s="7"/>
@@ -7855,7 +8202,7 @@
       <c r="W52" s="7"/>
       <c r="X52" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y52" s="7">
         <f t="shared" si="1"/>
@@ -7867,14 +8214,14 @@
       </c>
     </row>
     <row r="53" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="C53" s="32"/>
+      <c r="C53" s="36"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="8">
-        <f t="shared" ref="F53:S53" si="3">COUNTIF(F6:F52,"P")</f>
+        <f t="shared" ref="F53:W53" si="3">COUNTIF(F6:F52,"P")</f>
         <v>31</v>
       </c>
       <c r="G53" s="8">
@@ -7883,7 +8230,7 @@
       </c>
       <c r="H53" s="8">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I53" s="8">
         <f t="shared" si="3"/>
@@ -7891,15 +8238,15 @@
       </c>
       <c r="J53" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K53" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L53" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M53" s="8">
         <f t="shared" si="3"/>
@@ -7929,14 +8276,20 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T53" s="8"/>
-      <c r="U53" s="8"/>
+      <c r="T53" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="V53" s="8">
-        <f>COUNTIF(V6:V52,"P")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="W53" s="8">
-        <f>COUNTIF(W6:W52,"P")</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="X53" s="7"/>
@@ -7944,14 +8297,14 @@
       <c r="Z53" s="7"/>
     </row>
     <row r="54" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B54" s="33" t="s">
+      <c r="B54" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="C54" s="33"/>
+      <c r="C54" s="37"/>
       <c r="D54" s="9"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7">
-        <f t="shared" ref="F54:S54" si="4">COUNTIF(F6:F52,"A")</f>
+        <f t="shared" ref="F54:V54" si="4">COUNTIF(F6:F52,"A")</f>
         <v>15</v>
       </c>
       <c r="G54" s="7">
@@ -7960,7 +8313,7 @@
       </c>
       <c r="H54" s="7">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I54" s="7">
         <f t="shared" si="4"/>
@@ -7968,15 +8321,15 @@
       </c>
       <c r="J54" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K54" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L54" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M54" s="7">
         <f t="shared" si="4"/>
@@ -8006,10 +8359,16 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T54" s="7"/>
-      <c r="U54" s="7"/>
+      <c r="T54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="V54" s="7">
-        <f>COUNTIF(V6:V52,"A")</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="W54" s="7">
@@ -8021,14 +8380,14 @@
       <c r="Z54" s="7"/>
     </row>
     <row r="55" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B55" s="26" t="s">
+      <c r="B55" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C55" s="26"/>
+      <c r="C55" s="30"/>
       <c r="D55" s="9"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7">
-        <f t="shared" ref="F55:S55" si="5">COUNTIF(F6:F52,"L")</f>
+        <f t="shared" ref="F55:V55" si="5">COUNTIF(F6:F52,"L")</f>
         <v>1</v>
       </c>
       <c r="G55" s="7">
@@ -8037,7 +8396,7 @@
       </c>
       <c r="H55" s="7">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55" s="7">
         <f t="shared" si="5"/>
@@ -8045,7 +8404,7 @@
       </c>
       <c r="J55" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" s="7">
         <f t="shared" si="5"/>
@@ -8083,10 +8442,16 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T55" s="7"/>
-      <c r="U55" s="7"/>
+      <c r="T55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U55" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="V55" s="7">
-        <f>COUNTIF(V6:V52,"L")</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W55" s="7">
@@ -8098,12 +8463,13 @@
       <c r="Z55" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B55:C55"/>
     <mergeCell ref="D2:E3"/>
     <mergeCell ref="F2:W3"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="B54:C54"/>
+    <mergeCell ref="I6:I52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8127,30 +8493,30 @@
       <c r="D2" s="25">
         <v>45941</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="27" t="s">
+      <c r="F2" s="34"/>
+      <c r="G2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="28"/>
-      <c r="X2" s="28"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
@@ -8162,26 +8528,26 @@
       <c r="D3" s="22">
         <v>2025</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
-      <c r="X3" s="28"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="32"/>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
@@ -8535,10 +8901,10 @@
       </c>
     </row>
     <row r="11" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="32"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="8" t="e">
@@ -8612,10 +8978,10 @@
       <c r="AA11" s="7"/>
     </row>
     <row r="12" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="33"/>
+      <c r="D12" s="37"/>
       <c r="E12" s="9"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7" t="e">
@@ -8689,10 +9055,10 @@
       <c r="AA12" s="7"/>
     </row>
     <row r="13" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="26"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="9"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7" t="e">

--- a/BOYS PRESENT.xlsx
+++ b/BOYS PRESENT.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="165">
   <si>
     <t>S.NO</t>
   </si>
@@ -515,7 +515,7 @@
     <t>p</t>
   </si>
   <si>
-    <t>a</t>
+    <t>P.</t>
   </si>
 </sst>
 </file>
@@ -1099,7 +1099,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5411,9 +5411,7 @@
     <col min="3" max="3" width="27.7109375" style="24" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.85546875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="13" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="22" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="22" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="2.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5620,10 +5618,18 @@
         <v>163</v>
       </c>
       <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
+      <c r="N6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
@@ -5632,11 +5638,11 @@
       <c r="W6" s="7"/>
       <c r="X6" s="7">
         <f t="shared" ref="X6:X52" si="0">COUNTIF(F6:W6,"P")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y6" s="7">
         <f t="shared" ref="Y6:Y52" si="1">COUNTIF(F6:W6,"A")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z6" s="7">
         <f t="shared" ref="Z6:Z52" si="2">COUNTIF(F6:P6,"L")</f>
@@ -5673,13 +5679,21 @@
         <v>163</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
+      <c r="N7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
@@ -5692,65 +5706,73 @@
       </c>
       <c r="Y7" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Z7" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="14">
+    <row r="8" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="26">
         <v>3</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H8" s="7" t="s">
+      <c r="F8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="27" t="s">
         <v>77</v>
       </c>
       <c r="I8" s="39"/>
-      <c r="J8" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7">
+      <c r="J8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="27"/>
+      <c r="V8" s="27"/>
+      <c r="W8" s="27"/>
+      <c r="X8" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y8" s="7">
+      <c r="Y8" s="27">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="Z8" s="7">
+        <v>10</v>
+      </c>
+      <c r="Z8" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -5785,13 +5807,21 @@
         <v>76</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
+      <c r="N9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -5800,7 +5830,7 @@
       <c r="W9" s="7"/>
       <c r="X9" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y9" s="7">
         <f t="shared" si="1"/>
@@ -5841,13 +5871,21 @@
         <v>76</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
+      <c r="N10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
@@ -5856,7 +5894,7 @@
       <c r="W10" s="7"/>
       <c r="X10" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y10" s="7">
         <f t="shared" si="1"/>
@@ -5897,13 +5935,21 @@
         <v>76</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
+      <c r="N11" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -5912,11 +5958,11 @@
       <c r="W11" s="7"/>
       <c r="X11" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y11" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z11" s="7">
         <f t="shared" si="2"/>
@@ -5953,13 +5999,21 @@
         <v>76</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
+      <c r="N12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
@@ -5968,7 +6022,7 @@
       <c r="W12" s="7"/>
       <c r="X12" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y12" s="7">
         <f t="shared" si="1"/>
@@ -6009,13 +6063,21 @@
         <v>76</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
+      <c r="N13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
@@ -6024,7 +6086,7 @@
       <c r="W13" s="7"/>
       <c r="X13" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y13" s="7">
         <f t="shared" si="1"/>
@@ -6065,13 +6127,21 @@
         <v>76</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M14" s="7"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
+      <c r="N14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="O14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q14" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
       <c r="T14" s="16"/>
@@ -6084,7 +6154,7 @@
       </c>
       <c r="Y14" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z14" s="16">
         <f t="shared" si="2"/>
@@ -6121,13 +6191,21 @@
         <v>76</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
+      <c r="N15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
@@ -6136,11 +6214,11 @@
       <c r="W15" s="7"/>
       <c r="X15" s="7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y15" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z15" s="7">
         <f t="shared" si="2"/>
@@ -6177,13 +6255,21 @@
         <v>76</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M16" s="7"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
+      <c r="N16" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q16" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="R16" s="16"/>
       <c r="S16" s="16"/>
       <c r="T16" s="16"/>
@@ -6192,11 +6278,11 @@
       <c r="W16" s="16"/>
       <c r="X16" s="16">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y16" s="16">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z16" s="7">
         <f t="shared" si="2"/>
@@ -6233,13 +6319,21 @@
         <v>76</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
+      <c r="N17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
@@ -6248,11 +6342,11 @@
       <c r="W17" s="7"/>
       <c r="X17" s="7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y17" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z17" s="7">
         <f t="shared" si="2"/>
@@ -6289,13 +6383,21 @@
         <v>76</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
+      <c r="N18" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
@@ -6304,69 +6406,77 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y18" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z18" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="14">
+    <row r="19" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="26">
         <v>14</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" s="16" t="s">
+      <c r="F19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" s="27" t="s">
         <v>77</v>
       </c>
       <c r="I19" s="39"/>
-      <c r="J19" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="M19" s="7"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16">
+      <c r="J19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R19" s="27"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="27"/>
+      <c r="W19" s="27"/>
+      <c r="X19" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y19" s="16">
+      <c r="Y19" s="27">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="Z19" s="16">
+        <v>10</v>
+      </c>
+      <c r="Z19" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6401,13 +6511,21 @@
         <v>76</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
+      <c r="N20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
@@ -6416,11 +6534,11 @@
       <c r="W20" s="7"/>
       <c r="X20" s="7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y20" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z20" s="7">
         <f t="shared" si="2"/>
@@ -6457,13 +6575,21 @@
         <v>76</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
+      <c r="N21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
@@ -6472,11 +6598,11 @@
       <c r="W21" s="7"/>
       <c r="X21" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z21" s="7">
         <f t="shared" si="2"/>
@@ -6513,13 +6639,21 @@
         <v>76</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
+      <c r="N22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
@@ -6528,7 +6662,7 @@
       <c r="W22" s="7"/>
       <c r="X22" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y22" s="7">
         <f t="shared" si="1"/>
@@ -6569,13 +6703,21 @@
         <v>77</v>
       </c>
       <c r="L23" s="27" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="M23" s="7"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
+      <c r="N23" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O23" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P23" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q23" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
       <c r="T23" s="27"/>
@@ -6588,7 +6730,7 @@
       </c>
       <c r="Y23" s="27">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Z23" s="27">
         <f t="shared" si="2"/>
@@ -6625,13 +6767,21 @@
         <v>76</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
+      <c r="N24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
@@ -6640,7 +6790,7 @@
       <c r="W24" s="7"/>
       <c r="X24" s="7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y24" s="7">
         <f t="shared" si="1"/>
@@ -6681,13 +6831,21 @@
         <v>76</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
+      <c r="N25" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -6696,7 +6854,7 @@
       <c r="W25" s="7"/>
       <c r="X25" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y25" s="7">
         <f t="shared" si="1"/>
@@ -6734,16 +6892,24 @@
         <v>77</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="M26" s="7"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
+      <c r="N26" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="O26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="P26" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q26" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="R26" s="16"/>
       <c r="S26" s="16"/>
       <c r="T26" s="16"/>
@@ -6752,11 +6918,11 @@
       <c r="W26" s="16"/>
       <c r="X26" s="16">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y26" s="16">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z26" s="16">
         <f t="shared" si="2"/>
@@ -6793,13 +6959,21 @@
         <v>76</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
+      <c r="N27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
@@ -6808,7 +6982,7 @@
       <c r="W27" s="7"/>
       <c r="X27" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y27" s="7">
         <f t="shared" si="1"/>
@@ -6819,58 +6993,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="14">
+    <row r="28" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="26">
         <v>23</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H28" s="7" t="s">
+      <c r="F28" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="27" t="s">
         <v>76</v>
       </c>
       <c r="I28" s="39"/>
-      <c r="J28" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="7"/>
-      <c r="V28" s="7"/>
-      <c r="W28" s="7"/>
-      <c r="X28" s="7">
+      <c r="J28" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="K28" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="L28" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O28" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P28" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q28" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="27"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="27"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="27">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="Y28" s="7">
+      <c r="Y28" s="27">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z28" s="7">
+        <v>4</v>
+      </c>
+      <c r="Z28" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -6905,13 +7087,21 @@
         <v>76</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
+      <c r="N29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q29" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
       <c r="T29" s="7"/>
@@ -6920,125 +7110,141 @@
       <c r="W29" s="7"/>
       <c r="X29" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y29" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="14">
+    <row r="30" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="26">
         <v>25</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H30" s="7" t="s">
+      <c r="F30" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="H30" s="27" t="s">
         <v>76</v>
       </c>
       <c r="I30" s="39"/>
-      <c r="J30" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
-      <c r="R30" s="7"/>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
-      <c r="U30" s="7"/>
-      <c r="V30" s="7"/>
-      <c r="W30" s="7"/>
-      <c r="X30" s="7">
+      <c r="J30" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="K30" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="L30" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O30" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P30" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q30" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R30" s="27"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="27"/>
+      <c r="U30" s="27"/>
+      <c r="V30" s="27"/>
+      <c r="W30" s="27"/>
+      <c r="X30" s="27">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="Y30" s="7">
+      <c r="Y30" s="27">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z30" s="7">
+        <v>4</v>
+      </c>
+      <c r="Z30" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="14">
+    <row r="31" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="26">
         <v>26</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H31" s="7" t="s">
+      <c r="F31" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" s="27" t="s">
         <v>77</v>
       </c>
       <c r="I31" s="39"/>
-      <c r="J31" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="L31" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="7"/>
-      <c r="R31" s="7"/>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="7"/>
-      <c r="V31" s="7"/>
-      <c r="W31" s="7"/>
-      <c r="X31" s="7">
+      <c r="J31" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K31" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L31" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M31" s="27"/>
+      <c r="N31" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O31" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P31" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q31" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R31" s="27"/>
+      <c r="S31" s="27"/>
+      <c r="T31" s="27"/>
+      <c r="U31" s="27"/>
+      <c r="V31" s="27"/>
+      <c r="W31" s="27"/>
+      <c r="X31" s="27">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Y31" s="7">
+      <c r="Y31" s="27">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="Z31" s="7">
+        <v>9</v>
+      </c>
+      <c r="Z31" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7073,13 +7279,21 @@
         <v>76</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="7"/>
+      <c r="N32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O32" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="P32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q32" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R32" s="7"/>
       <c r="S32" s="7"/>
       <c r="T32" s="7"/>
@@ -7088,7 +7302,7 @@
       <c r="W32" s="7"/>
       <c r="X32" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y32" s="7">
         <f t="shared" si="1"/>
@@ -7096,7 +7310,7 @@
       </c>
       <c r="Z32" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -7129,13 +7343,21 @@
         <v>77</v>
       </c>
       <c r="L33" s="27" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="M33" s="27"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="27"/>
-      <c r="P33" s="27"/>
-      <c r="Q33" s="27"/>
+      <c r="N33" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O33" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P33" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q33" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="R33" s="27"/>
       <c r="S33" s="27"/>
       <c r="T33" s="27"/>
@@ -7148,7 +7370,7 @@
       </c>
       <c r="Y33" s="27">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Z33" s="27">
         <f t="shared" si="2"/>
@@ -7185,13 +7407,21 @@
         <v>76</v>
       </c>
       <c r="L34" s="16" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M34" s="16"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="16"/>
-      <c r="Q34" s="16"/>
+      <c r="N34" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="O34" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="P34" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q34" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="R34" s="16"/>
       <c r="S34" s="16"/>
       <c r="T34" s="16"/>
@@ -7200,11 +7430,11 @@
       <c r="W34" s="16"/>
       <c r="X34" s="16">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y34" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z34" s="16">
         <f t="shared" si="2"/>
@@ -7240,12 +7470,22 @@
       <c r="K35" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L35" s="7"/>
+      <c r="L35" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
+      <c r="N35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q35" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R35" s="7"/>
       <c r="S35" s="7"/>
       <c r="T35" s="7"/>
@@ -7254,7 +7494,7 @@
       <c r="W35" s="7"/>
       <c r="X35" s="7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y35" s="7">
         <f t="shared" si="1"/>
@@ -7294,12 +7534,22 @@
       <c r="K36" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="L36" s="16"/>
+      <c r="L36" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16"/>
-      <c r="Q36" s="16"/>
+      <c r="N36" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="O36" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="P36" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q36" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="R36" s="16"/>
       <c r="S36" s="16"/>
       <c r="T36" s="16"/>
@@ -7308,11 +7558,11 @@
       <c r="W36" s="16"/>
       <c r="X36" s="16">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y36" s="16">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z36" s="7">
         <f t="shared" si="2"/>
@@ -7348,12 +7598,22 @@
       <c r="K37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="L37" s="7"/>
+      <c r="L37" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="M37" s="7"/>
-      <c r="N37" s="7"/>
-      <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
+      <c r="N37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R37" s="7"/>
       <c r="S37" s="7"/>
       <c r="T37" s="7"/>
@@ -7362,7 +7622,7 @@
       <c r="W37" s="7"/>
       <c r="X37" s="7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y37" s="7">
         <f t="shared" si="1"/>
@@ -7373,170 +7633,194 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="14">
+    <row r="38" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="26">
         <v>33</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="F38" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="G38" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="H38" s="16" t="s">
+      <c r="F38" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" s="27" t="s">
         <v>77</v>
       </c>
       <c r="I38" s="39"/>
-      <c r="J38" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K38" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="L38" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="16"/>
-      <c r="R38" s="16"/>
-      <c r="S38" s="16"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="16"/>
-      <c r="V38" s="16"/>
-      <c r="W38" s="16"/>
-      <c r="X38" s="16">
+      <c r="J38" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K38" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L38" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M38" s="27"/>
+      <c r="N38" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O38" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P38" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q38" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R38" s="27"/>
+      <c r="S38" s="27"/>
+      <c r="T38" s="27"/>
+      <c r="U38" s="27"/>
+      <c r="V38" s="27"/>
+      <c r="W38" s="27"/>
+      <c r="X38" s="27">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Y38" s="16">
+      <c r="Y38" s="27">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="Z38" s="16">
+        <v>9</v>
+      </c>
+      <c r="Z38" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="17">
+    <row r="39" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="26">
         <v>34</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="G39" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="H39" s="16" t="s">
+      <c r="F39" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H39" s="27" t="s">
         <v>77</v>
       </c>
       <c r="I39" s="39"/>
-      <c r="J39" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K39" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="L39" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="16"/>
-      <c r="S39" s="16"/>
-      <c r="T39" s="16"/>
-      <c r="U39" s="16"/>
-      <c r="V39" s="16"/>
-      <c r="W39" s="16"/>
-      <c r="X39" s="16">
+      <c r="J39" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K39" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L39" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M39" s="27"/>
+      <c r="N39" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O39" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P39" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q39" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R39" s="27"/>
+      <c r="S39" s="27"/>
+      <c r="T39" s="27"/>
+      <c r="U39" s="27"/>
+      <c r="V39" s="27"/>
+      <c r="W39" s="27"/>
+      <c r="X39" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y39" s="16">
+      <c r="Y39" s="27">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="Z39" s="16">
+        <v>10</v>
+      </c>
+      <c r="Z39" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="14">
+    <row r="40" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B40" s="26">
         <v>35</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H40" s="7" t="s">
+      <c r="F40" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H40" s="27" t="s">
         <v>76</v>
       </c>
       <c r="I40" s="39"/>
-      <c r="J40" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="L40" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
-      <c r="O40" s="7"/>
-      <c r="P40" s="7"/>
-      <c r="Q40" s="7"/>
-      <c r="R40" s="7"/>
-      <c r="S40" s="7"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="7"/>
-      <c r="V40" s="7"/>
-      <c r="W40" s="7"/>
-      <c r="X40" s="7">
+      <c r="J40" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K40" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L40" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O40" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P40" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q40" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R40" s="27"/>
+      <c r="S40" s="27"/>
+      <c r="T40" s="27"/>
+      <c r="U40" s="27"/>
+      <c r="V40" s="27"/>
+      <c r="W40" s="27"/>
+      <c r="X40" s="27">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Y40" s="7">
+      <c r="Y40" s="27">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="Z40" s="7">
+        <v>9</v>
+      </c>
+      <c r="Z40" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7571,13 +7855,21 @@
         <v>76</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="M41" s="7"/>
-      <c r="N41" s="7"/>
-      <c r="O41" s="7"/>
-      <c r="P41" s="7"/>
-      <c r="Q41" s="7"/>
+      <c r="N41" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q41" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R41" s="7"/>
       <c r="S41" s="7"/>
       <c r="T41" s="7"/>
@@ -7586,11 +7878,11 @@
       <c r="W41" s="7"/>
       <c r="X41" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y41" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z41" s="7">
         <f t="shared" si="2"/>
@@ -7627,13 +7919,21 @@
         <v>76</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M42" s="16"/>
-      <c r="N42" s="16"/>
-      <c r="O42" s="16"/>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="16"/>
+      <c r="N42" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="O42" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="P42" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q42" s="16" t="s">
+        <v>80</v>
+      </c>
       <c r="R42" s="16"/>
       <c r="S42" s="16"/>
       <c r="T42" s="16"/>
@@ -7650,7 +7950,7 @@
       </c>
       <c r="Z42" s="16">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
@@ -7683,13 +7983,21 @@
         <v>76</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M43" s="7"/>
-      <c r="N43" s="7"/>
-      <c r="O43" s="7"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="7"/>
+      <c r="N43" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O43" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P43" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q43" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R43" s="7"/>
       <c r="S43" s="7"/>
       <c r="T43" s="7"/>
@@ -7698,11 +8006,11 @@
       <c r="W43" s="7"/>
       <c r="X43" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y43" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z43" s="7">
         <f t="shared" si="2"/>
@@ -7739,13 +8047,21 @@
         <v>77</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="M44" s="7"/>
-      <c r="N44" s="7"/>
-      <c r="O44" s="7"/>
-      <c r="P44" s="7"/>
-      <c r="Q44" s="7"/>
+      <c r="N44" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="O44" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="P44" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q44" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="R44" s="7"/>
       <c r="S44" s="7"/>
       <c r="T44" s="7"/>
@@ -7754,15 +8070,15 @@
       <c r="W44" s="7"/>
       <c r="X44" s="7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y44" s="7">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z44" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
@@ -7795,13 +8111,21 @@
         <v>76</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M45" s="7"/>
-      <c r="N45" s="7"/>
-      <c r="O45" s="7"/>
-      <c r="P45" s="7"/>
-      <c r="Q45" s="7"/>
+      <c r="N45" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O45" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P45" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q45" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R45" s="7"/>
       <c r="S45" s="7"/>
       <c r="T45" s="7"/>
@@ -7810,7 +8134,7 @@
       <c r="W45" s="7"/>
       <c r="X45" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y45" s="7">
         <f t="shared" si="1"/>
@@ -7851,13 +8175,21 @@
         <v>76</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
-      <c r="O46" s="7"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="7"/>
+      <c r="N46" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O46" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P46" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q46" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R46" s="7"/>
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
@@ -7866,7 +8198,7 @@
       <c r="W46" s="7"/>
       <c r="X46" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y46" s="7">
         <f t="shared" si="1"/>
@@ -7907,13 +8239,21 @@
         <v>76</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M47" s="7"/>
-      <c r="N47" s="7"/>
-      <c r="O47" s="7"/>
-      <c r="P47" s="7"/>
-      <c r="Q47" s="7"/>
+      <c r="N47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q47" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R47" s="7"/>
       <c r="S47" s="7"/>
       <c r="T47" s="7"/>
@@ -7922,7 +8262,7 @@
       <c r="W47" s="7"/>
       <c r="X47" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y47" s="7">
         <f t="shared" si="1"/>
@@ -7963,13 +8303,21 @@
         <v>77</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
-      <c r="O48" s="7"/>
-      <c r="P48" s="7"/>
-      <c r="Q48" s="7"/>
+      <c r="N48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q48" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="R48" s="7"/>
       <c r="S48" s="7"/>
       <c r="T48" s="7"/>
@@ -7982,7 +8330,7 @@
       </c>
       <c r="Y48" s="7">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z48" s="7">
         <f t="shared" si="2"/>
@@ -8019,13 +8367,21 @@
         <v>77</v>
       </c>
       <c r="L49" s="27" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="27"/>
-      <c r="P49" s="27"/>
-      <c r="Q49" s="27"/>
+      <c r="N49" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O49" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P49" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q49" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="R49" s="27"/>
       <c r="S49" s="27"/>
       <c r="T49" s="27"/>
@@ -8038,121 +8394,137 @@
       </c>
       <c r="Y49" s="27">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z49" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="14">
+    <row r="50" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B50" s="26">
         <v>45</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="F50" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H50" s="7" t="s">
+      <c r="F50" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G50" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H50" s="27" t="s">
         <v>77</v>
       </c>
       <c r="I50" s="39"/>
-      <c r="J50" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K50" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="L50" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="M50" s="7"/>
-      <c r="N50" s="7"/>
-      <c r="O50" s="7"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="7"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="7"/>
-      <c r="T50" s="7"/>
-      <c r="U50" s="7"/>
-      <c r="V50" s="7"/>
-      <c r="W50" s="7"/>
-      <c r="X50" s="7">
+      <c r="J50" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K50" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L50" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M50" s="27"/>
+      <c r="N50" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O50" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P50" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q50" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R50" s="27"/>
+      <c r="S50" s="27"/>
+      <c r="T50" s="27"/>
+      <c r="U50" s="27"/>
+      <c r="V50" s="27"/>
+      <c r="W50" s="27"/>
+      <c r="X50" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y50" s="7">
+      <c r="Y50" s="27">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="Z50" s="7">
+        <v>10</v>
+      </c>
+      <c r="Z50" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="14">
+    <row r="51" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B51" s="26">
         <v>46</v>
       </c>
-      <c r="C51" s="16" t="s">
+      <c r="C51" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="F51" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H51" s="7" t="s">
+      <c r="F51" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G51" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H51" s="27" t="s">
         <v>77</v>
       </c>
       <c r="I51" s="39"/>
-      <c r="J51" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="L51" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="M51" s="7"/>
-      <c r="N51" s="7"/>
-      <c r="O51" s="7"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="7"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="7"/>
-      <c r="T51" s="7"/>
-      <c r="U51" s="7"/>
-      <c r="V51" s="7"/>
-      <c r="W51" s="7"/>
-      <c r="X51" s="7">
+      <c r="J51" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K51" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L51" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M51" s="27"/>
+      <c r="N51" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O51" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P51" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q51" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R51" s="27"/>
+      <c r="S51" s="27"/>
+      <c r="T51" s="27"/>
+      <c r="U51" s="27"/>
+      <c r="V51" s="27"/>
+      <c r="W51" s="27"/>
+      <c r="X51" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y51" s="7">
+      <c r="Y51" s="27">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="Z51" s="7">
+        <v>10</v>
+      </c>
+      <c r="Z51" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8187,13 +8559,21 @@
         <v>76</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-      <c r="O52" s="7"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="7"/>
+      <c r="N52" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O52" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P52" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q52" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
@@ -8202,11 +8582,11 @@
       <c r="W52" s="7"/>
       <c r="X52" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y52" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z52" s="7">
         <f t="shared" si="2"/>
@@ -8242,11 +8622,11 @@
       </c>
       <c r="K53" s="8">
         <f t="shared" si="3"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L53" s="8">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M53" s="8">
         <f t="shared" si="3"/>
@@ -8254,19 +8634,19 @@
       </c>
       <c r="N53" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O53" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>COUNTIF(O6:O52,"P")</f>
+        <v>16</v>
       </c>
       <c r="P53" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q53" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="R53" s="8">
         <f t="shared" si="3"/>
@@ -8325,7 +8705,7 @@
       </c>
       <c r="K54" s="7">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L54" s="7">
         <f t="shared" si="4"/>
@@ -8337,19 +8717,19 @@
       </c>
       <c r="N54" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O54" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="P54" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q54" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R54" s="7">
         <f t="shared" si="4"/>
@@ -8420,19 +8800,19 @@
       </c>
       <c r="N55" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O55" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P55" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q55" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" s="7">
         <f t="shared" si="5"/>

--- a/BOYS PRESENT.xlsx
+++ b/BOYS PRESENT.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="165">
   <si>
     <t>S.NO</t>
   </si>
@@ -1099,7 +1099,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5630,8 +5630,12 @@
       <c r="Q6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
+      <c r="R6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="T6" s="7"/>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -5642,7 +5646,7 @@
       </c>
       <c r="Y6" s="7">
         <f t="shared" ref="Y6:Y52" si="1">COUNTIF(F6:W6,"A")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z6" s="7">
         <f t="shared" ref="Z6:Z52" si="2">COUNTIF(F6:P6,"L")</f>
@@ -5694,8 +5698,12 @@
       <c r="Q7" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
+      <c r="R7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S7" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="T7" s="7"/>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
@@ -5706,7 +5714,7 @@
       </c>
       <c r="Y7" s="7">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z7" s="7">
         <f t="shared" si="2"/>
@@ -5758,8 +5766,12 @@
       <c r="Q8" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R8" s="27"/>
-      <c r="S8" s="27"/>
+      <c r="R8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S8" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="T8" s="27"/>
       <c r="U8" s="27"/>
       <c r="V8" s="27"/>
@@ -5770,7 +5782,7 @@
       </c>
       <c r="Y8" s="27">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z8" s="27">
         <f t="shared" si="2"/>
@@ -5822,15 +5834,19 @@
       <c r="Q9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
+      <c r="R9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S9" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
       <c r="W9" s="7"/>
       <c r="X9" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y9" s="7">
         <f t="shared" si="1"/>
@@ -5886,8 +5902,12 @@
       <c r="Q10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
+      <c r="R10" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="T10" s="7"/>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
@@ -5898,7 +5918,7 @@
       </c>
       <c r="Y10" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z10" s="7">
         <f t="shared" si="2"/>
@@ -5950,8 +5970,12 @@
       <c r="Q11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
+      <c r="R11" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
@@ -5962,7 +5986,7 @@
       </c>
       <c r="Y11" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z11" s="7">
         <f t="shared" si="2"/>
@@ -6014,15 +6038,19 @@
       <c r="Q12" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
+      <c r="R12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S12" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T12" s="7"/>
       <c r="U12" s="7"/>
       <c r="V12" s="7"/>
       <c r="W12" s="7"/>
       <c r="X12" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y12" s="7">
         <f t="shared" si="1"/>
@@ -6078,15 +6106,19 @@
       <c r="Q13" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
+      <c r="R13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S13" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y13" s="7">
         <f t="shared" si="1"/>
@@ -6142,8 +6174,12 @@
       <c r="Q14" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
+      <c r="R14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="S14" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="T14" s="16"/>
       <c r="U14" s="16"/>
       <c r="V14" s="16"/>
@@ -6154,7 +6190,7 @@
       </c>
       <c r="Y14" s="16">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z14" s="16">
         <f t="shared" si="2"/>
@@ -6206,15 +6242,19 @@
       <c r="Q15" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
+      <c r="R15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y15" s="7">
         <f t="shared" si="1"/>
@@ -6270,15 +6310,19 @@
       <c r="Q16" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
+      <c r="R16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="S16" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="T16" s="16"/>
       <c r="U16" s="16"/>
       <c r="V16" s="16"/>
       <c r="W16" s="16"/>
       <c r="X16" s="16">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y16" s="16">
         <f t="shared" si="1"/>
@@ -6334,15 +6378,19 @@
       <c r="Q17" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
+      <c r="R17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y17" s="7">
         <f t="shared" si="1"/>
@@ -6398,8 +6446,12 @@
       <c r="Q18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
+      <c r="R18" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S18" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
       <c r="V18" s="7"/>
@@ -6410,7 +6462,7 @@
       </c>
       <c r="Y18" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z18" s="7">
         <f t="shared" si="2"/>
@@ -6462,8 +6514,12 @@
       <c r="Q19" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
+      <c r="R19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S19" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="T19" s="27"/>
       <c r="U19" s="27"/>
       <c r="V19" s="27"/>
@@ -6474,7 +6530,7 @@
       </c>
       <c r="Y19" s="27">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z19" s="27">
         <f t="shared" si="2"/>
@@ -6526,15 +6582,19 @@
       <c r="Q20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
+      <c r="R20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S20" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T20" s="7"/>
       <c r="U20" s="7"/>
       <c r="V20" s="7"/>
       <c r="W20" s="7"/>
       <c r="X20" s="7">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y20" s="7">
         <f t="shared" si="1"/>
@@ -6590,15 +6650,19 @@
       <c r="Q21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
+      <c r="R21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
       <c r="X21" s="7">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y21" s="7">
         <f t="shared" si="1"/>
@@ -6654,15 +6718,19 @@
       <c r="Q22" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
+      <c r="R22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S22" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
       <c r="V22" s="7"/>
       <c r="W22" s="7"/>
       <c r="X22" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y22" s="7">
         <f t="shared" si="1"/>
@@ -6718,8 +6786,12 @@
       <c r="Q23" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
+      <c r="R23" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S23" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="T23" s="27"/>
       <c r="U23" s="27"/>
       <c r="V23" s="27"/>
@@ -6730,7 +6802,7 @@
       </c>
       <c r="Y23" s="27">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z23" s="27">
         <f t="shared" si="2"/>
@@ -6782,15 +6854,19 @@
       <c r="Q24" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R24" s="7"/>
-      <c r="S24" s="7"/>
+      <c r="R24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S24" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T24" s="7"/>
       <c r="U24" s="7"/>
       <c r="V24" s="7"/>
       <c r="W24" s="7"/>
       <c r="X24" s="7">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y24" s="7">
         <f t="shared" si="1"/>
@@ -6846,15 +6922,19 @@
       <c r="Q25" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R25" s="7"/>
-      <c r="S25" s="7"/>
+      <c r="R25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S25" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
       <c r="W25" s="7"/>
       <c r="X25" s="7">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y25" s="7">
         <f t="shared" si="1"/>
@@ -6910,15 +6990,19 @@
       <c r="Q26" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="R26" s="16"/>
-      <c r="S26" s="16"/>
+      <c r="R26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="S26" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="T26" s="16"/>
       <c r="U26" s="16"/>
       <c r="V26" s="16"/>
       <c r="W26" s="16"/>
       <c r="X26" s="16">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y26" s="16">
         <f t="shared" si="1"/>
@@ -6974,15 +7058,19 @@
       <c r="Q27" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R27" s="7"/>
-      <c r="S27" s="7"/>
+      <c r="R27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y27" s="7">
         <f t="shared" si="1"/>
@@ -7038,8 +7126,12 @@
       <c r="Q28" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
+      <c r="R28" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S28" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="T28" s="27"/>
       <c r="U28" s="27"/>
       <c r="V28" s="27"/>
@@ -7050,7 +7142,7 @@
       </c>
       <c r="Y28" s="27">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z28" s="27">
         <f t="shared" si="2"/>
@@ -7102,15 +7194,19 @@
       <c r="Q29" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R29" s="7"/>
-      <c r="S29" s="7"/>
+      <c r="R29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
       <c r="W29" s="7"/>
       <c r="X29" s="7">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y29" s="7">
         <f t="shared" si="1"/>
@@ -7166,8 +7262,12 @@
       <c r="Q30" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R30" s="27"/>
-      <c r="S30" s="27"/>
+      <c r="R30" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S30" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="T30" s="27"/>
       <c r="U30" s="27"/>
       <c r="V30" s="27"/>
@@ -7178,7 +7278,7 @@
       </c>
       <c r="Y30" s="27">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z30" s="27">
         <f t="shared" si="2"/>
@@ -7230,8 +7330,12 @@
       <c r="Q31" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R31" s="27"/>
-      <c r="S31" s="27"/>
+      <c r="R31" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S31" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="T31" s="27"/>
       <c r="U31" s="27"/>
       <c r="V31" s="27"/>
@@ -7242,7 +7346,7 @@
       </c>
       <c r="Y31" s="27">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z31" s="27">
         <f t="shared" si="2"/>
@@ -7294,15 +7398,19 @@
       <c r="Q32" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R32" s="7"/>
-      <c r="S32" s="7"/>
+      <c r="R32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S32" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T32" s="7"/>
       <c r="U32" s="7"/>
       <c r="V32" s="7"/>
       <c r="W32" s="7"/>
       <c r="X32" s="7">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y32" s="7">
         <f t="shared" si="1"/>
@@ -7358,8 +7466,12 @@
       <c r="Q33" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R33" s="27"/>
-      <c r="S33" s="27"/>
+      <c r="R33" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S33" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="T33" s="27"/>
       <c r="U33" s="27"/>
       <c r="V33" s="27"/>
@@ -7370,7 +7482,7 @@
       </c>
       <c r="Y33" s="27">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z33" s="27">
         <f t="shared" si="2"/>
@@ -7422,15 +7534,19 @@
       <c r="Q34" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="R34" s="16"/>
-      <c r="S34" s="16"/>
+      <c r="R34" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="S34" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="T34" s="16"/>
       <c r="U34" s="16"/>
       <c r="V34" s="16"/>
       <c r="W34" s="16"/>
       <c r="X34" s="16">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y34" s="16">
         <f t="shared" si="1"/>
@@ -7486,15 +7602,19 @@
       <c r="Q35" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R35" s="7"/>
-      <c r="S35" s="7"/>
+      <c r="R35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
       <c r="W35" s="7"/>
       <c r="X35" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y35" s="7">
         <f t="shared" si="1"/>
@@ -7550,8 +7670,12 @@
       <c r="Q36" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="R36" s="16"/>
-      <c r="S36" s="16"/>
+      <c r="R36" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="S36" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="T36" s="16"/>
       <c r="U36" s="16"/>
       <c r="V36" s="16"/>
@@ -7562,7 +7686,7 @@
       </c>
       <c r="Y36" s="16">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z36" s="7">
         <f t="shared" si="2"/>
@@ -7614,15 +7738,19 @@
       <c r="Q37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R37" s="7"/>
-      <c r="S37" s="7"/>
+      <c r="R37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S37" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y37" s="7">
         <f t="shared" si="1"/>
@@ -7678,8 +7806,12 @@
       <c r="Q38" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R38" s="27"/>
-      <c r="S38" s="27"/>
+      <c r="R38" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S38" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="T38" s="27"/>
       <c r="U38" s="27"/>
       <c r="V38" s="27"/>
@@ -7690,7 +7822,7 @@
       </c>
       <c r="Y38" s="27">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z38" s="27">
         <f t="shared" si="2"/>
@@ -7742,8 +7874,12 @@
       <c r="Q39" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R39" s="27"/>
-      <c r="S39" s="27"/>
+      <c r="R39" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S39" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="T39" s="27"/>
       <c r="U39" s="27"/>
       <c r="V39" s="27"/>
@@ -7754,7 +7890,7 @@
       </c>
       <c r="Y39" s="27">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z39" s="27">
         <f t="shared" si="2"/>
@@ -7806,8 +7942,12 @@
       <c r="Q40" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
+      <c r="R40" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S40" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="T40" s="27"/>
       <c r="U40" s="27"/>
       <c r="V40" s="27"/>
@@ -7818,7 +7958,7 @@
       </c>
       <c r="Y40" s="27">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z40" s="27">
         <f t="shared" si="2"/>
@@ -7870,15 +8010,19 @@
       <c r="Q41" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R41" s="7"/>
-      <c r="S41" s="7"/>
+      <c r="R41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S41" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T41" s="7"/>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
       <c r="W41" s="7"/>
       <c r="X41" s="7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y41" s="7">
         <f t="shared" si="1"/>
@@ -7934,8 +8078,12 @@
       <c r="Q42" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="R42" s="16"/>
-      <c r="S42" s="16"/>
+      <c r="R42" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="S42" s="16" t="s">
+        <v>80</v>
+      </c>
       <c r="T42" s="16"/>
       <c r="U42" s="16"/>
       <c r="V42" s="16"/>
@@ -7998,15 +8146,19 @@
       <c r="Q43" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R43" s="7"/>
-      <c r="S43" s="7"/>
+      <c r="R43" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
       <c r="W43" s="7"/>
       <c r="X43" s="7">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y43" s="7">
         <f t="shared" si="1"/>
@@ -8062,15 +8214,19 @@
       <c r="Q44" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="R44" s="7"/>
-      <c r="S44" s="7"/>
+      <c r="R44" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S44" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T44" s="7"/>
       <c r="U44" s="7"/>
       <c r="V44" s="7"/>
       <c r="W44" s="7"/>
       <c r="X44" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y44" s="7">
         <f t="shared" si="1"/>
@@ -8126,15 +8282,19 @@
       <c r="Q45" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R45" s="7"/>
-      <c r="S45" s="7"/>
+      <c r="R45" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S45" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
       <c r="V45" s="7"/>
       <c r="W45" s="7"/>
       <c r="X45" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y45" s="7">
         <f t="shared" si="1"/>
@@ -8190,15 +8350,19 @@
       <c r="Q46" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R46" s="7"/>
-      <c r="S46" s="7"/>
+      <c r="R46" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S46" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
       <c r="V46" s="7"/>
       <c r="W46" s="7"/>
       <c r="X46" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y46" s="7">
         <f t="shared" si="1"/>
@@ -8254,15 +8418,19 @@
       <c r="Q47" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R47" s="7"/>
-      <c r="S47" s="7"/>
+      <c r="R47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S47" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
       <c r="X47" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y47" s="7">
         <f t="shared" si="1"/>
@@ -8318,8 +8486,12 @@
       <c r="Q48" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="R48" s="7"/>
-      <c r="S48" s="7"/>
+      <c r="R48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S48" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="T48" s="7"/>
       <c r="U48" s="7"/>
       <c r="V48" s="7"/>
@@ -8330,7 +8502,7 @@
       </c>
       <c r="Y48" s="7">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z48" s="7">
         <f t="shared" si="2"/>
@@ -8382,8 +8554,12 @@
       <c r="Q49" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R49" s="27"/>
-      <c r="S49" s="27"/>
+      <c r="R49" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S49" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="T49" s="27"/>
       <c r="U49" s="27"/>
       <c r="V49" s="27"/>
@@ -8394,7 +8570,7 @@
       </c>
       <c r="Y49" s="27">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z49" s="27">
         <f t="shared" si="2"/>
@@ -8446,8 +8622,12 @@
       <c r="Q50" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R50" s="27"/>
-      <c r="S50" s="27"/>
+      <c r="R50" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S50" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="T50" s="27"/>
       <c r="U50" s="27"/>
       <c r="V50" s="27"/>
@@ -8458,7 +8638,7 @@
       </c>
       <c r="Y50" s="27">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z50" s="27">
         <f t="shared" si="2"/>
@@ -8510,8 +8690,12 @@
       <c r="Q51" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="R51" s="27"/>
-      <c r="S51" s="27"/>
+      <c r="R51" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S51" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="T51" s="27"/>
       <c r="U51" s="27"/>
       <c r="V51" s="27"/>
@@ -8522,7 +8706,7 @@
       </c>
       <c r="Y51" s="27">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z51" s="27">
         <f t="shared" si="2"/>
@@ -8563,7 +8747,7 @@
       </c>
       <c r="M52" s="7"/>
       <c r="N52" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O52" s="7" t="s">
         <v>77</v>
@@ -8574,19 +8758,23 @@
       <c r="Q52" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="R52" s="7"/>
-      <c r="S52" s="7"/>
+      <c r="R52" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S52" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
       <c r="W52" s="7"/>
       <c r="X52" s="7">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Y52" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z52" s="7">
         <f t="shared" si="2"/>
@@ -8634,7 +8822,7 @@
       </c>
       <c r="N53" s="8">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O53" s="8">
         <f>COUNTIF(O6:O52,"P")</f>
@@ -8650,11 +8838,11 @@
       </c>
       <c r="R53" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S53" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T53" s="8">
         <f t="shared" si="3"/>
@@ -8717,7 +8905,7 @@
       </c>
       <c r="N54" s="7">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O54" s="7">
         <f t="shared" si="4"/>
@@ -8733,11 +8921,11 @@
       </c>
       <c r="R54" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S54" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T54" s="7">
         <f t="shared" si="4"/>
@@ -8816,11 +9004,11 @@
       </c>
       <c r="R55" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" s="7">
         <f t="shared" si="5"/>

--- a/BOYS PRESENT.xlsx
+++ b/BOYS PRESENT.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1854" uniqueCount="166">
   <si>
     <t>S.NO</t>
   </si>
@@ -516,6 +516,9 @@
   </si>
   <si>
     <t>P.</t>
+  </si>
+  <si>
+    <t>.</t>
   </si>
 </sst>
 </file>
@@ -5637,8 +5640,12 @@
         <v>77</v>
       </c>
       <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
+      <c r="U6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="V6" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="W6" s="7"/>
       <c r="X6" s="7">
         <f t="shared" ref="X6:X52" si="0">COUNTIF(F6:W6,"P")</f>
@@ -5646,7 +5653,7 @@
       </c>
       <c r="Y6" s="7">
         <f t="shared" ref="Y6:Y52" si="1">COUNTIF(F6:W6,"A")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z6" s="7">
         <f t="shared" ref="Z6:Z52" si="2">COUNTIF(F6:P6,"L")</f>
@@ -5705,8 +5712,12 @@
         <v>77</v>
       </c>
       <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
+      <c r="U7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="V7" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="W7" s="7"/>
       <c r="X7" s="7">
         <f t="shared" si="0"/>
@@ -5714,7 +5725,7 @@
       </c>
       <c r="Y7" s="7">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z7" s="7">
         <f t="shared" si="2"/>
@@ -5773,8 +5784,12 @@
         <v>77</v>
       </c>
       <c r="T8" s="27"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="27"/>
+      <c r="U8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V8" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="W8" s="27"/>
       <c r="X8" s="27">
         <f t="shared" si="0"/>
@@ -5782,7 +5797,7 @@
       </c>
       <c r="Y8" s="27">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z8" s="27">
         <f t="shared" si="2"/>
@@ -5841,16 +5856,20 @@
         <v>76</v>
       </c>
       <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
+      <c r="U9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V9" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y9" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="7">
         <f t="shared" si="2"/>
@@ -5909,12 +5928,16 @@
         <v>77</v>
       </c>
       <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
+      <c r="U10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V10" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W10" s="7"/>
       <c r="X10" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y10" s="7">
         <f t="shared" si="1"/>
@@ -5977,12 +6000,16 @@
         <v>77</v>
       </c>
       <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
+      <c r="U11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V11" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y11" s="7">
         <f t="shared" si="1"/>
@@ -6045,12 +6072,16 @@
         <v>76</v>
       </c>
       <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
+      <c r="U12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V12" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W12" s="7"/>
       <c r="X12" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y12" s="7">
         <f t="shared" si="1"/>
@@ -6113,16 +6144,20 @@
         <v>76</v>
       </c>
       <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
+      <c r="U13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="V13" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W13" s="7"/>
       <c r="X13" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y13" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" s="7">
         <f t="shared" si="2"/>
@@ -6181,16 +6216,20 @@
         <v>77</v>
       </c>
       <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
+      <c r="U14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="V14" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="W14" s="16"/>
       <c r="X14" s="16">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y14" s="16">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z14" s="16">
         <f t="shared" si="2"/>
@@ -6249,8 +6288,12 @@
         <v>76</v>
       </c>
       <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
+      <c r="U15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="V15" s="7" t="s">
+        <v>165</v>
+      </c>
       <c r="W15" s="7"/>
       <c r="X15" s="7">
         <f t="shared" si="0"/>
@@ -6258,7 +6301,7 @@
       </c>
       <c r="Y15" s="7">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z15" s="7">
         <f t="shared" si="2"/>
@@ -6317,12 +6360,16 @@
         <v>76</v>
       </c>
       <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
+      <c r="U16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="V16" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="W16" s="16"/>
       <c r="X16" s="16">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y16" s="16">
         <f t="shared" si="1"/>
@@ -6385,12 +6432,14 @@
         <v>76</v>
       </c>
       <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
+      <c r="U17" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y17" s="7">
         <f t="shared" si="1"/>
@@ -6453,12 +6502,14 @@
         <v>77</v>
       </c>
       <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
+      <c r="U18" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V18" s="7"/>
       <c r="W18" s="7"/>
       <c r="X18" s="7">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18" s="7">
         <f t="shared" si="1"/>
@@ -6521,8 +6572,12 @@
         <v>77</v>
       </c>
       <c r="T19" s="27"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="27"/>
+      <c r="U19" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V19" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="W19" s="27"/>
       <c r="X19" s="27">
         <f t="shared" si="0"/>
@@ -6530,7 +6585,7 @@
       </c>
       <c r="Y19" s="27">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z19" s="27">
         <f t="shared" si="2"/>
@@ -6589,12 +6644,16 @@
         <v>76</v>
       </c>
       <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
+      <c r="U20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V20" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W20" s="7"/>
       <c r="X20" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y20" s="7">
         <f t="shared" si="1"/>
@@ -6657,12 +6716,16 @@
         <v>76</v>
       </c>
       <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
+      <c r="U21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V21" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W21" s="7"/>
       <c r="X21" s="7">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y21" s="7">
         <f t="shared" si="1"/>
@@ -6725,12 +6788,16 @@
         <v>76</v>
       </c>
       <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
+      <c r="U22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V22" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W22" s="7"/>
       <c r="X22" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y22" s="7">
         <f t="shared" si="1"/>
@@ -6793,8 +6860,12 @@
         <v>77</v>
       </c>
       <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
+      <c r="U23" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V23" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="W23" s="27"/>
       <c r="X23" s="27">
         <f t="shared" si="0"/>
@@ -6802,7 +6873,7 @@
       </c>
       <c r="Y23" s="27">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z23" s="27">
         <f t="shared" si="2"/>
@@ -6861,12 +6932,16 @@
         <v>76</v>
       </c>
       <c r="T24" s="7"/>
-      <c r="U24" s="7"/>
-      <c r="V24" s="7"/>
+      <c r="U24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V24" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W24" s="7"/>
       <c r="X24" s="7">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y24" s="7">
         <f t="shared" si="1"/>
@@ -6929,12 +7004,16 @@
         <v>76</v>
       </c>
       <c r="T25" s="7"/>
-      <c r="U25" s="7"/>
-      <c r="V25" s="7"/>
+      <c r="U25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V25" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W25" s="7"/>
       <c r="X25" s="7">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y25" s="7">
         <f t="shared" si="1"/>
@@ -6997,8 +7076,12 @@
         <v>76</v>
       </c>
       <c r="T26" s="16"/>
-      <c r="U26" s="16"/>
-      <c r="V26" s="16"/>
+      <c r="U26" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="V26" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="W26" s="16"/>
       <c r="X26" s="16">
         <f t="shared" si="0"/>
@@ -7006,7 +7089,7 @@
       </c>
       <c r="Y26" s="16">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z26" s="16">
         <f t="shared" si="2"/>
@@ -7065,12 +7148,16 @@
         <v>76</v>
       </c>
       <c r="T27" s="7"/>
-      <c r="U27" s="7"/>
-      <c r="V27" s="7"/>
+      <c r="U27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V27" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W27" s="7"/>
       <c r="X27" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y27" s="7">
         <f t="shared" si="1"/>
@@ -7133,8 +7220,12 @@
         <v>77</v>
       </c>
       <c r="T28" s="27"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="27"/>
+      <c r="U28" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V28" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="W28" s="27"/>
       <c r="X28" s="27">
         <f t="shared" si="0"/>
@@ -7142,7 +7233,7 @@
       </c>
       <c r="Y28" s="27">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z28" s="27">
         <f t="shared" si="2"/>
@@ -7201,12 +7292,16 @@
         <v>76</v>
       </c>
       <c r="T29" s="7"/>
-      <c r="U29" s="7"/>
-      <c r="V29" s="7"/>
+      <c r="U29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V29" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W29" s="7"/>
       <c r="X29" s="7">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y29" s="7">
         <f t="shared" si="1"/>
@@ -7269,8 +7364,12 @@
         <v>77</v>
       </c>
       <c r="T30" s="27"/>
-      <c r="U30" s="27"/>
-      <c r="V30" s="27"/>
+      <c r="U30" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V30" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="W30" s="27"/>
       <c r="X30" s="27">
         <f t="shared" si="0"/>
@@ -7278,7 +7377,7 @@
       </c>
       <c r="Y30" s="27">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z30" s="27">
         <f t="shared" si="2"/>
@@ -7337,8 +7436,12 @@
         <v>77</v>
       </c>
       <c r="T31" s="27"/>
-      <c r="U31" s="27"/>
-      <c r="V31" s="27"/>
+      <c r="U31" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V31" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="W31" s="27"/>
       <c r="X31" s="27">
         <f t="shared" si="0"/>
@@ -7346,7 +7449,7 @@
       </c>
       <c r="Y31" s="27">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z31" s="27">
         <f t="shared" si="2"/>
@@ -7405,12 +7508,16 @@
         <v>76</v>
       </c>
       <c r="T32" s="7"/>
-      <c r="U32" s="7"/>
-      <c r="V32" s="7"/>
+      <c r="U32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V32" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W32" s="7"/>
       <c r="X32" s="7">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y32" s="7">
         <f t="shared" si="1"/>
@@ -7473,8 +7580,12 @@
         <v>77</v>
       </c>
       <c r="T33" s="27"/>
-      <c r="U33" s="27"/>
-      <c r="V33" s="27"/>
+      <c r="U33" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V33" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="W33" s="27"/>
       <c r="X33" s="27">
         <f t="shared" si="0"/>
@@ -7482,7 +7593,7 @@
       </c>
       <c r="Y33" s="27">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z33" s="27">
         <f t="shared" si="2"/>
@@ -7541,16 +7652,20 @@
         <v>76</v>
       </c>
       <c r="T34" s="16"/>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16"/>
+      <c r="U34" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="V34" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="W34" s="16"/>
       <c r="X34" s="16">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y34" s="16">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z34" s="16">
         <f t="shared" si="2"/>
@@ -7609,16 +7724,20 @@
         <v>76</v>
       </c>
       <c r="T35" s="7"/>
-      <c r="U35" s="7"/>
-      <c r="V35" s="7"/>
+      <c r="U35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V35" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="W35" s="7"/>
       <c r="X35" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y35" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z35" s="7">
         <f t="shared" si="2"/>
@@ -7677,8 +7796,12 @@
         <v>77</v>
       </c>
       <c r="T36" s="16"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="16"/>
+      <c r="U36" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="V36" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="W36" s="16"/>
       <c r="X36" s="16">
         <f t="shared" si="0"/>
@@ -7686,7 +7809,7 @@
       </c>
       <c r="Y36" s="16">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z36" s="7">
         <f t="shared" si="2"/>
@@ -7745,12 +7868,16 @@
         <v>76</v>
       </c>
       <c r="T37" s="7"/>
-      <c r="U37" s="7"/>
-      <c r="V37" s="7"/>
+      <c r="U37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V37" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W37" s="7"/>
       <c r="X37" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y37" s="7">
         <f t="shared" si="1"/>
@@ -7813,8 +7940,12 @@
         <v>77</v>
       </c>
       <c r="T38" s="27"/>
-      <c r="U38" s="27"/>
-      <c r="V38" s="27"/>
+      <c r="U38" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V38" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="W38" s="27"/>
       <c r="X38" s="27">
         <f t="shared" si="0"/>
@@ -7822,7 +7953,7 @@
       </c>
       <c r="Y38" s="27">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z38" s="27">
         <f t="shared" si="2"/>
@@ -7881,8 +8012,12 @@
         <v>77</v>
       </c>
       <c r="T39" s="27"/>
-      <c r="U39" s="27"/>
-      <c r="V39" s="27"/>
+      <c r="U39" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V39" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="W39" s="27"/>
       <c r="X39" s="27">
         <f t="shared" si="0"/>
@@ -7890,7 +8025,7 @@
       </c>
       <c r="Y39" s="27">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z39" s="27">
         <f t="shared" si="2"/>
@@ -7949,8 +8084,12 @@
         <v>77</v>
       </c>
       <c r="T40" s="27"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
+      <c r="U40" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V40" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="W40" s="27"/>
       <c r="X40" s="27">
         <f t="shared" si="0"/>
@@ -7958,7 +8097,7 @@
       </c>
       <c r="Y40" s="27">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z40" s="27">
         <f t="shared" si="2"/>
@@ -8017,12 +8156,16 @@
         <v>76</v>
       </c>
       <c r="T41" s="7"/>
-      <c r="U41" s="7"/>
-      <c r="V41" s="7"/>
+      <c r="U41" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="V41" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W41" s="7"/>
       <c r="X41" s="7">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y41" s="7">
         <f t="shared" si="1"/>
@@ -8085,12 +8228,16 @@
         <v>80</v>
       </c>
       <c r="T42" s="16"/>
-      <c r="U42" s="16"/>
-      <c r="V42" s="16"/>
+      <c r="U42" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="V42" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="W42" s="16"/>
       <c r="X42" s="16">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y42" s="16">
         <f t="shared" si="1"/>
@@ -8153,16 +8300,20 @@
         <v>76</v>
       </c>
       <c r="T43" s="7"/>
-      <c r="U43" s="7"/>
-      <c r="V43" s="7"/>
+      <c r="U43" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V43" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="W43" s="7"/>
       <c r="X43" s="7">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y43" s="7">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z43" s="7">
         <f t="shared" si="2"/>
@@ -8221,12 +8372,14 @@
         <v>76</v>
       </c>
       <c r="T44" s="7"/>
-      <c r="U44" s="7"/>
+      <c r="U44" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V44" s="7"/>
       <c r="W44" s="7"/>
       <c r="X44" s="7">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y44" s="7">
         <f t="shared" si="1"/>
@@ -8289,16 +8442,20 @@
         <v>76</v>
       </c>
       <c r="T45" s="7"/>
-      <c r="U45" s="7"/>
-      <c r="V45" s="7"/>
+      <c r="U45" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V45" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="W45" s="7"/>
       <c r="X45" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y45" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z45" s="7">
         <f t="shared" si="2"/>
@@ -8357,12 +8514,14 @@
         <v>76</v>
       </c>
       <c r="T46" s="7"/>
-      <c r="U46" s="7"/>
+      <c r="U46" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="V46" s="7"/>
       <c r="W46" s="7"/>
       <c r="X46" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y46" s="7">
         <f t="shared" si="1"/>
@@ -8425,12 +8584,16 @@
         <v>76</v>
       </c>
       <c r="T47" s="7"/>
-      <c r="U47" s="7"/>
-      <c r="V47" s="7"/>
+      <c r="U47" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V47" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W47" s="7"/>
       <c r="X47" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y47" s="7">
         <f t="shared" si="1"/>
@@ -8493,8 +8656,12 @@
         <v>77</v>
       </c>
       <c r="T48" s="7"/>
-      <c r="U48" s="7"/>
-      <c r="V48" s="7"/>
+      <c r="U48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="V48" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="W48" s="7"/>
       <c r="X48" s="7">
         <f t="shared" si="0"/>
@@ -8502,7 +8669,7 @@
       </c>
       <c r="Y48" s="7">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z48" s="7">
         <f t="shared" si="2"/>
@@ -8561,8 +8728,12 @@
         <v>77</v>
       </c>
       <c r="T49" s="27"/>
-      <c r="U49" s="27"/>
-      <c r="V49" s="27"/>
+      <c r="U49" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V49" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="W49" s="27"/>
       <c r="X49" s="27">
         <f t="shared" si="0"/>
@@ -8570,7 +8741,7 @@
       </c>
       <c r="Y49" s="27">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z49" s="27">
         <f t="shared" si="2"/>
@@ -8629,8 +8800,12 @@
         <v>77</v>
       </c>
       <c r="T50" s="27"/>
-      <c r="U50" s="27"/>
-      <c r="V50" s="27"/>
+      <c r="U50" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V50" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="W50" s="27"/>
       <c r="X50" s="27">
         <f t="shared" si="0"/>
@@ -8638,7 +8813,7 @@
       </c>
       <c r="Y50" s="27">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z50" s="27">
         <f t="shared" si="2"/>
@@ -8697,8 +8872,12 @@
         <v>77</v>
       </c>
       <c r="T51" s="27"/>
-      <c r="U51" s="27"/>
-      <c r="V51" s="27"/>
+      <c r="U51" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V51" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="W51" s="27"/>
       <c r="X51" s="27">
         <f t="shared" si="0"/>
@@ -8706,7 +8885,7 @@
       </c>
       <c r="Y51" s="27">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z51" s="27">
         <f t="shared" si="2"/>
@@ -8765,12 +8944,16 @@
         <v>76</v>
       </c>
       <c r="T52" s="7"/>
-      <c r="U52" s="7"/>
-      <c r="V52" s="7"/>
+      <c r="U52" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="V52" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W52" s="7"/>
       <c r="X52" s="7">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y52" s="7">
         <f t="shared" si="1"/>
@@ -8850,11 +9033,11 @@
       </c>
       <c r="U53" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="V53" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="W53" s="8">
         <f t="shared" si="3"/>
@@ -8933,11 +9116,11 @@
       </c>
       <c r="U54" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="V54" s="7">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="W54" s="7">
         <f>COUNTIF(W6:W52,"A")</f>
@@ -9016,7 +9199,7 @@
       </c>
       <c r="U55" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" s="7">
         <f t="shared" si="5"/>

--- a/BOYS PRESENT.xlsx
+++ b/BOYS PRESENT.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15600" windowHeight="11760" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15600" windowHeight="11760" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="OCT-NOV" sheetId="1" r:id="rId1"/>
     <sheet name="DEC-JAN" sheetId="2" r:id="rId2"/>
-    <sheet name="STAFF" sheetId="3" r:id="rId3"/>
+    <sheet name="FEB- MAR" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1854" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="172">
   <si>
     <t>S.NO</t>
   </si>
@@ -518,14 +518,32 @@
     <t>P.</t>
   </si>
   <si>
-    <t>.</t>
+    <t>USMAN AKMAL</t>
+  </si>
+  <si>
+    <t>M.AKMAL</t>
+  </si>
+  <si>
+    <t>03113876598</t>
+  </si>
+  <si>
+    <t>HUZAIFA KAYANI</t>
+  </si>
+  <si>
+    <t>IFTIKHAR HUSSAIN</t>
+  </si>
+  <si>
+    <t>03148064779</t>
+  </si>
+  <si>
+    <t>a</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -633,8 +651,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -667,6 +691,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -745,7 +775,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -796,6 +826,20 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -820,13 +864,10 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1138,28 +1179,28 @@
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="31" t="s">
+      <c r="E2" s="40"/>
+      <c r="F2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
     </row>
     <row r="3" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
@@ -1168,24 +1209,24 @@
       <c r="C3" s="2">
         <v>2025</v>
       </c>
-      <c r="D3" s="35"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="32"/>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="38"/>
     </row>
     <row r="5" spans="2:25" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
@@ -5161,10 +5202,10 @@
       <c r="Y57" s="21"/>
     </row>
     <row r="58" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B58" s="36" t="s">
+      <c r="B58" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="C58" s="36"/>
+      <c r="C58" s="42"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
       <c r="F58" s="8">
@@ -5237,10 +5278,10 @@
       <c r="Y58" s="21"/>
     </row>
     <row r="59" spans="2:25" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B59" s="37" t="s">
+      <c r="B59" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="C59" s="37"/>
+      <c r="C59" s="43"/>
       <c r="D59" s="9"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7">
@@ -5313,10 +5354,10 @@
       <c r="Y59" s="21"/>
     </row>
     <row r="60" spans="2:25" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B60" s="30" t="s">
+      <c r="B60" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="C60" s="30"/>
+      <c r="C60" s="36"/>
       <c r="D60" s="9"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7">
@@ -5425,30 +5466,30 @@
       <c r="C2" s="25">
         <v>45941</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="31" t="s">
+      <c r="E2" s="40"/>
+      <c r="F2" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
@@ -5460,26 +5501,26 @@
       <c r="C3" s="22">
         <v>2025</v>
       </c>
-      <c r="D3" s="35"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="32"/>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32"/>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="38"/>
+      <c r="V3" s="38"/>
+      <c r="W3" s="38"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
@@ -5588,147 +5629,159 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="14">
+    <row r="6" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="26">
         <v>1</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I6" s="38"/>
-      <c r="J6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K6" s="7" t="s">
+      <c r="F6" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="P6" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="V6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7">
+      <c r="M6" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="N6" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O6" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P6" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q6" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R6" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S6" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="T6" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="U6" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V6" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="W6" s="27"/>
+      <c r="X6" s="27">
         <f t="shared" ref="X6:X52" si="0">COUNTIF(F6:W6,"P")</f>
         <v>5</v>
       </c>
-      <c r="Y6" s="7">
+      <c r="Y6" s="27">
         <f t="shared" ref="Y6:Y52" si="1">COUNTIF(F6:W6,"A")</f>
-        <v>9</v>
-      </c>
-      <c r="Z6" s="7">
-        <f t="shared" ref="Z6:Z52" si="2">COUNTIF(F6:P6,"L")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="14">
+        <v>12</v>
+      </c>
+      <c r="Z6" s="27" t="e">
+        <f ca="1">AC13COUNTIF(F6:P6,"L")</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="26">
         <v>2</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I7" s="39"/>
-      <c r="J7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="K7" s="7" t="s">
+      <c r="F7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="K7" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="V7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7">
+      <c r="L7" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="M7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="T7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="U7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="W7" s="27"/>
+      <c r="X7" s="27">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="Y7" s="7">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="Z7" s="7">
-        <f t="shared" si="2"/>
+      <c r="Y7" s="27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="Z7" s="27">
+        <f t="shared" ref="Z7:Z52" si="2">COUNTIF(F7:P7,"L")</f>
         <v>0</v>
       </c>
     </row>
@@ -5754,7 +5807,9 @@
       <c r="H8" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="I8" s="39"/>
+      <c r="I8" s="35" t="s">
+        <v>77</v>
+      </c>
       <c r="J8" s="27" t="s">
         <v>77</v>
       </c>
@@ -5764,7 +5819,9 @@
       <c r="L8" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="M8" s="27"/>
+      <c r="M8" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="N8" s="27" t="s">
         <v>77</v>
       </c>
@@ -5783,7 +5840,9 @@
       <c r="S8" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="T8" s="27"/>
+      <c r="T8" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U8" s="27" t="s">
         <v>77</v>
       </c>
@@ -5797,7 +5856,7 @@
       </c>
       <c r="Y8" s="27">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z8" s="27">
         <f t="shared" si="2"/>
@@ -5826,7 +5885,9 @@
       <c r="H9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I9" s="39"/>
+      <c r="I9" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J9" s="7" t="s">
         <v>76</v>
       </c>
@@ -5836,7 +5897,9 @@
       <c r="L9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M9" s="7"/>
+      <c r="M9" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N9" s="7" t="s">
         <v>76</v>
       </c>
@@ -5855,7 +5918,9 @@
       <c r="S9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T9" s="7"/>
+      <c r="T9" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U9" s="7" t="s">
         <v>76</v>
       </c>
@@ -5865,7 +5930,7 @@
       <c r="W9" s="7"/>
       <c r="X9" s="7">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y9" s="7">
         <f t="shared" si="1"/>
@@ -5898,7 +5963,9 @@
       <c r="H10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="39"/>
+      <c r="I10" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J10" s="7" t="s">
         <v>76</v>
       </c>
@@ -5908,7 +5975,9 @@
       <c r="L10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M10" s="7"/>
+      <c r="M10" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N10" s="7" t="s">
         <v>76</v>
       </c>
@@ -5927,7 +5996,9 @@
       <c r="S10" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="T10" s="7"/>
+      <c r="T10" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U10" s="7" t="s">
         <v>76</v>
       </c>
@@ -5937,7 +6008,7 @@
       <c r="W10" s="7"/>
       <c r="X10" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y10" s="7">
         <f t="shared" si="1"/>
@@ -5970,7 +6041,9 @@
       <c r="H11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="39"/>
+      <c r="I11" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J11" s="7" t="s">
         <v>76</v>
       </c>
@@ -5980,7 +6053,9 @@
       <c r="L11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M11" s="7"/>
+      <c r="M11" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N11" s="7" t="s">
         <v>77</v>
       </c>
@@ -5999,7 +6074,9 @@
       <c r="S11" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="T11" s="7"/>
+      <c r="T11" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U11" s="7" t="s">
         <v>76</v>
       </c>
@@ -6009,7 +6086,7 @@
       <c r="W11" s="7"/>
       <c r="X11" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y11" s="7">
         <f t="shared" si="1"/>
@@ -6042,7 +6119,9 @@
       <c r="H12" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I12" s="39"/>
+      <c r="I12" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J12" s="7" t="s">
         <v>76</v>
       </c>
@@ -6052,7 +6131,9 @@
       <c r="L12" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M12" s="7"/>
+      <c r="M12" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N12" s="7" t="s">
         <v>76</v>
       </c>
@@ -6071,7 +6152,9 @@
       <c r="S12" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T12" s="7"/>
+      <c r="T12" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U12" s="7" t="s">
         <v>76</v>
       </c>
@@ -6081,7 +6164,7 @@
       <c r="W12" s="7"/>
       <c r="X12" s="7">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y12" s="7">
         <f t="shared" si="1"/>
@@ -6114,7 +6197,9 @@
       <c r="H13" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I13" s="39"/>
+      <c r="I13" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J13" s="7" t="s">
         <v>76</v>
       </c>
@@ -6124,7 +6209,9 @@
       <c r="L13" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M13" s="7"/>
+      <c r="M13" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N13" s="7" t="s">
         <v>76</v>
       </c>
@@ -6143,7 +6230,9 @@
       <c r="S13" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T13" s="7"/>
+      <c r="T13" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U13" s="7" t="s">
         <v>77</v>
       </c>
@@ -6153,7 +6242,7 @@
       <c r="W13" s="7"/>
       <c r="X13" s="7">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y13" s="7">
         <f t="shared" si="1"/>
@@ -6186,7 +6275,9 @@
       <c r="H14" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="I14" s="39"/>
+      <c r="I14" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J14" s="16" t="s">
         <v>76</v>
       </c>
@@ -6196,7 +6287,9 @@
       <c r="L14" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="M14" s="7"/>
+      <c r="M14" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="N14" s="16" t="s">
         <v>77</v>
       </c>
@@ -6215,7 +6308,9 @@
       <c r="S14" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="T14" s="16"/>
+      <c r="T14" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="U14" s="16" t="s">
         <v>77</v>
       </c>
@@ -6225,11 +6320,11 @@
       <c r="W14" s="16"/>
       <c r="X14" s="16">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14" s="16">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z14" s="16">
         <f t="shared" si="2"/>
@@ -6258,7 +6353,9 @@
       <c r="H15" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="39"/>
+      <c r="I15" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J15" s="7" t="s">
         <v>76</v>
       </c>
@@ -6268,7 +6365,9 @@
       <c r="L15" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M15" s="7"/>
+      <c r="M15" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N15" s="7" t="s">
         <v>77</v>
       </c>
@@ -6287,17 +6386,19 @@
       <c r="S15" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T15" s="7"/>
+      <c r="T15" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U15" s="7" t="s">
         <v>77</v>
       </c>
       <c r="V15" s="7" t="s">
-        <v>165</v>
+        <v>76</v>
       </c>
       <c r="W15" s="7"/>
       <c r="X15" s="7">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Y15" s="7">
         <f t="shared" si="1"/>
@@ -6330,7 +6431,9 @@
       <c r="H16" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="39"/>
+      <c r="I16" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J16" s="16" t="s">
         <v>76</v>
       </c>
@@ -6340,7 +6443,9 @@
       <c r="L16" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="M16" s="7"/>
+      <c r="M16" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N16" s="16" t="s">
         <v>77</v>
       </c>
@@ -6359,7 +6464,9 @@
       <c r="S16" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="T16" s="16"/>
+      <c r="T16" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="U16" s="16" t="s">
         <v>76</v>
       </c>
@@ -6369,7 +6476,7 @@
       <c r="W16" s="16"/>
       <c r="X16" s="16">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y16" s="16">
         <f t="shared" si="1"/>
@@ -6402,7 +6509,9 @@
       <c r="H17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I17" s="39"/>
+      <c r="I17" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J17" s="7" t="s">
         <v>76</v>
       </c>
@@ -6412,7 +6521,9 @@
       <c r="L17" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M17" s="7"/>
+      <c r="M17" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N17" s="7" t="s">
         <v>77</v>
       </c>
@@ -6431,15 +6542,19 @@
       <c r="S17" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T17" s="7"/>
+      <c r="T17" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U17" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="V17" s="7"/>
+      <c r="V17" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W17" s="7"/>
       <c r="X17" s="7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Y17" s="7">
         <f t="shared" si="1"/>
@@ -6472,7 +6587,9 @@
       <c r="H18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I18" s="39"/>
+      <c r="I18" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J18" s="7" t="s">
         <v>76</v>
       </c>
@@ -6482,7 +6599,9 @@
       <c r="L18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M18" s="7"/>
+      <c r="M18" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N18" s="7" t="s">
         <v>77</v>
       </c>
@@ -6501,15 +6620,19 @@
       <c r="S18" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="T18" s="7"/>
+      <c r="T18" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="V18" s="7"/>
+      <c r="V18" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="W18" s="7"/>
       <c r="X18" s="7">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Y18" s="7">
         <f t="shared" si="1"/>
@@ -6542,7 +6665,9 @@
       <c r="H19" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="I19" s="39"/>
+      <c r="I19" s="35" t="s">
+        <v>77</v>
+      </c>
       <c r="J19" s="27" t="s">
         <v>77</v>
       </c>
@@ -6552,7 +6677,9 @@
       <c r="L19" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="M19" s="27"/>
+      <c r="M19" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="N19" s="27" t="s">
         <v>77</v>
       </c>
@@ -6571,7 +6698,9 @@
       <c r="S19" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="T19" s="27"/>
+      <c r="T19" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U19" s="27" t="s">
         <v>77</v>
       </c>
@@ -6585,7 +6714,7 @@
       </c>
       <c r="Y19" s="27">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z19" s="27">
         <f t="shared" si="2"/>
@@ -6614,7 +6743,9 @@
       <c r="H20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I20" s="39"/>
+      <c r="I20" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J20" s="7" t="s">
         <v>77</v>
       </c>
@@ -6624,7 +6755,9 @@
       <c r="L20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M20" s="7"/>
+      <c r="M20" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N20" s="7" t="s">
         <v>76</v>
       </c>
@@ -6643,7 +6776,9 @@
       <c r="S20" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T20" s="7"/>
+      <c r="T20" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U20" s="7" t="s">
         <v>76</v>
       </c>
@@ -6653,7 +6788,7 @@
       <c r="W20" s="7"/>
       <c r="X20" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y20" s="7">
         <f t="shared" si="1"/>
@@ -6686,7 +6821,9 @@
       <c r="H21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I21" s="39"/>
+      <c r="I21" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J21" s="7" t="s">
         <v>76</v>
       </c>
@@ -6696,7 +6833,9 @@
       <c r="L21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M21" s="7"/>
+      <c r="M21" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="N21" s="7" t="s">
         <v>77</v>
       </c>
@@ -6715,7 +6854,9 @@
       <c r="S21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T21" s="7"/>
+      <c r="T21" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U21" s="7" t="s">
         <v>76</v>
       </c>
@@ -6725,11 +6866,11 @@
       <c r="W21" s="7"/>
       <c r="X21" s="7">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y21" s="7">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z21" s="7">
         <f t="shared" si="2"/>
@@ -6758,7 +6899,9 @@
       <c r="H22" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I22" s="39"/>
+      <c r="I22" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J22" s="7" t="s">
         <v>76</v>
       </c>
@@ -6768,7 +6911,9 @@
       <c r="L22" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M22" s="7"/>
+      <c r="M22" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N22" s="7" t="s">
         <v>76</v>
       </c>
@@ -6787,7 +6932,9 @@
       <c r="S22" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T22" s="7"/>
+      <c r="T22" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U22" s="7" t="s">
         <v>76</v>
       </c>
@@ -6797,7 +6944,7 @@
       <c r="W22" s="7"/>
       <c r="X22" s="7">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y22" s="7">
         <f t="shared" si="1"/>
@@ -6830,7 +6977,9 @@
       <c r="H23" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="I23" s="39"/>
+      <c r="I23" s="32" t="s">
+        <v>77</v>
+      </c>
       <c r="J23" s="27" t="s">
         <v>77</v>
       </c>
@@ -6840,7 +6989,9 @@
       <c r="L23" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="M23" s="7"/>
+      <c r="M23" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="N23" s="27" t="s">
         <v>77</v>
       </c>
@@ -6859,7 +7010,9 @@
       <c r="S23" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="T23" s="27"/>
+      <c r="T23" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U23" s="27" t="s">
         <v>77</v>
       </c>
@@ -6873,7 +7026,7 @@
       </c>
       <c r="Y23" s="27">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z23" s="27">
         <f t="shared" si="2"/>
@@ -6902,7 +7055,9 @@
       <c r="H24" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I24" s="39"/>
+      <c r="I24" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J24" s="7" t="s">
         <v>76</v>
       </c>
@@ -6912,7 +7067,9 @@
       <c r="L24" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M24" s="7"/>
+      <c r="M24" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N24" s="7" t="s">
         <v>76</v>
       </c>
@@ -6931,7 +7088,9 @@
       <c r="S24" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T24" s="7"/>
+      <c r="T24" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U24" s="7" t="s">
         <v>76</v>
       </c>
@@ -6941,7 +7100,7 @@
       <c r="W24" s="7"/>
       <c r="X24" s="7">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y24" s="7">
         <f t="shared" si="1"/>
@@ -6974,7 +7133,9 @@
       <c r="H25" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I25" s="39"/>
+      <c r="I25" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J25" s="7" t="s">
         <v>76</v>
       </c>
@@ -6984,7 +7145,9 @@
       <c r="L25" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M25" s="7"/>
+      <c r="M25" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N25" s="7" t="s">
         <v>164</v>
       </c>
@@ -7003,7 +7166,9 @@
       <c r="S25" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T25" s="7"/>
+      <c r="T25" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U25" s="7" t="s">
         <v>76</v>
       </c>
@@ -7013,7 +7178,7 @@
       <c r="W25" s="7"/>
       <c r="X25" s="7">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y25" s="7">
         <f t="shared" si="1"/>
@@ -7046,7 +7211,9 @@
       <c r="H26" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I26" s="39"/>
+      <c r="I26" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J26" s="16" t="s">
         <v>77</v>
       </c>
@@ -7056,7 +7223,9 @@
       <c r="L26" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="M26" s="7"/>
+      <c r="M26" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="N26" s="16" t="s">
         <v>77</v>
       </c>
@@ -7075,7 +7244,9 @@
       <c r="S26" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="T26" s="16"/>
+      <c r="T26" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="U26" s="16" t="s">
         <v>77</v>
       </c>
@@ -7085,11 +7256,11 @@
       <c r="W26" s="16"/>
       <c r="X26" s="16">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26" s="16">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z26" s="16">
         <f t="shared" si="2"/>
@@ -7118,7 +7289,9 @@
       <c r="H27" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I27" s="39"/>
+      <c r="I27" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J27" s="7" t="s">
         <v>76</v>
       </c>
@@ -7128,7 +7301,9 @@
       <c r="L27" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M27" s="7"/>
+      <c r="M27" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N27" s="7" t="s">
         <v>76</v>
       </c>
@@ -7147,7 +7322,9 @@
       <c r="S27" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T27" s="7"/>
+      <c r="T27" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U27" s="7" t="s">
         <v>76</v>
       </c>
@@ -7157,7 +7334,7 @@
       <c r="W27" s="7"/>
       <c r="X27" s="7">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y27" s="7">
         <f t="shared" si="1"/>
@@ -7190,7 +7367,9 @@
       <c r="H28" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="I28" s="39"/>
+      <c r="I28" s="35" t="s">
+        <v>76</v>
+      </c>
       <c r="J28" s="27" t="s">
         <v>76</v>
       </c>
@@ -7200,7 +7379,9 @@
       <c r="L28" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="M28" s="27"/>
+      <c r="M28" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="N28" s="27" t="s">
         <v>77</v>
       </c>
@@ -7219,7 +7400,9 @@
       <c r="S28" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="T28" s="27"/>
+      <c r="T28" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U28" s="27" t="s">
         <v>77</v>
       </c>
@@ -7229,11 +7412,11 @@
       <c r="W28" s="27"/>
       <c r="X28" s="27">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y28" s="27">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z28" s="27">
         <f t="shared" si="2"/>
@@ -7262,7 +7445,9 @@
       <c r="H29" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I29" s="39"/>
+      <c r="I29" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J29" s="7" t="s">
         <v>76</v>
       </c>
@@ -7272,7 +7457,9 @@
       <c r="L29" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M29" s="7"/>
+      <c r="M29" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N29" s="7" t="s">
         <v>76</v>
       </c>
@@ -7291,7 +7478,9 @@
       <c r="S29" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T29" s="7"/>
+      <c r="T29" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U29" s="7" t="s">
         <v>76</v>
       </c>
@@ -7301,7 +7490,7 @@
       <c r="W29" s="7"/>
       <c r="X29" s="7">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y29" s="7">
         <f t="shared" si="1"/>
@@ -7334,7 +7523,9 @@
       <c r="H30" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="I30" s="39"/>
+      <c r="I30" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J30" s="27" t="s">
         <v>76</v>
       </c>
@@ -7344,7 +7535,9 @@
       <c r="L30" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="M30" s="27"/>
+      <c r="M30" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="N30" s="27" t="s">
         <v>77</v>
       </c>
@@ -7363,7 +7556,9 @@
       <c r="S30" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="T30" s="27"/>
+      <c r="T30" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U30" s="27" t="s">
         <v>77</v>
       </c>
@@ -7373,11 +7568,11 @@
       <c r="W30" s="27"/>
       <c r="X30" s="27">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30" s="27">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z30" s="27">
         <f t="shared" si="2"/>
@@ -7406,7 +7601,9 @@
       <c r="H31" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="I31" s="39"/>
+      <c r="I31" s="35" t="s">
+        <v>77</v>
+      </c>
       <c r="J31" s="27" t="s">
         <v>77</v>
       </c>
@@ -7416,7 +7613,9 @@
       <c r="L31" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="M31" s="27"/>
+      <c r="M31" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="N31" s="27" t="s">
         <v>77</v>
       </c>
@@ -7435,7 +7634,9 @@
       <c r="S31" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="T31" s="27"/>
+      <c r="T31" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U31" s="27" t="s">
         <v>77</v>
       </c>
@@ -7449,7 +7650,7 @@
       </c>
       <c r="Y31" s="27">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Z31" s="27">
         <f t="shared" si="2"/>
@@ -7478,7 +7679,9 @@
       <c r="H32" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I32" s="39"/>
+      <c r="I32" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J32" s="7" t="s">
         <v>76</v>
       </c>
@@ -7488,7 +7691,9 @@
       <c r="L32" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M32" s="7"/>
+      <c r="M32" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N32" s="7" t="s">
         <v>76</v>
       </c>
@@ -7507,7 +7712,9 @@
       <c r="S32" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T32" s="7"/>
+      <c r="T32" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U32" s="7" t="s">
         <v>76</v>
       </c>
@@ -7517,7 +7724,7 @@
       <c r="W32" s="7"/>
       <c r="X32" s="7">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y32" s="7">
         <f t="shared" si="1"/>
@@ -7550,7 +7757,9 @@
       <c r="H33" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="I33" s="39"/>
+      <c r="I33" s="35" t="s">
+        <v>77</v>
+      </c>
       <c r="J33" s="27" t="s">
         <v>77</v>
       </c>
@@ -7560,7 +7769,9 @@
       <c r="L33" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="M33" s="27"/>
+      <c r="M33" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="N33" s="27" t="s">
         <v>77</v>
       </c>
@@ -7579,7 +7790,9 @@
       <c r="S33" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="T33" s="27"/>
+      <c r="T33" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U33" s="27" t="s">
         <v>77</v>
       </c>
@@ -7593,7 +7806,7 @@
       </c>
       <c r="Y33" s="27">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Z33" s="27">
         <f t="shared" si="2"/>
@@ -7622,7 +7835,9 @@
       <c r="H34" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I34" s="39"/>
+      <c r="I34" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J34" s="16" t="s">
         <v>76</v>
       </c>
@@ -7632,7 +7847,9 @@
       <c r="L34" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="M34" s="16"/>
+      <c r="M34" s="16" t="s">
+        <v>77</v>
+      </c>
       <c r="N34" s="16" t="s">
         <v>77</v>
       </c>
@@ -7651,7 +7868,9 @@
       <c r="S34" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="T34" s="16"/>
+      <c r="T34" s="16" t="s">
+        <v>76</v>
+      </c>
       <c r="U34" s="16" t="s">
         <v>76</v>
       </c>
@@ -7661,11 +7880,11 @@
       <c r="W34" s="16"/>
       <c r="X34" s="16">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y34" s="16">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z34" s="16">
         <f t="shared" si="2"/>
@@ -7694,7 +7913,9 @@
       <c r="H35" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I35" s="39"/>
+      <c r="I35" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J35" s="7" t="s">
         <v>76</v>
       </c>
@@ -7704,7 +7925,9 @@
       <c r="L35" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M35" s="7"/>
+      <c r="M35" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N35" s="7" t="s">
         <v>76</v>
       </c>
@@ -7723,7 +7946,9 @@
       <c r="S35" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T35" s="7"/>
+      <c r="T35" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U35" s="7" t="s">
         <v>76</v>
       </c>
@@ -7733,7 +7958,7 @@
       <c r="W35" s="7"/>
       <c r="X35" s="7">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y35" s="7">
         <f t="shared" si="1"/>
@@ -7744,74 +7969,80 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="14">
+    <row r="36" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="26">
         <v>31</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H36" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I36" s="39"/>
-      <c r="J36" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K36" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="L36" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="O36" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="P36" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q36" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="R36" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="S36" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="T36" s="16"/>
-      <c r="U36" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="V36" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="W36" s="16"/>
-      <c r="X36" s="16">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Y36" s="16">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Z36" s="7">
+      <c r="F36" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="H36" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="I36" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="J36" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K36" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="L36" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="M36" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="N36" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="O36" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P36" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q36" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R36" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S36" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="T36" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="U36" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V36" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="W36" s="27"/>
+      <c r="X36" s="27">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="Y36" s="27">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="Z36" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -7838,7 +8069,9 @@
       <c r="H37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I37" s="39"/>
+      <c r="I37" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J37" s="7" t="s">
         <v>76</v>
       </c>
@@ -7848,7 +8081,9 @@
       <c r="L37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M37" s="7"/>
+      <c r="M37" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N37" s="7" t="s">
         <v>76</v>
       </c>
@@ -7867,7 +8102,9 @@
       <c r="S37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T37" s="7"/>
+      <c r="T37" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U37" s="7" t="s">
         <v>76</v>
       </c>
@@ -7877,7 +8114,7 @@
       <c r="W37" s="7"/>
       <c r="X37" s="7">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y37" s="7">
         <f t="shared" si="1"/>
@@ -7910,7 +8147,9 @@
       <c r="H38" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="I38" s="39"/>
+      <c r="I38" s="35" t="s">
+        <v>77</v>
+      </c>
       <c r="J38" s="27" t="s">
         <v>77</v>
       </c>
@@ -7920,7 +8159,9 @@
       <c r="L38" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="M38" s="27"/>
+      <c r="M38" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="N38" s="27" t="s">
         <v>77</v>
       </c>
@@ -7939,7 +8180,9 @@
       <c r="S38" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="T38" s="27"/>
+      <c r="T38" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U38" s="27" t="s">
         <v>77</v>
       </c>
@@ -7953,7 +8196,7 @@
       </c>
       <c r="Y38" s="27">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Z38" s="27">
         <f t="shared" si="2"/>
@@ -7982,7 +8225,9 @@
       <c r="H39" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="I39" s="39"/>
+      <c r="I39" s="35" t="s">
+        <v>77</v>
+      </c>
       <c r="J39" s="27" t="s">
         <v>77</v>
       </c>
@@ -7992,7 +8237,9 @@
       <c r="L39" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="M39" s="27"/>
+      <c r="M39" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="N39" s="27" t="s">
         <v>77</v>
       </c>
@@ -8011,7 +8258,9 @@
       <c r="S39" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="T39" s="27"/>
+      <c r="T39" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U39" s="27" t="s">
         <v>77</v>
       </c>
@@ -8025,7 +8274,7 @@
       </c>
       <c r="Y39" s="27">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z39" s="27">
         <f t="shared" si="2"/>
@@ -8054,7 +8303,9 @@
       <c r="H40" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="I40" s="39"/>
+      <c r="I40" s="35" t="s">
+        <v>76</v>
+      </c>
       <c r="J40" s="27" t="s">
         <v>77</v>
       </c>
@@ -8064,7 +8315,9 @@
       <c r="L40" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="M40" s="27"/>
+      <c r="M40" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="N40" s="27" t="s">
         <v>77</v>
       </c>
@@ -8083,7 +8336,9 @@
       <c r="S40" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="T40" s="27"/>
+      <c r="T40" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U40" s="27" t="s">
         <v>77</v>
       </c>
@@ -8093,11 +8348,11 @@
       <c r="W40" s="27"/>
       <c r="X40" s="27">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y40" s="27">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z40" s="27">
         <f t="shared" si="2"/>
@@ -8126,7 +8381,9 @@
       <c r="H41" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="I41" s="39"/>
+      <c r="I41" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J41" s="7" t="s">
         <v>76</v>
       </c>
@@ -8136,7 +8393,9 @@
       <c r="L41" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="M41" s="7"/>
+      <c r="M41" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="N41" s="7" t="s">
         <v>77</v>
       </c>
@@ -8155,7 +8414,9 @@
       <c r="S41" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T41" s="7"/>
+      <c r="T41" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U41" s="7" t="s">
         <v>80</v>
       </c>
@@ -8165,11 +8426,11 @@
       <c r="W41" s="7"/>
       <c r="X41" s="7">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y41" s="7">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z41" s="7">
         <f t="shared" si="2"/>
@@ -8198,7 +8459,9 @@
       <c r="H42" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I42" s="39"/>
+      <c r="I42" s="32" t="s">
+        <v>77</v>
+      </c>
       <c r="J42" s="16" t="s">
         <v>80</v>
       </c>
@@ -8208,7 +8471,9 @@
       <c r="L42" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="M42" s="16"/>
+      <c r="M42" s="16" t="s">
+        <v>80</v>
+      </c>
       <c r="N42" s="16" t="s">
         <v>80</v>
       </c>
@@ -8227,7 +8492,9 @@
       <c r="S42" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="T42" s="16"/>
+      <c r="T42" s="16" t="s">
+        <v>80</v>
+      </c>
       <c r="U42" s="16" t="s">
         <v>76</v>
       </c>
@@ -8241,11 +8508,11 @@
       </c>
       <c r="Y42" s="16">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z42" s="16">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
@@ -8270,7 +8537,9 @@
       <c r="H43" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I43" s="39"/>
+      <c r="I43" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J43" s="7" t="s">
         <v>76</v>
       </c>
@@ -8280,7 +8549,9 @@
       <c r="L43" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M43" s="7"/>
+      <c r="M43" s="7" t="s">
+        <v>77</v>
+      </c>
       <c r="N43" s="7" t="s">
         <v>77</v>
       </c>
@@ -8299,7 +8570,9 @@
       <c r="S43" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T43" s="7"/>
+      <c r="T43" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U43" s="7" t="s">
         <v>76</v>
       </c>
@@ -8309,11 +8582,11 @@
       <c r="W43" s="7"/>
       <c r="X43" s="7">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y43" s="7">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z43" s="7">
         <f t="shared" si="2"/>
@@ -8342,7 +8615,9 @@
       <c r="H44" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I44" s="39"/>
+      <c r="I44" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J44" s="7" t="s">
         <v>77</v>
       </c>
@@ -8352,7 +8627,9 @@
       <c r="L44" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="M44" s="7"/>
+      <c r="M44" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N44" s="7" t="s">
         <v>80</v>
       </c>
@@ -8371,7 +8648,9 @@
       <c r="S44" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T44" s="7"/>
+      <c r="T44" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U44" s="7" t="s">
         <v>76</v>
       </c>
@@ -8379,7 +8658,7 @@
       <c r="W44" s="7"/>
       <c r="X44" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y44" s="7">
         <f t="shared" si="1"/>
@@ -8412,7 +8691,9 @@
       <c r="H45" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I45" s="39"/>
+      <c r="I45" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J45" s="7" t="s">
         <v>76</v>
       </c>
@@ -8422,7 +8703,9 @@
       <c r="L45" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M45" s="7"/>
+      <c r="M45" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N45" s="7" t="s">
         <v>76</v>
       </c>
@@ -8441,7 +8724,9 @@
       <c r="S45" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T45" s="7"/>
+      <c r="T45" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U45" s="7" t="s">
         <v>76</v>
       </c>
@@ -8451,7 +8736,7 @@
       <c r="W45" s="7"/>
       <c r="X45" s="7">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y45" s="7">
         <f t="shared" si="1"/>
@@ -8484,7 +8769,9 @@
       <c r="H46" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I46" s="39"/>
+      <c r="I46" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J46" s="7" t="s">
         <v>76</v>
       </c>
@@ -8494,7 +8781,9 @@
       <c r="L46" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M46" s="7"/>
+      <c r="M46" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N46" s="7" t="s">
         <v>76</v>
       </c>
@@ -8513,7 +8802,9 @@
       <c r="S46" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T46" s="7"/>
+      <c r="T46" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U46" s="7" t="s">
         <v>76</v>
       </c>
@@ -8521,7 +8812,7 @@
       <c r="W46" s="7"/>
       <c r="X46" s="7">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y46" s="7">
         <f t="shared" si="1"/>
@@ -8554,7 +8845,9 @@
       <c r="H47" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I47" s="39"/>
+      <c r="I47" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="J47" s="7" t="s">
         <v>76</v>
       </c>
@@ -8564,7 +8857,9 @@
       <c r="L47" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M47" s="7"/>
+      <c r="M47" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N47" s="7" t="s">
         <v>76</v>
       </c>
@@ -8583,7 +8878,9 @@
       <c r="S47" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T47" s="7"/>
+      <c r="T47" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U47" s="7" t="s">
         <v>76</v>
       </c>
@@ -8593,7 +8890,7 @@
       <c r="W47" s="7"/>
       <c r="X47" s="7">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y47" s="7">
         <f t="shared" si="1"/>
@@ -8604,74 +8901,80 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="14">
+    <row r="48" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B48" s="26">
         <v>43</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="F48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I48" s="39"/>
-      <c r="J48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="L48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="O48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="P48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="R48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="S48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="T48" s="7"/>
-      <c r="U48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="V48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="W48" s="7"/>
-      <c r="X48" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y48" s="7">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="Z48" s="7">
+      <c r="F48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="H48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I48" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="J48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="K48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="N48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="O48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="P48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="R48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="S48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="T48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="U48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="V48" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="W48" s="27"/>
+      <c r="X48" s="27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="27">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="Z48" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -8698,7 +9001,9 @@
       <c r="H49" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="I49" s="39"/>
+      <c r="I49" s="35" t="s">
+        <v>77</v>
+      </c>
       <c r="J49" s="27" t="s">
         <v>77</v>
       </c>
@@ -8708,7 +9013,9 @@
       <c r="L49" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="M49" s="27"/>
+      <c r="M49" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="N49" s="27" t="s">
         <v>77</v>
       </c>
@@ -8727,7 +9034,9 @@
       <c r="S49" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="T49" s="27"/>
+      <c r="T49" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U49" s="27" t="s">
         <v>77</v>
       </c>
@@ -8741,7 +9050,7 @@
       </c>
       <c r="Y49" s="27">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z49" s="27">
         <f t="shared" si="2"/>
@@ -8770,7 +9079,9 @@
       <c r="H50" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="I50" s="39"/>
+      <c r="I50" s="35" t="s">
+        <v>77</v>
+      </c>
       <c r="J50" s="27" t="s">
         <v>77</v>
       </c>
@@ -8780,7 +9091,9 @@
       <c r="L50" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="M50" s="27"/>
+      <c r="M50" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="N50" s="27" t="s">
         <v>77</v>
       </c>
@@ -8799,7 +9112,9 @@
       <c r="S50" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="T50" s="27"/>
+      <c r="T50" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U50" s="27" t="s">
         <v>77</v>
       </c>
@@ -8813,7 +9128,7 @@
       </c>
       <c r="Y50" s="27">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z50" s="27">
         <f t="shared" si="2"/>
@@ -8842,7 +9157,9 @@
       <c r="H51" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="I51" s="39"/>
+      <c r="I51" s="35" t="s">
+        <v>77</v>
+      </c>
       <c r="J51" s="27" t="s">
         <v>77</v>
       </c>
@@ -8852,7 +9169,9 @@
       <c r="L51" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="M51" s="27"/>
+      <c r="M51" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="N51" s="27" t="s">
         <v>77</v>
       </c>
@@ -8871,7 +9190,9 @@
       <c r="S51" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="T51" s="27"/>
+      <c r="T51" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U51" s="27" t="s">
         <v>77</v>
       </c>
@@ -8885,7 +9206,7 @@
       </c>
       <c r="Y51" s="27">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Z51" s="27">
         <f t="shared" si="2"/>
@@ -8914,7 +9235,9 @@
       <c r="H52" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I52" s="40"/>
+      <c r="I52" s="33" t="s">
+        <v>76</v>
+      </c>
       <c r="J52" s="7" t="s">
         <v>76</v>
       </c>
@@ -8924,7 +9247,9 @@
       <c r="L52" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="M52" s="7"/>
+      <c r="M52" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="N52" s="7" t="s">
         <v>76</v>
       </c>
@@ -8943,7 +9268,9 @@
       <c r="S52" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T52" s="7"/>
+      <c r="T52" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="U52" s="7" t="s">
         <v>76</v>
       </c>
@@ -8953,7 +9280,7 @@
       <c r="W52" s="7"/>
       <c r="X52" s="7">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y52" s="7">
         <f t="shared" si="1"/>
@@ -8965,14 +9292,14 @@
       </c>
     </row>
     <row r="53" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="36" t="s">
+      <c r="B53" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="C53" s="36"/>
+      <c r="C53" s="42"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
       <c r="F53" s="8">
-        <f t="shared" ref="F53:W53" si="3">COUNTIF(F6:F52,"P")</f>
+        <f t="shared" ref="F53:H53" si="3">COUNTIF(F6:F52,"P")</f>
         <v>31</v>
       </c>
       <c r="G53" s="8">
@@ -8984,63 +9311,63 @@
         <v>30</v>
       </c>
       <c r="I53" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" ref="I53:W53" si="4">COUNTIF(I6:I52,"P")</f>
+        <v>33</v>
       </c>
       <c r="J53" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="K53" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>34</v>
       </c>
       <c r="L53" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>32</v>
       </c>
       <c r="M53" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>23</v>
       </c>
       <c r="N53" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="O53" s="8">
-        <f>COUNTIF(O6:O52,"P")</f>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="P53" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="Q53" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="R53" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="S53" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="T53" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>27</v>
       </c>
       <c r="U53" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="V53" s="8">
-        <f t="shared" si="3"/>
-        <v>19</v>
+        <f t="shared" si="4"/>
+        <v>22</v>
       </c>
       <c r="W53" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X53" s="7"/>
@@ -9048,82 +9375,82 @@
       <c r="Z53" s="7"/>
     </row>
     <row r="54" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B54" s="37" t="s">
+      <c r="B54" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="C54" s="37"/>
+      <c r="C54" s="43"/>
       <c r="D54" s="9"/>
       <c r="E54" s="7"/>
       <c r="F54" s="7">
-        <f t="shared" ref="F54:V54" si="4">COUNTIF(F6:F52,"A")</f>
+        <f t="shared" ref="F54:H54" si="5">COUNTIF(F6:F52,"A")</f>
         <v>15</v>
       </c>
       <c r="G54" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="H54" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="I54" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" ref="I54:W54" si="6">COUNTIF(I6:I52,"A")</f>
+        <v>14</v>
       </c>
       <c r="J54" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="K54" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="L54" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="M54" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>23</v>
       </c>
       <c r="N54" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>27</v>
       </c>
       <c r="O54" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
       <c r="P54" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="Q54" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="R54" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="S54" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="T54" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="U54" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="V54" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="W54" s="7">
-        <f>COUNTIF(W6:W52,"A")</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X54" s="7"/>
@@ -9131,82 +9458,82 @@
       <c r="Z54" s="7"/>
     </row>
     <row r="55" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B55" s="30" t="s">
+      <c r="B55" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="C55" s="30"/>
+      <c r="C55" s="36"/>
       <c r="D55" s="9"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7">
-        <f t="shared" ref="F55:V55" si="5">COUNTIF(F6:F52,"L")</f>
+        <f t="shared" ref="F55:H55" si="7">COUNTIF(F6:F52,"L")</f>
         <v>1</v>
       </c>
       <c r="G55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="I55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="I55:W55" si="8">COUNTIF(I6:I52,"L")</f>
         <v>0</v>
       </c>
       <c r="J55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M55" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="N55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="O55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="P55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="Q55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="R55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="S55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="T55" s="7">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
       <c r="U55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="V55" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W55" s="7">
-        <f>COUNTIF(W6:W52,"L")</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X55" s="7"/>
@@ -9214,13 +9541,12 @@
       <c r="Z55" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="B55:C55"/>
     <mergeCell ref="D2:E3"/>
     <mergeCell ref="F2:W3"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="B54:C54"/>
-    <mergeCell ref="I6:I52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9228,295 +9554,210 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:AA13"/>
+  <dimension ref="A2:Z43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" hidden="1" customWidth="1"/>
-    <col min="7" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="33.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:27" x14ac:dyDescent="0.25">
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2" s="31"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="C3" s="24"/>
+    </row>
+    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="25">
+      <c r="C4" s="25">
         <v>45941</v>
       </c>
-      <c r="E2" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="34"/>
-      <c r="G2" s="31" t="s">
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-    </row>
-    <row r="3" spans="3:27" x14ac:dyDescent="0.25">
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="22">
-        <v>2025</v>
-      </c>
-      <c r="E3" s="35"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="32"/>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32"/>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-    </row>
-    <row r="4" spans="3:27" x14ac:dyDescent="0.25">
-      <c r="C4" s="5"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
+      <c r="S4" s="37"/>
+      <c r="T4" s="37"/>
+      <c r="U4" s="37"/>
+      <c r="V4" s="37"/>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-    </row>
-    <row r="5" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C5" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="23" t="s">
+    </row>
+    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="22">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="44"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="37"/>
+      <c r="T5" s="37"/>
+      <c r="U5" s="37"/>
+      <c r="V5" s="37"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+    </row>
+    <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="8">
-        <v>6</v>
-      </c>
-      <c r="H5" s="8">
+      <c r="F7" s="8">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8">
         <v>7</v>
       </c>
-      <c r="I5" s="8">
+      <c r="H7" s="8">
+        <v>8</v>
+      </c>
+      <c r="I7" s="8">
+        <v>14</v>
+      </c>
+      <c r="J7" s="8">
+        <v>15</v>
+      </c>
+      <c r="K7" s="8">
+        <v>21</v>
+      </c>
+      <c r="L7" s="8">
+        <v>22</v>
+      </c>
+      <c r="M7" s="8">
+        <v>28</v>
+      </c>
+      <c r="N7" s="8">
+        <v>1</v>
+      </c>
+      <c r="O7" s="8">
+        <v>7</v>
+      </c>
+      <c r="P7" s="8">
+        <v>8</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>14</v>
+      </c>
+      <c r="R7" s="8">
+        <v>15</v>
+      </c>
+      <c r="S7" s="8">
+        <v>21</v>
+      </c>
+      <c r="T7" s="8">
+        <v>22</v>
+      </c>
+      <c r="U7" s="8">
+        <v>28</v>
+      </c>
+      <c r="V7" s="8">
+        <v>29</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="X7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y7" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="14">
+        <v>1</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="8">
-        <v>14</v>
-      </c>
-      <c r="K5" s="8">
-        <v>20</v>
-      </c>
-      <c r="L5" s="8">
-        <v>21</v>
-      </c>
-      <c r="M5" s="8">
-        <v>27</v>
-      </c>
-      <c r="N5" s="8">
-        <v>28</v>
-      </c>
-      <c r="O5" s="8">
-        <v>3</v>
-      </c>
-      <c r="P5" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>10</v>
-      </c>
-      <c r="R5" s="8">
-        <v>11</v>
-      </c>
-      <c r="S5" s="8">
-        <v>17</v>
-      </c>
-      <c r="T5" s="8">
-        <v>18</v>
-      </c>
-      <c r="U5" s="8">
-        <v>24</v>
-      </c>
-      <c r="V5" s="8">
-        <v>25</v>
-      </c>
-      <c r="W5" s="8">
-        <v>31</v>
-      </c>
-      <c r="X5" s="8">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z5" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C6" s="14">
-        <v>47</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7">
-        <f>COUNTIF(G6:X6,"P")</f>
-        <v>3</v>
-      </c>
-      <c r="Z6" s="7">
-        <f>COUNTIF(G6:X6,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="AA6" s="7">
-        <f>COUNTIF(G6:Q6,"L")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C7" s="14">
-        <v>48</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7">
-        <f>COUNTIF(G7:X7,"P")</f>
-        <v>1</v>
-      </c>
-      <c r="Z7" s="7">
-        <f>COUNTIF(G7:X7,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="AA7" s="7">
-        <f>COUNTIF(G7:Q7,"L")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C8" s="14">
-        <v>49</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>149</v>
+      <c r="D8" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>76</v>
@@ -9525,9 +9766,11 @@
         <v>76</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J8" s="7"/>
+        <v>171</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
@@ -9540,42 +9783,47 @@
       <c r="T8" s="7"/>
       <c r="U8" s="7"/>
       <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
+      <c r="W8" s="7">
+        <f t="shared" ref="W8:W35" si="0">COUNTIF(F8:V8,"P")</f>
+        <v>4</v>
+      </c>
+      <c r="X8" s="7">
+        <f t="shared" ref="X8:X35" si="1">COUNTIF(F8:V8,"A")</f>
+        <v>1</v>
+      </c>
       <c r="Y8" s="7">
-        <f>COUNTIF(G8:X8,"P")</f>
-        <v>3</v>
-      </c>
-      <c r="Z8" s="7">
-        <f>COUNTIF(G8:X8,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="AA8" s="7">
-        <f>COUNTIF(G8:Q8,"L")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C9" s="14">
-        <v>50</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>150</v>
+        <f t="shared" ref="Y8:Y40" si="2">COUNTIF(F8:O8,"L")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="14">
+        <v>2</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
@@ -9588,42 +9836,47 @@
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
+      <c r="W9" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X9" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="Y9" s="7">
-        <f>COUNTIF(G9:X9,"P")</f>
-        <v>0</v>
-      </c>
-      <c r="Z9" s="7">
-        <f>COUNTIF(G9:X9,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="AA9" s="7">
-        <f>COUNTIF(G9:Q9,"L")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C10" s="14">
-        <v>51</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>159</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="14">
+        <v>3</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
+      <c r="I10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>163</v>
+      </c>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
@@ -9636,260 +9889,1846 @@
       <c r="T10" s="7"/>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
+      <c r="W10" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X10" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="Y10" s="7">
-        <f>COUNTIF(G10:X10,"P")</f>
-        <v>1</v>
-      </c>
-      <c r="Z10" s="7">
-        <f>COUNTIF(G10:X10,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="7">
-        <f>COUNTIF(G10:Q10,"L")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="T11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="X11" s="8" t="e">
-        <f>COUNTIF(#REF!,"P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
-    </row>
-    <row r="12" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C12" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="T12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="X12" s="7" t="e">
-        <f>COUNTIF(#REF!,"A")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
-    </row>
-    <row r="13" spans="3:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C13" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="N13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="O13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="P13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Q13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="R13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="S13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="T13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="14">
+        <v>4</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X11" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="14">
+        <v>5</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" s="16"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X12" s="16">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Y12" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="14">
+        <v>6</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
-      <c r="W13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="X13" s="7" t="e">
-        <f>COUNTIF(#REF!,"L")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="7"/>
+      <c r="W13" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="X13" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y13" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="14">
+        <v>7</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" s="16"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X14" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="14">
+        <v>8</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X15" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="14">
+        <v>9</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X16" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="14">
+        <v>10</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X17" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="14">
+        <v>11</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X18" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="14">
+        <v>12</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X19" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="14">
+        <v>13</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X20" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Y20" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="14">
+        <v>14</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X21" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Y21" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="14">
+        <v>15</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K22" s="16"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="16"/>
+      <c r="W22" s="16">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="X22" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y22" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="14">
+        <v>16</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X23" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="14">
+        <v>17</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X24" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B25" s="14">
+        <v>18</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X25" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Y25" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="14">
+        <v>19</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="16"/>
+      <c r="U26" s="16"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="16">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X26" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="14">
+        <v>20</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X27" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="14">
+        <v>21</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X28" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="14">
+        <v>22</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="X29" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y29" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="14">
+        <v>23</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="J30" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="16"/>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="16"/>
+      <c r="S30" s="16"/>
+      <c r="T30" s="16"/>
+      <c r="U30" s="16"/>
+      <c r="V30" s="16"/>
+      <c r="W30" s="16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="X30" s="16">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Y30" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="14">
+        <v>24</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X31" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="14">
+        <v>25</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="7"/>
+      <c r="V32" s="7"/>
+      <c r="W32" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X32" s="7">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Y32" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="14">
+        <v>26</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X33" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B34" s="14">
+        <v>27</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="X34" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="14">
+        <v>28</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X35" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y35" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="14">
+        <v>29</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="7"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+      <c r="U36" s="7"/>
+      <c r="V36" s="7"/>
+      <c r="W36" s="7">
+        <v>0</v>
+      </c>
+      <c r="X36" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B37" s="14">
+        <v>30</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7">
+        <v>0</v>
+      </c>
+      <c r="X37" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="14">
+        <v>31</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="7"/>
+      <c r="W38" s="7">
+        <v>0</v>
+      </c>
+      <c r="X38" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="14">
+        <v>32</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
+      <c r="Y39" s="7"/>
+    </row>
+    <row r="40" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B40" s="14">
+        <v>33</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="7"/>
+      <c r="W40" s="7">
+        <f>COUNTIF(F40:V40,"P")</f>
+        <v>3</v>
+      </c>
+      <c r="X40" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B41" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="42"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="8">
+        <f t="shared" ref="F41:W41" si="3">COUNTIF(F8:F40,"P")</f>
+        <v>26</v>
+      </c>
+      <c r="G41" s="8">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="H41" s="8">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="I41" s="8">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="J41" s="8">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="K41" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L41" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N41" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O41" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P41" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R41" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X41" s="7"/>
+      <c r="Y41" s="7"/>
+      <c r="Z41" s="7"/>
+    </row>
+    <row r="42" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B42" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" s="43"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7">
+        <f t="shared" ref="F42:W42" si="4">COUNTIF(F8:F40,"A")</f>
+        <v>5</v>
+      </c>
+      <c r="G42" s="7">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H42" s="7">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="I42" s="7">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="J42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W42" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X42" s="7"/>
+      <c r="Y42" s="7"/>
+      <c r="Z42" s="7"/>
+    </row>
+    <row r="43" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B43" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7">
+        <f t="shared" ref="F43:W43" si="5">COUNTIF(F8:F40,"L")</f>
+        <v>2</v>
+      </c>
+      <c r="G43" s="7">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I43" s="7">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="J43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W43" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X43" s="7"/>
+      <c r="Y43" s="7"/>
+      <c r="Z43" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="E2:F3"/>
-    <mergeCell ref="G2:X3"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D4:E5"/>
+    <mergeCell ref="F4:V5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/BOYS PRESENT.xlsx
+++ b/BOYS PRESENT.xlsx
@@ -4,12 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15600" windowHeight="11760" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15570" windowHeight="11760" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="OCT-NOV" sheetId="1" r:id="rId1"/>
     <sheet name="DEC-JAN" sheetId="2" r:id="rId2"/>
-    <sheet name="FEB- MAR" sheetId="4" r:id="rId3"/>
+    <sheet name="FEB- MAR-APR" sheetId="4" r:id="rId3"/>
+    <sheet name="APR- MAY-JUN" sheetId="5" r:id="rId4"/>
+    <sheet name="JUN-JUL-AUG" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="144525"/>
   <extLst>
@@ -21,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3108" uniqueCount="180">
   <si>
     <t>S.NO</t>
   </si>
@@ -537,6 +539,30 @@
   </si>
   <si>
     <t>a</t>
+  </si>
+  <si>
+    <t>salman khan</t>
+  </si>
+  <si>
+    <t>hamzullah</t>
+  </si>
+  <si>
+    <t>03452140357</t>
+  </si>
+  <si>
+    <t>PP</t>
+  </si>
+  <si>
+    <t>.P</t>
+  </si>
+  <si>
+    <t>MONTHLY TURNOUT</t>
+  </si>
+  <si>
+    <t>SALMAN KHAN</t>
+  </si>
+  <si>
+    <t>HAMZAULLAH</t>
   </si>
 </sst>
 </file>
@@ -658,7 +684,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -697,6 +723,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -775,7 +807,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -869,6 +901,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1143,7 +1178,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2049,7 +2084,7 @@
       </c>
       <c r="Y15" s="21"/>
     </row>
-    <row r="16" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="B16" s="14">
         <v>11</v>
       </c>
@@ -2124,7 +2159,7 @@
       </c>
       <c r="Y16" s="21"/>
     </row>
-    <row r="17" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B17" s="14">
         <v>12</v>
       </c>
@@ -2199,7 +2234,7 @@
       </c>
       <c r="Y17" s="21"/>
     </row>
-    <row r="18" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B18" s="14">
         <v>13</v>
       </c>
@@ -2274,7 +2309,7 @@
       </c>
       <c r="Y18" s="21"/>
     </row>
-    <row r="19" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="B19" s="14">
         <v>14</v>
       </c>
@@ -2349,7 +2384,7 @@
       </c>
       <c r="Y19" s="21"/>
     </row>
-    <row r="20" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B20" s="14">
         <v>15</v>
       </c>
@@ -2424,7 +2459,7 @@
       </c>
       <c r="Y20" s="21"/>
     </row>
-    <row r="21" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B21" s="14">
         <v>16</v>
       </c>
@@ -2499,7 +2534,7 @@
       </c>
       <c r="Y21" s="21"/>
     </row>
-    <row r="22" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B22" s="14">
         <v>17</v>
       </c>
@@ -2574,7 +2609,7 @@
       </c>
       <c r="Y22" s="21"/>
     </row>
-    <row r="23" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B23" s="14">
         <v>18</v>
       </c>
@@ -2649,7 +2684,7 @@
       </c>
       <c r="Y23" s="21"/>
     </row>
-    <row r="24" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B24" s="14">
         <v>19</v>
       </c>
@@ -2724,7 +2759,7 @@
       </c>
       <c r="Y24" s="21"/>
     </row>
-    <row r="25" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B25" s="14">
         <v>20</v>
       </c>
@@ -2799,7 +2834,7 @@
       </c>
       <c r="Y25" s="21"/>
     </row>
-    <row r="26" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="B26" s="14">
         <v>21</v>
       </c>
@@ -2876,7 +2911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B27" s="14">
         <v>22</v>
       </c>
@@ -2951,7 +2986,7 @@
       </c>
       <c r="Y27" s="21"/>
     </row>
-    <row r="28" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B28" s="14">
         <v>23</v>
       </c>
@@ -3026,7 +3061,7 @@
       </c>
       <c r="Y28" s="21"/>
     </row>
-    <row r="29" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B29" s="14">
         <v>24</v>
       </c>
@@ -3101,7 +3136,7 @@
       </c>
       <c r="Y29" s="21"/>
     </row>
-    <row r="30" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B30" s="14">
         <v>25</v>
       </c>
@@ -3176,7 +3211,7 @@
       </c>
       <c r="Y30" s="21"/>
     </row>
-    <row r="31" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B31" s="14">
         <v>26</v>
       </c>
@@ -3251,7 +3286,7 @@
       </c>
       <c r="Y31" s="21"/>
     </row>
-    <row r="32" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B32" s="14">
         <v>27</v>
       </c>
@@ -3326,7 +3361,7 @@
       </c>
       <c r="Y32" s="21"/>
     </row>
-    <row r="33" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B33" s="14">
         <v>28</v>
       </c>
@@ -3401,7 +3436,7 @@
       </c>
       <c r="Y33" s="21"/>
     </row>
-    <row r="34" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="B34" s="14">
         <v>29</v>
       </c>
@@ -3476,7 +3511,7 @@
       </c>
       <c r="Y34" s="21"/>
     </row>
-    <row r="35" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B35" s="14">
         <v>30</v>
       </c>
@@ -3551,7 +3586,7 @@
       </c>
       <c r="Y35" s="21"/>
     </row>
-    <row r="36" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="B36" s="14">
         <v>31</v>
       </c>
@@ -3626,7 +3661,7 @@
       </c>
       <c r="Y36" s="21"/>
     </row>
-    <row r="37" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B37" s="14">
         <v>32</v>
       </c>
@@ -3701,7 +3736,7 @@
       </c>
       <c r="Y37" s="21"/>
     </row>
-    <row r="38" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="B38" s="14">
         <v>33</v>
       </c>
@@ -3776,7 +3811,7 @@
       </c>
       <c r="Y38" s="21"/>
     </row>
-    <row r="39" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="B39" s="17">
         <v>34</v>
       </c>
@@ -3851,7 +3886,7 @@
       </c>
       <c r="Y39" s="21"/>
     </row>
-    <row r="40" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B40" s="14">
         <v>35</v>
       </c>
@@ -3926,7 +3961,7 @@
       </c>
       <c r="Y40" s="21"/>
     </row>
-    <row r="41" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B41" s="14">
         <v>36</v>
       </c>
@@ -4001,7 +4036,7 @@
       </c>
       <c r="Y41" s="21"/>
     </row>
-    <row r="42" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="B42" s="17">
         <v>37</v>
       </c>
@@ -4076,7 +4111,7 @@
       </c>
       <c r="Y42" s="21"/>
     </row>
-    <row r="43" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B43" s="14">
         <v>38</v>
       </c>
@@ -4151,7 +4186,7 @@
       </c>
       <c r="Y43" s="21"/>
     </row>
-    <row r="44" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B44" s="14">
         <v>39</v>
       </c>
@@ -4226,7 +4261,7 @@
       </c>
       <c r="Y44" s="21"/>
     </row>
-    <row r="45" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B45" s="14">
         <v>40</v>
       </c>
@@ -4301,7 +4336,7 @@
       </c>
       <c r="Y45" s="21"/>
     </row>
-    <row r="46" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B46" s="14">
         <v>41</v>
       </c>
@@ -4376,7 +4411,7 @@
       </c>
       <c r="Y46" s="21"/>
     </row>
-    <row r="47" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B47" s="14">
         <v>42</v>
       </c>
@@ -4451,7 +4486,7 @@
       </c>
       <c r="Y47" s="21"/>
     </row>
-    <row r="48" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B48" s="14">
         <v>43</v>
       </c>
@@ -4526,7 +4561,7 @@
       </c>
       <c r="Y48" s="21"/>
     </row>
-    <row r="49" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B49" s="14">
         <v>44</v>
       </c>
@@ -4601,7 +4636,7 @@
       </c>
       <c r="Y49" s="21"/>
     </row>
-    <row r="50" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B50" s="14">
         <v>45</v>
       </c>
@@ -4676,7 +4711,7 @@
       </c>
       <c r="Y50" s="21"/>
     </row>
-    <row r="51" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B51" s="14">
         <v>46</v>
       </c>
@@ -4751,7 +4786,7 @@
       </c>
       <c r="Y51" s="21"/>
     </row>
-    <row r="52" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B52" s="14">
         <v>47</v>
       </c>
@@ -4826,7 +4861,7 @@
       </c>
       <c r="Y52" s="21"/>
     </row>
-    <row r="53" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B53" s="14">
         <v>48</v>
       </c>
@@ -4901,7 +4936,7 @@
       </c>
       <c r="Y53" s="21"/>
     </row>
-    <row r="54" spans="2:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:25" ht="15" x14ac:dyDescent="0.25">
       <c r="B54" s="14">
         <v>49</v>
       </c>
@@ -6253,7 +6288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14" s="14">
         <v>9</v>
       </c>
@@ -6331,7 +6366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B15" s="14">
         <v>10</v>
       </c>
@@ -6409,7 +6444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B16" s="14">
         <v>11</v>
       </c>
@@ -6487,7 +6522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B17" s="14">
         <v>12</v>
       </c>
@@ -6565,7 +6600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B18" s="14">
         <v>13</v>
       </c>
@@ -6643,7 +6678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:26" s="29" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B19" s="26">
         <v>14</v>
       </c>
@@ -6721,7 +6756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B20" s="14">
         <v>15</v>
       </c>
@@ -6799,7 +6834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B21" s="14">
         <v>16</v>
       </c>
@@ -6877,7 +6912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B22" s="14">
         <v>17</v>
       </c>
@@ -6955,7 +6990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:26" s="29" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B23" s="26">
         <v>18</v>
       </c>
@@ -7033,7 +7068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B24" s="14">
         <v>19</v>
       </c>
@@ -7111,7 +7146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B25" s="14">
         <v>20</v>
       </c>
@@ -7189,7 +7224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B26" s="14">
         <v>21</v>
       </c>
@@ -7267,7 +7302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B27" s="14">
         <v>22</v>
       </c>
@@ -7345,7 +7380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:26" s="29" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B28" s="26">
         <v>23</v>
       </c>
@@ -7423,7 +7458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B29" s="14">
         <v>24</v>
       </c>
@@ -7501,7 +7536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:26" s="29" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B30" s="26">
         <v>25</v>
       </c>
@@ -7579,7 +7614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:26" s="29" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B31" s="26">
         <v>26</v>
       </c>
@@ -7657,7 +7692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B32" s="14">
         <v>27</v>
       </c>
@@ -7735,7 +7770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:26" s="29" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B33" s="26">
         <v>28</v>
       </c>
@@ -7813,7 +7848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B34" s="14">
         <v>29</v>
       </c>
@@ -7891,7 +7926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B35" s="14">
         <v>30</v>
       </c>
@@ -7969,7 +8004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:26" s="29" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B36" s="26">
         <v>31</v>
       </c>
@@ -8047,7 +8082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B37" s="14">
         <v>32</v>
       </c>
@@ -8125,7 +8160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:26" s="29" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B38" s="26">
         <v>33</v>
       </c>
@@ -8203,7 +8238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:26" s="29" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B39" s="26">
         <v>34</v>
       </c>
@@ -8281,7 +8316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:26" s="29" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:26" s="29" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B40" s="26">
         <v>35</v>
       </c>
@@ -9554,7 +9589,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:Z43"/>
+  <dimension ref="A2:Z44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="27.28515625" customWidth="1"/>
@@ -9704,16 +9739,16 @@
         <v>22</v>
       </c>
       <c r="M7" s="8">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="N7" s="8">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O7" s="8">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="P7" s="8">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="Q7" s="8">
         <v>14</v>
@@ -9771,6 +9806,5287 @@
       <c r="J8" s="7" t="s">
         <v>76</v>
       </c>
+      <c r="K8" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7">
+        <f t="shared" ref="W8:W35" si="0">COUNTIF(F8:V8,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="X8" s="7">
+        <f t="shared" ref="X8:X35" si="1">COUNTIF(F8:V8,"A")</f>
+        <v>1</v>
+      </c>
+      <c r="Y8" s="7">
+        <f t="shared" ref="Y8:Y41" si="2">COUNTIF(F8:O8,"L")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="14">
+        <v>2</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="X9" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y9" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="14">
+        <v>3</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X10" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="14">
+        <v>4</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X11" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="14">
+        <v>5</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="O12" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="P12" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="X12" s="16">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Y12" s="16">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="14">
+        <v>6</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="X13" s="7">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Y13" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="14">
+        <v>7</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="O14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X14" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y14" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="14">
+        <v>8</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X15" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y15" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="14">
+        <v>9</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X16" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y16" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="14">
+        <v>10</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X17" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y17" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="14">
+        <v>11</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X18" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="14">
+        <v>12</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X19" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="14">
+        <v>13</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="X20" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Y20" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="14">
+        <v>14</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X21" s="7">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="Y21" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="14">
+        <v>15</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="O22" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="P22" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="16"/>
+      <c r="W22" s="16">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X22" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y22" s="16">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="14">
+        <v>16</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X23" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y23" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="14">
+        <v>17</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X24" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B25" s="14">
+        <v>18</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="X25" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Y25" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B26" s="14">
+        <v>19</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="O26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="P26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="16"/>
+      <c r="U26" s="16"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="16">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X26" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="16">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B27" s="14">
+        <v>20</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X27" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B28" s="14">
+        <v>21</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X28" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B29" s="14">
+        <v>22</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X29" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y29" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B30" s="14">
+        <v>23</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="J30" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N30" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="O30" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="P30" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="16"/>
+      <c r="S30" s="16"/>
+      <c r="T30" s="16"/>
+      <c r="U30" s="16"/>
+      <c r="V30" s="16"/>
+      <c r="W30" s="16">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X30" s="16">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Y30" s="16">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B31" s="14">
+        <v>24</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X31" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B32" s="14">
+        <v>25</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="O32" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P32" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="7"/>
+      <c r="V32" s="7"/>
+      <c r="W32" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X32" s="7">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="Y32" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B33" s="14">
+        <v>26</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X33" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="7">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B34" s="14">
+        <v>27</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X34" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B35" s="14">
+        <v>28</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="O35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="X35" s="7">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Y35" s="7">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B36" s="14">
+        <v>29</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+      <c r="U36" s="7"/>
+      <c r="V36" s="7"/>
+      <c r="W36" s="7">
+        <v>0</v>
+      </c>
+      <c r="X36" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B37" s="14">
+        <v>30</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7">
+        <v>0</v>
+      </c>
+      <c r="X37" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B38" s="14">
+        <v>31</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N38" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="O38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="7"/>
+      <c r="W38" s="7">
+        <v>0</v>
+      </c>
+      <c r="X38" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B39" s="14">
+        <v>32</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M39" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="O39" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P39" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
+      <c r="Y39" s="7"/>
+    </row>
+    <row r="40" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B40" s="14">
+        <v>33</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N40" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="7"/>
+      <c r="W40" s="7"/>
+      <c r="X40" s="7"/>
+      <c r="Y40" s="7"/>
+    </row>
+    <row r="41" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B41" s="14">
+        <v>34</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7">
+        <f>COUNTIF(F41:V41,"P")</f>
+        <v>8</v>
+      </c>
+      <c r="X41" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B42" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="42"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="8">
+        <f t="shared" ref="F42:W42" si="3">COUNTIF(F8:F41,"P")</f>
+        <v>26</v>
+      </c>
+      <c r="G42" s="8">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="H42" s="8">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="I42" s="8">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="J42" s="8">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="K42" s="8">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="L42" s="8">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="M42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="8">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="O42" s="8">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="P42" s="8">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="Q42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X42" s="7"/>
+      <c r="Y42" s="7"/>
+      <c r="Z42" s="7"/>
+    </row>
+    <row r="43" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B43" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="43"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7">
+        <f t="shared" ref="F43:W43" si="4">COUNTIF(F8:F41,"A")</f>
+        <v>6</v>
+      </c>
+      <c r="G43" s="7">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H43" s="7">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="I43" s="7">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J43" s="7">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="K43" s="7">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="L43" s="7">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="M43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N43" s="7">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="O43" s="7">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="P43" s="7">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="Q43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X43" s="7"/>
+      <c r="Y43" s="7"/>
+      <c r="Z43" s="7"/>
+    </row>
+    <row r="44" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B44" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="36"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7">
+        <f t="shared" ref="F44:W44" si="5">COUNTIF(F8:F41,"L")</f>
+        <v>2</v>
+      </c>
+      <c r="G44" s="7">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="7">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="J44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="7">
+        <f t="shared" si="5"/>
+        <v>34</v>
+      </c>
+      <c r="N44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O44" s="7">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="P44" s="7">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X44" s="7"/>
+      <c r="Y44" s="7"/>
+      <c r="Z44" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D4:E5"/>
+    <mergeCell ref="F4:V5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B3:Z44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="C3" s="24"/>
+    </row>
+    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="25">
+        <v>45941</v>
+      </c>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
+      <c r="S4" s="37"/>
+      <c r="T4" s="37"/>
+      <c r="U4" s="37"/>
+      <c r="V4" s="37"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+    </row>
+    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="22">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="44"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="37"/>
+      <c r="T5" s="37"/>
+      <c r="U5" s="37"/>
+      <c r="V5" s="37"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+    </row>
+    <row r="6" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+    </row>
+    <row r="7" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="8">
+        <v>26</v>
+      </c>
+      <c r="G7" s="8">
+        <v>2</v>
+      </c>
+      <c r="H7" s="8">
+        <v>3</v>
+      </c>
+      <c r="I7" s="8">
+        <v>9</v>
+      </c>
+      <c r="J7" s="8">
+        <v>10</v>
+      </c>
+      <c r="K7" s="8">
+        <v>16</v>
+      </c>
+      <c r="L7" s="8">
+        <v>17</v>
+      </c>
+      <c r="M7" s="8">
+        <v>23</v>
+      </c>
+      <c r="N7" s="8">
+        <v>24</v>
+      </c>
+      <c r="O7" s="8">
+        <v>30</v>
+      </c>
+      <c r="P7" s="8">
+        <v>31</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>6</v>
+      </c>
+      <c r="R7" s="8">
+        <v>7</v>
+      </c>
+      <c r="S7" s="8">
+        <v>13</v>
+      </c>
+      <c r="T7" s="8">
+        <v>14</v>
+      </c>
+      <c r="U7" s="8">
+        <v>20</v>
+      </c>
+      <c r="V7" s="8">
+        <v>21</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="X7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y7" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="14">
+        <v>1</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7">
+        <f t="shared" ref="W8:W35" si="0">COUNTIF(F8:V8,"P")</f>
+        <v>10</v>
+      </c>
+      <c r="X8" s="7">
+        <f t="shared" ref="X8:X35" si="1">COUNTIF(F8:V8,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="7">
+        <f t="shared" ref="Y8:Y41" si="2">COUNTIF(F8:O8,"L")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="14">
+        <v>2</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X9" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y9" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="14">
+        <v>3</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X10" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y10" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="14">
+        <v>4</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X11" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y11" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B12" s="14">
+        <v>5</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="O12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="P12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="R12" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X12" s="16">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="Y12" s="16">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B13" s="14">
+        <v>6</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X13" s="7">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="Y13" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="14">
+        <v>7</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="O14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="R14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X14" s="16">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Y14" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B15" s="14">
+        <v>8</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="X15" s="7">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Y15" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B16" s="14">
+        <v>9</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X16" s="7">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Y16" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B17" s="14">
+        <v>10</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X17" s="7">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Y17" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B18" s="14">
+        <v>11</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X18" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B19" s="14">
+        <v>12</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X19" s="7">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Y19" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B20" s="14">
+        <v>13</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X20" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B21" s="14">
+        <v>14</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X21" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y21" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B22" s="14">
+        <v>15</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="O22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="P22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="R22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="S22" s="16"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="16"/>
+      <c r="W22" s="16">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X22" s="16">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="Y22" s="16">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B23" s="14">
+        <v>16</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="X23" s="7">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Y23" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B24" s="14">
+        <v>17</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X24" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y24" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B25" s="14">
+        <v>18</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X25" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B26" s="14">
+        <v>19</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="O26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="16"/>
+      <c r="U26" s="16"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="16">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X26" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y26" s="16">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B27" s="14">
+        <v>20</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="X27" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y27" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B28" s="14">
+        <v>21</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X28" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B29" s="14">
+        <v>22</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R29" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X29" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B30" s="14">
+        <v>23</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="N30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="O30" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="P30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="R30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="S30" s="16"/>
+      <c r="T30" s="16"/>
+      <c r="U30" s="16"/>
+      <c r="V30" s="16"/>
+      <c r="W30" s="16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X30" s="16">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="Y30" s="16">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B31" s="14">
+        <v>24</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X31" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y31" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B32" s="14">
+        <v>25</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="7"/>
+      <c r="V32" s="7"/>
+      <c r="W32" s="7">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="X32" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y32" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B33" s="14">
+        <v>26</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
+      <c r="V33" s="7"/>
+      <c r="W33" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X33" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B34" s="14">
+        <v>27</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R34" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="7"/>
+      <c r="W34" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="X34" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B35" s="14">
+        <v>28</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="X35" s="7">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="Y35" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B36" s="14">
+        <v>29</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R36" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+      <c r="U36" s="7"/>
+      <c r="V36" s="7"/>
+      <c r="W36" s="7">
+        <v>0</v>
+      </c>
+      <c r="X36" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B37" s="14">
+        <v>30</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R37" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7">
+        <v>0</v>
+      </c>
+      <c r="X37" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B38" s="14">
+        <v>31</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="7"/>
+      <c r="W38" s="7">
+        <v>0</v>
+      </c>
+      <c r="X38" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B39" s="14">
+        <v>32</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M39" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O39" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="P39" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q39" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R39" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
+      <c r="Y39" s="7"/>
+    </row>
+    <row r="40" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B40" s="14">
+        <v>33</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P40" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="R40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="7"/>
+      <c r="W40" s="7"/>
+      <c r="X40" s="7"/>
+      <c r="Y40" s="7"/>
+    </row>
+    <row r="41" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B41" s="14">
+        <v>34</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="P41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="R41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7">
+        <f>COUNTIF(F41:V41,"P")</f>
+        <v>7</v>
+      </c>
+      <c r="X41" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="7">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B42" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="42"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="8">
+        <f t="shared" ref="F42:W42" si="3">COUNTIF(F8:F41,"P")</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="8">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="H42" s="8">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="I42" s="8">
+        <f>COUNTIF(I8:I41,"P")</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="8">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="L42" s="8">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="M42" s="8">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="N42" s="8">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="O42" s="8">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="P42" s="8">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="Q42" s="8">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="R42" s="8">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="S42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W42" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X42" s="7"/>
+      <c r="Y42" s="7"/>
+      <c r="Z42" s="7"/>
+    </row>
+    <row r="43" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B43" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="43"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7">
+        <f t="shared" ref="F43:W43" si="4">COUNTIF(F8:F41,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="7">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="H43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I43" s="7">
+        <f>COUNTIF(I8:I41,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="7">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="L43" s="7">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="M43" s="7">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="N43" s="7">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="O43" s="7">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="P43" s="7">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="Q43" s="7">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="R43" s="7">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="S43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W43" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X43" s="7"/>
+      <c r="Y43" s="7"/>
+      <c r="Z43" s="7"/>
+    </row>
+    <row r="44" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B44" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="36"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7">
+        <f t="shared" ref="F44:W44" si="5">COUNTIF(F8:F41,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="7">
+        <f>COUNTIF(I8:I41,"L")</f>
+        <v>34</v>
+      </c>
+      <c r="J44" s="7">
+        <f t="shared" si="5"/>
+        <v>34</v>
+      </c>
+      <c r="K44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W44" s="7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X44" s="7"/>
+      <c r="Y44" s="7"/>
+      <c r="Z44" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D4:E5"/>
+    <mergeCell ref="F4:V5"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B3:Z44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:25" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="C3" s="24"/>
+    </row>
+    <row r="4" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="25">
+        <v>45941</v>
+      </c>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="37"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
+      <c r="S4" s="37"/>
+      <c r="T4" s="37"/>
+      <c r="U4" s="37"/>
+      <c r="V4" s="37"/>
+      <c r="W4" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="46"/>
+    </row>
+    <row r="5" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="22">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="44"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="37"/>
+      <c r="T5" s="37"/>
+      <c r="U5" s="37"/>
+      <c r="V5" s="37"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="46"/>
+      <c r="Y5" s="46"/>
+    </row>
+    <row r="6" spans="2:25" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+    </row>
+    <row r="7" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="8">
+        <v>27</v>
+      </c>
+      <c r="G7" s="8">
+        <v>28</v>
+      </c>
+      <c r="H7" s="8">
+        <v>4</v>
+      </c>
+      <c r="I7" s="8">
+        <v>5</v>
+      </c>
+      <c r="J7" s="8">
+        <v>8</v>
+      </c>
+      <c r="K7" s="8">
+        <v>9</v>
+      </c>
+      <c r="L7" s="8">
+        <v>15</v>
+      </c>
+      <c r="M7" s="8">
+        <v>16</v>
+      </c>
+      <c r="N7" s="8">
+        <v>22</v>
+      </c>
+      <c r="O7" s="8">
+        <v>23</v>
+      </c>
+      <c r="P7" s="8">
+        <v>29</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>30</v>
+      </c>
+      <c r="R7" s="8">
+        <v>3</v>
+      </c>
+      <c r="S7" s="8">
+        <v>4</v>
+      </c>
+      <c r="T7" s="8">
+        <v>10</v>
+      </c>
+      <c r="U7" s="8">
+        <v>11</v>
+      </c>
+      <c r="V7" s="8">
+        <v>17</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="X7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y7" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="14">
+        <v>1</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
@@ -9783,20 +15099,11 @@
       <c r="T8" s="7"/>
       <c r="U8" s="7"/>
       <c r="V8" s="7"/>
-      <c r="W8" s="7">
-        <f t="shared" ref="W8:W35" si="0">COUNTIF(F8:V8,"P")</f>
-        <v>4</v>
-      </c>
-      <c r="X8" s="7">
-        <f t="shared" ref="X8:X35" si="1">COUNTIF(F8:V8,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="Y8" s="7">
-        <f t="shared" ref="Y8:Y40" si="2">COUNTIF(F8:O8,"L")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+    </row>
+    <row r="9" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="14">
         <v>2</v>
       </c>
@@ -9810,20 +15117,12 @@
         <v>46</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
@@ -9836,20 +15135,11 @@
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
-      <c r="W9" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X9" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+    </row>
+    <row r="10" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="14">
         <v>3</v>
       </c>
@@ -9863,20 +15153,12 @@
         <v>47</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>163</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
@@ -9889,20 +15171,11 @@
       <c r="T10" s="7"/>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
-      <c r="W10" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X10" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+    </row>
+    <row r="11" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" s="14">
         <v>4</v>
       </c>
@@ -9918,18 +15191,10 @@
       <c r="F11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
@@ -9942,20 +15207,11 @@
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
-      <c r="W11" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X11" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+    </row>
+    <row r="12" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="14">
         <v>5</v>
       </c>
@@ -9969,22 +15225,14 @@
         <v>49</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G12" s="16"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
       <c r="K12" s="16"/>
-      <c r="L12" s="7"/>
+      <c r="L12" s="16"/>
       <c r="M12" s="16"/>
       <c r="N12" s="16"/>
       <c r="O12" s="16"/>
@@ -9995,20 +15243,11 @@
       <c r="T12" s="16"/>
       <c r="U12" s="16"/>
       <c r="V12" s="16"/>
-      <c r="W12" s="16">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="X12" s="16">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="Y12" s="16">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+    </row>
+    <row r="13" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13" s="14">
         <v>6</v>
       </c>
@@ -10022,20 +15261,12 @@
         <v>50</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
@@ -10048,20 +15279,11 @@
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
-      <c r="W13" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="X13" s="7">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y13" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+    </row>
+    <row r="14" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14" s="14">
         <v>7</v>
       </c>
@@ -10075,22 +15297,14 @@
         <v>51</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I14" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G14" s="16"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
       <c r="K14" s="16"/>
-      <c r="L14" s="7"/>
+      <c r="L14" s="16"/>
       <c r="M14" s="16"/>
       <c r="N14" s="16"/>
       <c r="O14" s="16"/>
@@ -10101,20 +15315,11 @@
       <c r="T14" s="16"/>
       <c r="U14" s="16"/>
       <c r="V14" s="16"/>
-      <c r="W14" s="16">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X14" s="16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W14" s="16"/>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="7"/>
+    </row>
+    <row r="15" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B15" s="14">
         <v>8</v>
       </c>
@@ -10128,20 +15333,12 @@
         <v>51</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
@@ -10154,20 +15351,11 @@
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
-      <c r="W15" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X15" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+    </row>
+    <row r="16" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B16" s="14">
         <v>9</v>
       </c>
@@ -10181,20 +15369,12 @@
         <v>52</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
@@ -10207,20 +15387,11 @@
       <c r="T16" s="7"/>
       <c r="U16" s="7"/>
       <c r="V16" s="7"/>
-      <c r="W16" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X16" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+    </row>
+    <row r="17" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B17" s="14">
         <v>10</v>
       </c>
@@ -10236,18 +15407,10 @@
       <c r="F17" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
@@ -10260,20 +15423,11 @@
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
-      <c r="W17" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X17" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7"/>
+    </row>
+    <row r="18" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B18" s="14">
         <v>11</v>
       </c>
@@ -10289,18 +15443,10 @@
       <c r="F18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
@@ -10313,20 +15459,11 @@
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
       <c r="V18" s="7"/>
-      <c r="W18" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X18" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+    </row>
+    <row r="19" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B19" s="14">
         <v>12</v>
       </c>
@@ -10342,18 +15479,10 @@
       <c r="F19" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
@@ -10366,20 +15495,11 @@
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
-      <c r="W19" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X19" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+    </row>
+    <row r="20" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B20" s="14">
         <v>13</v>
       </c>
@@ -10395,18 +15515,10 @@
       <c r="F20" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
@@ -10419,20 +15531,11 @@
       <c r="T20" s="7"/>
       <c r="U20" s="7"/>
       <c r="V20" s="7"/>
-      <c r="W20" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="X20" s="7">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="Y20" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7"/>
+    </row>
+    <row r="21" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B21" s="14">
         <v>14</v>
       </c>
@@ -10448,18 +15551,10 @@
       <c r="F21" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
@@ -10472,20 +15567,11 @@
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
-      <c r="W21" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="X21" s="7">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="Y21" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W21" s="7"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+    </row>
+    <row r="22" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B22" s="14">
         <v>15</v>
       </c>
@@ -10499,22 +15585,14 @@
         <v>108</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="J22" s="16" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G22" s="16"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
       <c r="K22" s="16"/>
-      <c r="L22" s="7"/>
+      <c r="L22" s="16"/>
       <c r="M22" s="16"/>
       <c r="N22" s="16"/>
       <c r="O22" s="16"/>
@@ -10525,20 +15603,11 @@
       <c r="T22" s="16"/>
       <c r="U22" s="16"/>
       <c r="V22" s="16"/>
-      <c r="W22" s="16">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="X22" s="16">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y22" s="16">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W22" s="16"/>
+      <c r="X22" s="16"/>
+      <c r="Y22" s="16"/>
+    </row>
+    <row r="23" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B23" s="14">
         <v>16</v>
       </c>
@@ -10554,18 +15623,10 @@
       <c r="F23" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
       <c r="M23" s="7"/>
@@ -10578,20 +15639,11 @@
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
-      <c r="W23" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X23" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y23" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+    </row>
+    <row r="24" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B24" s="14">
         <v>17</v>
       </c>
@@ -10607,18 +15659,10 @@
       <c r="F24" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
       <c r="M24" s="7"/>
@@ -10631,20 +15675,11 @@
       <c r="T24" s="7"/>
       <c r="U24" s="7"/>
       <c r="V24" s="7"/>
-      <c r="W24" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X24" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y24" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W24" s="7"/>
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7"/>
+    </row>
+    <row r="25" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B25" s="14">
         <v>18</v>
       </c>
@@ -10660,18 +15695,10 @@
       <c r="F25" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
       <c r="M25" s="7"/>
@@ -10684,20 +15711,11 @@
       <c r="T25" s="7"/>
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
-      <c r="W25" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="X25" s="7">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="Y25" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+    </row>
+    <row r="26" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B26" s="14">
         <v>19</v>
       </c>
@@ -10713,18 +15731,10 @@
       <c r="F26" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="G26" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="J26" s="16" t="s">
-        <v>76</v>
-      </c>
+      <c r="G26" s="16"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
       <c r="K26" s="16"/>
       <c r="L26" s="16"/>
       <c r="M26" s="16"/>
@@ -10737,20 +15747,11 @@
       <c r="T26" s="16"/>
       <c r="U26" s="16"/>
       <c r="V26" s="16"/>
-      <c r="W26" s="16">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X26" s="16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y26" s="16">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W26" s="16"/>
+      <c r="X26" s="16"/>
+      <c r="Y26" s="16"/>
+    </row>
+    <row r="27" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B27" s="14">
         <v>20</v>
       </c>
@@ -10766,18 +15767,10 @@
       <c r="F27" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
       <c r="M27" s="7"/>
@@ -10790,20 +15783,11 @@
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
-      <c r="W27" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X27" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y27" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W27" s="7"/>
+      <c r="X27" s="7"/>
+      <c r="Y27" s="7"/>
+    </row>
+    <row r="28" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B28" s="14">
         <v>21</v>
       </c>
@@ -10819,18 +15803,10 @@
       <c r="F28" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G28" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
       <c r="M28" s="7"/>
@@ -10843,20 +15819,11 @@
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
       <c r="V28" s="7"/>
-      <c r="W28" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X28" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y28" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W28" s="7"/>
+      <c r="X28" s="7"/>
+      <c r="Y28" s="7"/>
+    </row>
+    <row r="29" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B29" s="14">
         <v>22</v>
       </c>
@@ -10872,18 +15839,10 @@
       <c r="F29" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G29" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
       <c r="M29" s="7"/>
@@ -10896,20 +15855,11 @@
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
-      <c r="W29" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="X29" s="7">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y29" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W29" s="7"/>
+      <c r="X29" s="7"/>
+      <c r="Y29" s="7"/>
+    </row>
+    <row r="30" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B30" s="14">
         <v>23</v>
       </c>
@@ -10925,18 +15875,10 @@
       <c r="F30" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="G30" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="H30" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I30" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>76</v>
-      </c>
+      <c r="G30" s="16"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
@@ -10949,20 +15891,11 @@
       <c r="T30" s="16"/>
       <c r="U30" s="16"/>
       <c r="V30" s="16"/>
-      <c r="W30" s="16">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="X30" s="16">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="Y30" s="16">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W30" s="16"/>
+      <c r="X30" s="16"/>
+      <c r="Y30" s="16"/>
+    </row>
+    <row r="31" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B31" s="14">
         <v>24</v>
       </c>
@@ -10976,20 +15909,12 @@
         <v>123</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
       <c r="M31" s="7"/>
@@ -11002,20 +15927,11 @@
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
-      <c r="W31" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X31" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
+      <c r="Y31" s="7"/>
+    </row>
+    <row r="32" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B32" s="14">
         <v>25</v>
       </c>
@@ -11029,20 +15945,12 @@
         <v>71</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
       <c r="M32" s="7"/>
@@ -11055,20 +15963,11 @@
       <c r="T32" s="7"/>
       <c r="U32" s="7"/>
       <c r="V32" s="7"/>
-      <c r="W32" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="X32" s="7">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="Y32" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W32" s="7"/>
+      <c r="X32" s="7"/>
+      <c r="Y32" s="7"/>
+    </row>
+    <row r="33" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B33" s="14">
         <v>26</v>
       </c>
@@ -11084,18 +15983,10 @@
       <c r="F33" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G33" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
       <c r="M33" s="7"/>
@@ -11108,20 +15999,11 @@
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
-      <c r="W33" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X33" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W33" s="7"/>
+      <c r="X33" s="7"/>
+      <c r="Y33" s="7"/>
+    </row>
+    <row r="34" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B34" s="14">
         <v>27</v>
       </c>
@@ -11135,20 +16017,12 @@
         <v>129</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c r="M34" s="7"/>
@@ -11161,20 +16035,11 @@
       <c r="T34" s="7"/>
       <c r="U34" s="7"/>
       <c r="V34" s="7"/>
-      <c r="W34" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="X34" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="7">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W34" s="7"/>
+      <c r="X34" s="7"/>
+      <c r="Y34" s="7"/>
+    </row>
+    <row r="35" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B35" s="14">
         <v>28</v>
       </c>
@@ -11188,20 +16053,12 @@
         <v>74</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c r="M35" s="7"/>
@@ -11214,20 +16071,11 @@
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
-      <c r="W35" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="X35" s="7">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Y35" s="7">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W35" s="7"/>
+      <c r="X35" s="7"/>
+      <c r="Y35" s="7"/>
+    </row>
+    <row r="36" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B36" s="14">
         <v>29</v>
       </c>
@@ -11241,20 +16089,12 @@
         <v>167</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
@@ -11267,17 +16107,11 @@
       <c r="T36" s="7"/>
       <c r="U36" s="7"/>
       <c r="V36" s="7"/>
-      <c r="W36" s="7">
-        <v>0</v>
-      </c>
-      <c r="X36" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W36" s="7"/>
+      <c r="X36" s="7"/>
+      <c r="Y36" s="7"/>
+    </row>
+    <row r="37" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B37" s="14">
         <v>30</v>
       </c>
@@ -11293,18 +16127,10 @@
       <c r="F37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
@@ -11317,17 +16143,11 @@
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
-      <c r="W37" s="7">
-        <v>0</v>
-      </c>
-      <c r="X37" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W37" s="7"/>
+      <c r="X37" s="7"/>
+      <c r="Y37" s="7"/>
+    </row>
+    <row r="38" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B38" s="14">
         <v>31</v>
       </c>
@@ -11341,20 +16161,12 @@
         <v>170</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
@@ -11367,17 +16179,11 @@
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
       <c r="V38" s="7"/>
-      <c r="W38" s="7">
-        <v>0</v>
-      </c>
-      <c r="X38" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W38" s="7"/>
+      <c r="X38" s="7"/>
+      <c r="Y38" s="7"/>
+    </row>
+    <row r="39" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B39" s="14">
         <v>32</v>
       </c>
@@ -11391,20 +16197,12 @@
         <v>42</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
       <c r="M39" s="7"/>
@@ -11421,31 +16219,25 @@
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
     </row>
-    <row r="40" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B40" s="14">
         <v>33</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>76</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -11459,274 +16251,303 @@
       <c r="T40" s="7"/>
       <c r="U40" s="7"/>
       <c r="V40" s="7"/>
-      <c r="W40" s="7">
-        <f>COUNTIF(F40:V40,"P")</f>
-        <v>3</v>
-      </c>
-      <c r="X40" s="7">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="7">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="42" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="42"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="8">
-        <f t="shared" ref="F41:W41" si="3">COUNTIF(F8:F40,"P")</f>
-        <v>26</v>
-      </c>
-      <c r="G41" s="8">
-        <f t="shared" si="3"/>
-        <v>28</v>
-      </c>
-      <c r="H41" s="8">
-        <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-      <c r="I41" s="8">
-        <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
-      <c r="J41" s="8">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-      <c r="K41" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L41" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M41" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N41" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O41" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P41" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q41" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R41" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S41" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T41" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U41" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V41" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W41" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="W40" s="7"/>
+      <c r="X40" s="7"/>
+      <c r="Y40" s="7"/>
+    </row>
+    <row r="41" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B41" s="14">
+        <v>34</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="7"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
-      <c r="Z41" s="7"/>
-    </row>
-    <row r="42" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B42" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="43"/>
-      <c r="D42" s="9"/>
+    </row>
+    <row r="42" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B42" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="42"/>
+      <c r="D42" s="7"/>
       <c r="E42" s="7"/>
-      <c r="F42" s="7">
-        <f t="shared" ref="F42:W42" si="4">COUNTIF(F8:F40,"A")</f>
-        <v>5</v>
-      </c>
-      <c r="G42" s="7">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="H42" s="7">
-        <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="I42" s="7">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="J42" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K42" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L42" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M42" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N42" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O42" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P42" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q42" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R42" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S42" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T42" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U42" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V42" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W42" s="7">
-        <f t="shared" si="4"/>
+      <c r="F42" s="8">
+        <f t="shared" ref="F42:W42" si="0">COUNTIF(F8:F41,"P")</f>
+        <v>16</v>
+      </c>
+      <c r="G42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="8">
+        <f>COUNTIF(I8:I41,"P")</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="V42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="W42" s="8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X42" s="7"/>
       <c r="Y42" s="7"/>
       <c r="Z42" s="7"/>
     </row>
-    <row r="43" spans="2:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="36"/>
+    <row r="43" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B43" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="43"/>
       <c r="D43" s="9"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7">
-        <f t="shared" ref="F43:W43" si="5">COUNTIF(F8:F40,"L")</f>
-        <v>2</v>
+        <f t="shared" ref="F43:W43" si="1">COUNTIF(F8:F41,"A")</f>
+        <v>18</v>
       </c>
       <c r="G43" s="7">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I43" s="7">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f>COUNTIF(I8:I41,"A")</f>
+        <v>0</v>
       </c>
       <c r="J43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="T43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="V43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W43" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="7"/>
     </row>
+    <row r="44" spans="2:26" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B44" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="36"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7">
+        <f t="shared" ref="F44:W44" si="2">COUNTIF(F8:F41,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="7">
+        <f>COUNTIF(I8:I41,"L")</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W44" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X44" s="7"/>
+      <c r="Y44" s="7"/>
+      <c r="Z44" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B41:C41"/>
+  <mergeCells count="6">
+    <mergeCell ref="W4:Y5"/>
+    <mergeCell ref="D4:E5"/>
+    <mergeCell ref="F4:V5"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D4:E5"/>
-    <mergeCell ref="F4:V5"/>
+    <mergeCell ref="B44:C44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
